--- a/excel/unidades.xlsx
+++ b/excel/unidades.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daniel.jimenez\Documents\dev\implementacion_eds_imb\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AE624FA-5570-4007-956A-D4FA9A7699BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{410D42FE-D3D2-4321-990A-B6F64A290D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-67320" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A71EBC0A-EF77-4480-B2A6-100C25EC669C}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{A71EBC0A-EF77-4480-B2A6-100C25EC669C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7935" uniqueCount="1764">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7955" uniqueCount="1771">
   <si>
     <t>CLUES</t>
   </si>
@@ -5332,6 +5332,27 @@
   <si>
     <t>TOTAL
 CAMAS</t>
+  </si>
+  <si>
+    <t>20.9018891</t>
+  </si>
+  <si>
+    <t>-89.6419666</t>
+  </si>
+  <si>
+    <t>21.0193421</t>
+  </si>
+  <si>
+    <t>-89.5819034</t>
+  </si>
+  <si>
+    <t>JIUTEPEC</t>
+  </si>
+  <si>
+    <t>18.8759753</t>
+  </si>
+  <si>
+    <t>-99.1693427</t>
   </si>
 </sst>
 </file>
@@ -5341,7 +5362,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5400,6 +5421,19 @@
       <u/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Noto Sans"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -5483,7 +5517,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -5519,11 +5553,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5581,658 +5628,15 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="117">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF7C80"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="27">
     <dxf>
       <fill>
         <patternFill>
@@ -6328,6 +5732,13 @@
       <fill>
         <patternFill>
           <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7C80"/>
         </patternFill>
       </fill>
     </dxf>
@@ -6748,7 +6159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB8C860C-69C5-482A-A322-88D4F7BD0ED6}">
-  <dimension ref="A1:AA611"/>
+  <dimension ref="A1:AD611"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:27" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -6912,16 +6323,6 @@
       </c>
       <c r="Z2" s="15"/>
       <c r="AA2" s="16">
-        <f t="shared" ref="AA2:AA65" si="0">(
-IF(R2="ENVIADO A LA CE/UM",1/3,IF(R2="ENTREGADO/REVISIÓN",2/3,IF(R2="ENVIADO A TICS",1,0)))+
-IF(S2="EN PROCESO",0,IF(S2="CONCLUIDO",1,0))+
-IF(T2="ENVIADO A LA CE/UM",1/3,IF(T2="EN REVISIÓN CENTRAL",2/3,IF(T2="CONCLUIDO",1,0)))+
-IF(U2="ENVIADO A LA CE/UM",1/3,IF(U2="EN REVISIÓN CENTRAL",2/3,IF(U2="CONCLUIDO",1,0)))+
-IF(V2="ENVIADO",1/3,IF(V2="EN PROCESO",2/3,IF(V2="CONCLUIDO",1,0)))+
-IF(W2="PROGRAMADAS",0,IF(W2="CONCLUIDAS",1,0))+
-IF(X2="SI",1,IF(X2="NO",0,0))+
-IF(Y2="SI",1,IF(Y2="NO",0,0))
-)/8</f>
         <v>0.875</v>
       </c>
     </row>
@@ -7003,7 +6404,6 @@
       </c>
       <c r="Z3" s="15"/>
       <c r="AA3" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -7085,7 +6485,6 @@
       </c>
       <c r="Z4" s="15"/>
       <c r="AA4" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -7167,7 +6566,6 @@
       </c>
       <c r="Z5" s="15"/>
       <c r="AA5" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -7249,7 +6647,6 @@
       </c>
       <c r="Z6" s="15"/>
       <c r="AA6" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -7331,7 +6728,6 @@
       </c>
       <c r="Z7" s="15"/>
       <c r="AA7" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -7413,7 +6809,6 @@
       </c>
       <c r="Z8" s="15"/>
       <c r="AA8" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -7495,7 +6890,6 @@
       </c>
       <c r="Z9" s="15"/>
       <c r="AA9" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -7577,7 +6971,6 @@
       </c>
       <c r="Z10" s="15"/>
       <c r="AA10" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -7659,7 +7052,6 @@
       </c>
       <c r="Z11" s="15"/>
       <c r="AA11" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -7741,7 +7133,6 @@
       </c>
       <c r="Z12" s="15"/>
       <c r="AA12" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -7823,7 +7214,6 @@
       </c>
       <c r="Z13" s="15"/>
       <c r="AA13" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -7905,7 +7295,6 @@
       </c>
       <c r="Z14" s="15"/>
       <c r="AA14" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -7987,7 +7376,6 @@
       </c>
       <c r="Z15" s="15"/>
       <c r="AA15" s="16">
-        <f t="shared" si="0"/>
         <v>0.875</v>
       </c>
     </row>
@@ -8069,7 +7457,6 @@
       </c>
       <c r="Z16" s="15"/>
       <c r="AA16" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -8151,7 +7538,6 @@
       </c>
       <c r="Z17" s="15"/>
       <c r="AA17" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -8233,7 +7619,6 @@
       </c>
       <c r="Z18" s="15"/>
       <c r="AA18" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -8315,7 +7700,6 @@
       </c>
       <c r="Z19" s="15"/>
       <c r="AA19" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -8397,7 +7781,6 @@
       </c>
       <c r="Z20" s="15"/>
       <c r="AA20" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -8479,7 +7862,6 @@
       </c>
       <c r="Z21" s="15"/>
       <c r="AA21" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -8561,7 +7943,6 @@
       </c>
       <c r="Z22" s="15"/>
       <c r="AA22" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -8643,7 +8024,6 @@
       </c>
       <c r="Z23" s="15"/>
       <c r="AA23" s="16">
-        <f t="shared" si="0"/>
         <v>0.875</v>
       </c>
     </row>
@@ -8725,7 +8105,6 @@
       </c>
       <c r="Z24" s="15"/>
       <c r="AA24" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -8807,7 +8186,6 @@
       </c>
       <c r="Z25" s="15"/>
       <c r="AA25" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -8889,7 +8267,6 @@
       </c>
       <c r="Z26" s="15"/>
       <c r="AA26" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -8971,7 +8348,6 @@
       </c>
       <c r="Z27" s="15"/>
       <c r="AA27" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -9053,7 +8429,6 @@
       </c>
       <c r="Z28" s="15"/>
       <c r="AA28" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -9135,7 +8510,6 @@
       </c>
       <c r="Z29" s="15"/>
       <c r="AA29" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -9217,7 +8591,6 @@
       </c>
       <c r="Z30" s="15"/>
       <c r="AA30" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -9299,7 +8672,6 @@
       </c>
       <c r="Z31" s="15"/>
       <c r="AA31" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -9381,7 +8753,6 @@
       </c>
       <c r="Z32" s="15"/>
       <c r="AA32" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -9463,7 +8834,6 @@
       </c>
       <c r="Z33" s="15"/>
       <c r="AA33" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -9545,7 +8915,6 @@
       </c>
       <c r="Z34" s="15"/>
       <c r="AA34" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -9627,7 +8996,6 @@
       </c>
       <c r="Z35" s="15"/>
       <c r="AA35" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -9709,7 +9077,6 @@
       </c>
       <c r="Z36" s="15"/>
       <c r="AA36" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -9791,7 +9158,6 @@
       </c>
       <c r="Z37" s="15"/>
       <c r="AA37" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -9873,7 +9239,6 @@
       </c>
       <c r="Z38" s="15"/>
       <c r="AA38" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -9955,7 +9320,6 @@
       </c>
       <c r="Z39" s="15"/>
       <c r="AA39" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -10037,7 +9401,6 @@
       </c>
       <c r="Z40" s="15"/>
       <c r="AA40" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -10119,7 +9482,6 @@
       </c>
       <c r="Z41" s="15"/>
       <c r="AA41" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -10201,7 +9563,6 @@
       </c>
       <c r="Z42" s="15"/>
       <c r="AA42" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -10283,7 +9644,6 @@
       </c>
       <c r="Z43" s="15"/>
       <c r="AA43" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -10365,7 +9725,6 @@
       </c>
       <c r="Z44" s="15"/>
       <c r="AA44" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -10447,7 +9806,6 @@
       </c>
       <c r="Z45" s="15"/>
       <c r="AA45" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -10529,7 +9887,6 @@
       </c>
       <c r="Z46" s="15"/>
       <c r="AA46" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -10543,22 +9900,42 @@
       <c r="C47" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="D47" s="6"/>
+      <c r="D47" t="s">
+        <v>1609</v>
+      </c>
       <c r="E47" s="6" t="s">
         <v>1750</v>
       </c>
-      <c r="F47" s="6"/>
-      <c r="G47" s="7"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="6"/>
-      <c r="J47" s="6"/>
-      <c r="K47" s="6"/>
-      <c r="L47" s="6"/>
+      <c r="F47" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="G47" s="7">
+        <v>1</v>
+      </c>
+      <c r="H47" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J47" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K47" s="6" t="s">
+        <v>1756</v>
+      </c>
+      <c r="L47" s="6" t="s">
+        <v>33</v>
+      </c>
       <c r="M47" s="10"/>
       <c r="N47" s="11"/>
       <c r="O47" s="12"/>
-      <c r="P47" s="13"/>
-      <c r="Q47" s="13"/>
+      <c r="P47" s="13" t="s">
+        <v>1764</v>
+      </c>
+      <c r="Q47" s="13" t="s">
+        <v>1765</v>
+      </c>
       <c r="R47" s="14" t="s">
         <v>34</v>
       </c>
@@ -10585,7 +9962,6 @@
       </c>
       <c r="Z47" s="15"/>
       <c r="AA47" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -10606,9 +9982,15 @@
         <v>1749</v>
       </c>
       <c r="F48" s="6"/>
-      <c r="G48" s="7"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="6"/>
+      <c r="G48" s="7">
+        <v>1</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>31</v>
+      </c>
       <c r="J48" s="6" t="s">
         <v>32</v>
       </c>
@@ -10621,11 +10003,11 @@
       <c r="M48" s="10"/>
       <c r="N48" s="11"/>
       <c r="O48" s="12"/>
-      <c r="P48" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q48" s="14" t="s">
-        <v>175</v>
+      <c r="P48" s="13" t="s">
+        <v>1766</v>
+      </c>
+      <c r="Q48" s="13" t="s">
+        <v>1767</v>
       </c>
       <c r="R48" s="14" t="s">
         <v>34</v>
@@ -10653,7 +10035,6 @@
       </c>
       <c r="Z48" s="15"/>
       <c r="AA48" s="16">
-        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -10727,7 +10108,6 @@
       <c r="Y49" s="14"/>
       <c r="Z49" s="15"/>
       <c r="AA49" s="16">
-        <f t="shared" si="0"/>
         <v>0.20833333333333331</v>
       </c>
     </row>
@@ -10801,7 +10181,6 @@
       <c r="Y50" s="14"/>
       <c r="Z50" s="15"/>
       <c r="AA50" s="16">
-        <f t="shared" si="0"/>
         <v>0.20833333333333331</v>
       </c>
     </row>
@@ -10875,7 +10254,6 @@
       <c r="Y51" s="14"/>
       <c r="Z51" s="15"/>
       <c r="AA51" s="16">
-        <f t="shared" si="0"/>
         <v>0.20833333333333331</v>
       </c>
     </row>
@@ -10943,7 +10321,6 @@
       <c r="Y52" s="14"/>
       <c r="Z52" s="15"/>
       <c r="AA52" s="16">
-        <f t="shared" si="0"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -11011,7 +10388,6 @@
       <c r="Y53" s="14"/>
       <c r="Z53" s="15"/>
       <c r="AA53" s="16">
-        <f t="shared" si="0"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -11079,7 +10455,6 @@
       <c r="Y54" s="14"/>
       <c r="Z54" s="15"/>
       <c r="AA54" s="16">
-        <f t="shared" si="0"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -11147,7 +10522,6 @@
       <c r="Y55" s="14"/>
       <c r="Z55" s="15"/>
       <c r="AA55" s="16">
-        <f t="shared" si="0"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -11215,7 +10589,6 @@
       <c r="Y56" s="14"/>
       <c r="Z56" s="15"/>
       <c r="AA56" s="16">
-        <f t="shared" si="0"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -11283,7 +10656,6 @@
       <c r="Y57" s="14"/>
       <c r="Z57" s="15"/>
       <c r="AA57" s="16">
-        <f t="shared" si="0"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -11351,7 +10723,6 @@
       <c r="Y58" s="14"/>
       <c r="Z58" s="15"/>
       <c r="AA58" s="16">
-        <f t="shared" si="0"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -11425,7 +10796,6 @@
       <c r="Y59" s="14"/>
       <c r="Z59" s="15"/>
       <c r="AA59" s="16">
-        <f t="shared" si="0"/>
         <v>0.29166666666666663</v>
       </c>
     </row>
@@ -11499,7 +10869,6 @@
       <c r="Y60" s="14"/>
       <c r="Z60" s="15"/>
       <c r="AA60" s="16">
-        <f t="shared" si="0"/>
         <v>0.29166666666666663</v>
       </c>
     </row>
@@ -11567,7 +10936,6 @@
       <c r="Y61" s="14"/>
       <c r="Z61" s="15"/>
       <c r="AA61" s="16">
-        <f t="shared" si="0"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -11635,7 +11003,6 @@
       <c r="Y62" s="14"/>
       <c r="Z62" s="15"/>
       <c r="AA62" s="16">
-        <f t="shared" si="0"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -11709,7 +11076,6 @@
       </c>
       <c r="Z63" s="15"/>
       <c r="AA63" s="16">
-        <f t="shared" si="0"/>
         <v>0.16666666666666666</v>
       </c>
     </row>
@@ -11777,7 +11143,6 @@
       <c r="Y64" s="14"/>
       <c r="Z64" s="15"/>
       <c r="AA64" s="16">
-        <f t="shared" si="0"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -11845,7 +11210,6 @@
       <c r="Y65" s="14"/>
       <c r="Z65" s="15"/>
       <c r="AA65" s="16">
-        <f t="shared" si="0"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -11913,16 +11277,6 @@
       <c r="Y66" s="14"/>
       <c r="Z66" s="15"/>
       <c r="AA66" s="16">
-        <f t="shared" ref="AA66:AA129" si="1">(
-IF(R66="ENVIADO A LA CE/UM",1/3,IF(R66="ENTREGADO/REVISIÓN",2/3,IF(R66="ENVIADO A TICS",1,0)))+
-IF(S66="EN PROCESO",0,IF(S66="CONCLUIDO",1,0))+
-IF(T66="ENVIADO A LA CE/UM",1/3,IF(T66="EN REVISIÓN CENTRAL",2/3,IF(T66="CONCLUIDO",1,0)))+
-IF(U66="ENVIADO A LA CE/UM",1/3,IF(U66="EN REVISIÓN CENTRAL",2/3,IF(U66="CONCLUIDO",1,0)))+
-IF(V66="ENVIADO",1/3,IF(V66="EN PROCESO",2/3,IF(V66="CONCLUIDO",1,0)))+
-IF(W66="PROGRAMADAS",0,IF(W66="CONCLUIDAS",1,0))+
-IF(X66="SI",1,IF(X66="NO",0,0))+
-IF(Y66="SI",1,IF(Y66="NO",0,0))
-)/8</f>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -11990,7 +11344,6 @@
       <c r="Y67" s="14"/>
       <c r="Z67" s="15"/>
       <c r="AA67" s="16">
-        <f t="shared" si="1"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -12058,7 +11411,6 @@
       <c r="Y68" s="14"/>
       <c r="Z68" s="15"/>
       <c r="AA68" s="16">
-        <f t="shared" si="1"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -12126,7 +11478,6 @@
       <c r="Y69" s="14"/>
       <c r="Z69" s="15"/>
       <c r="AA69" s="16">
-        <f t="shared" si="1"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -12194,7 +11545,6 @@
       <c r="Y70" s="14"/>
       <c r="Z70" s="15"/>
       <c r="AA70" s="16">
-        <f t="shared" si="1"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -12262,7 +11612,6 @@
       <c r="Y71" s="14"/>
       <c r="Z71" s="15"/>
       <c r="AA71" s="16">
-        <f t="shared" si="1"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -12330,7 +11679,6 @@
       <c r="Y72" s="14"/>
       <c r="Z72" s="15"/>
       <c r="AA72" s="16">
-        <f t="shared" si="1"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -12398,7 +11746,6 @@
       <c r="Y73" s="14"/>
       <c r="Z73" s="15"/>
       <c r="AA73" s="16">
-        <f t="shared" si="1"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -12466,7 +11813,6 @@
       <c r="Y74" s="14"/>
       <c r="Z74" s="15"/>
       <c r="AA74" s="16">
-        <f t="shared" si="1"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -12534,7 +11880,6 @@
       <c r="Y75" s="14"/>
       <c r="Z75" s="15"/>
       <c r="AA75" s="16">
-        <f t="shared" si="1"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -12602,7 +11947,6 @@
       <c r="Y76" s="14"/>
       <c r="Z76" s="15"/>
       <c r="AA76" s="16">
-        <f t="shared" si="1"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -12670,7 +12014,6 @@
       <c r="Y77" s="14"/>
       <c r="Z77" s="15"/>
       <c r="AA77" s="16">
-        <f t="shared" si="1"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -12738,7 +12081,6 @@
       <c r="Y78" s="14"/>
       <c r="Z78" s="15"/>
       <c r="AA78" s="16">
-        <f t="shared" si="1"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -12806,7 +12148,6 @@
       <c r="Y79" s="14"/>
       <c r="Z79" s="15"/>
       <c r="AA79" s="16">
-        <f t="shared" si="1"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -12874,7 +12215,6 @@
       <c r="Y80" s="14"/>
       <c r="Z80" s="15"/>
       <c r="AA80" s="16">
-        <f t="shared" si="1"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -12942,7 +12282,6 @@
       <c r="Y81" s="14"/>
       <c r="Z81" s="15"/>
       <c r="AA81" s="16">
-        <f t="shared" si="1"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -13010,7 +12349,6 @@
       <c r="Y82" s="14"/>
       <c r="Z82" s="15"/>
       <c r="AA82" s="16">
-        <f t="shared" si="1"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -13078,7 +12416,6 @@
       <c r="Y83" s="14"/>
       <c r="Z83" s="15"/>
       <c r="AA83" s="16">
-        <f t="shared" si="1"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -13146,7 +12483,6 @@
       <c r="Y84" s="14"/>
       <c r="Z84" s="15"/>
       <c r="AA84" s="16">
-        <f t="shared" si="1"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -13214,7 +12550,6 @@
       <c r="Y85" s="14"/>
       <c r="Z85" s="15"/>
       <c r="AA85" s="16">
-        <f t="shared" si="1"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -13282,7 +12617,6 @@
       <c r="Y86" s="14"/>
       <c r="Z86" s="15"/>
       <c r="AA86" s="16">
-        <f t="shared" si="1"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -13350,7 +12684,6 @@
       <c r="Y87" s="14"/>
       <c r="Z87" s="15"/>
       <c r="AA87" s="16">
-        <f t="shared" si="1"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -13418,7 +12751,6 @@
       <c r="Y88" s="14"/>
       <c r="Z88" s="15"/>
       <c r="AA88" s="16">
-        <f t="shared" si="1"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -13500,7 +12832,6 @@
       </c>
       <c r="Z89" s="15"/>
       <c r="AA89" s="16">
-        <f t="shared" si="1"/>
         <v>0.875</v>
       </c>
     </row>
@@ -13582,7 +12913,6 @@
       </c>
       <c r="Z90" s="15"/>
       <c r="AA90" s="16">
-        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -13664,7 +12994,6 @@
       </c>
       <c r="Z91" s="15"/>
       <c r="AA91" s="16">
-        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -13746,7 +13075,6 @@
       </c>
       <c r="Z92" s="15"/>
       <c r="AA92" s="16">
-        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -13824,7 +13152,6 @@
       <c r="Y93" s="14"/>
       <c r="Z93" s="15"/>
       <c r="AA93" s="16">
-        <f t="shared" si="1"/>
         <v>0.70833333333333337</v>
       </c>
     </row>
@@ -13902,7 +13229,6 @@
       <c r="Y94" s="14"/>
       <c r="Z94" s="15"/>
       <c r="AA94" s="16">
-        <f t="shared" si="1"/>
         <v>0.70833333333333337</v>
       </c>
     </row>
@@ -13980,7 +13306,6 @@
       <c r="Y95" s="14"/>
       <c r="Z95" s="15"/>
       <c r="AA95" s="16">
-        <f t="shared" si="1"/>
         <v>0.70833333333333337</v>
       </c>
     </row>
@@ -14048,7 +13373,6 @@
       <c r="Y96" s="14"/>
       <c r="Z96" s="15"/>
       <c r="AA96" s="16">
-        <f t="shared" si="1"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -14116,7 +13440,6 @@
       <c r="Y97" s="14"/>
       <c r="Z97" s="15"/>
       <c r="AA97" s="16">
-        <f t="shared" si="1"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -14184,7 +13507,6 @@
       <c r="Y98" s="14"/>
       <c r="Z98" s="15"/>
       <c r="AA98" s="16">
-        <f t="shared" si="1"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -14252,7 +13574,6 @@
       <c r="Y99" s="14"/>
       <c r="Z99" s="15"/>
       <c r="AA99" s="16">
-        <f t="shared" si="1"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -14320,7 +13641,6 @@
       <c r="Y100" s="14"/>
       <c r="Z100" s="15"/>
       <c r="AA100" s="16">
-        <f t="shared" si="1"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -14388,7 +13708,6 @@
       <c r="Y101" s="14"/>
       <c r="Z101" s="15"/>
       <c r="AA101" s="16">
-        <f t="shared" si="1"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -14456,7 +13775,6 @@
       <c r="Y102" s="14"/>
       <c r="Z102" s="15"/>
       <c r="AA102" s="16">
-        <f t="shared" si="1"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -14524,7 +13842,6 @@
       <c r="Y103" s="14"/>
       <c r="Z103" s="15"/>
       <c r="AA103" s="16">
-        <f t="shared" si="1"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -14592,7 +13909,6 @@
       <c r="Y104" s="14"/>
       <c r="Z104" s="15"/>
       <c r="AA104" s="16">
-        <f t="shared" si="1"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -14660,7 +13976,6 @@
       <c r="Y105" s="14"/>
       <c r="Z105" s="15"/>
       <c r="AA105" s="16">
-        <f t="shared" si="1"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -14728,7 +14043,6 @@
       <c r="Y106" s="14"/>
       <c r="Z106" s="15"/>
       <c r="AA106" s="16">
-        <f t="shared" si="1"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -14796,7 +14110,6 @@
       <c r="Y107" s="14"/>
       <c r="Z107" s="15"/>
       <c r="AA107" s="16">
-        <f t="shared" si="1"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -14864,7 +14177,6 @@
       <c r="Y108" s="14"/>
       <c r="Z108" s="15"/>
       <c r="AA108" s="16">
-        <f t="shared" si="1"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -14932,7 +14244,6 @@
       <c r="Y109" s="14"/>
       <c r="Z109" s="15"/>
       <c r="AA109" s="16">
-        <f t="shared" si="1"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -15000,7 +14311,6 @@
       <c r="Y110" s="14"/>
       <c r="Z110" s="15"/>
       <c r="AA110" s="16">
-        <f t="shared" si="1"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -15068,7 +14378,6 @@
       <c r="Y111" s="14"/>
       <c r="Z111" s="15"/>
       <c r="AA111" s="16">
-        <f t="shared" si="1"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -15136,7 +14445,6 @@
       <c r="Y112" s="14"/>
       <c r="Z112" s="15"/>
       <c r="AA112" s="16">
-        <f t="shared" si="1"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -15204,7 +14512,6 @@
       <c r="Y113" s="14"/>
       <c r="Z113" s="15"/>
       <c r="AA113" s="16">
-        <f t="shared" si="1"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -15272,7 +14579,6 @@
       <c r="Y114" s="14"/>
       <c r="Z114" s="15"/>
       <c r="AA114" s="16">
-        <f t="shared" si="1"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -15340,7 +14646,6 @@
       <c r="Y115" s="14"/>
       <c r="Z115" s="15"/>
       <c r="AA115" s="16">
-        <f t="shared" si="1"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -15408,7 +14713,6 @@
       <c r="Y116" s="14"/>
       <c r="Z116" s="15"/>
       <c r="AA116" s="16">
-        <f t="shared" si="1"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -15476,7 +14780,6 @@
       <c r="Y117" s="14"/>
       <c r="Z117" s="15"/>
       <c r="AA117" s="16">
-        <f t="shared" si="1"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -15544,7 +14847,6 @@
       <c r="Y118" s="14"/>
       <c r="Z118" s="15"/>
       <c r="AA118" s="16">
-        <f t="shared" si="1"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -15612,7 +14914,6 @@
       <c r="Y119" s="14"/>
       <c r="Z119" s="15"/>
       <c r="AA119" s="16">
-        <f t="shared" si="1"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -15680,7 +14981,6 @@
       <c r="Y120" s="14"/>
       <c r="Z120" s="15"/>
       <c r="AA120" s="16">
-        <f t="shared" si="1"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -15748,7 +15048,6 @@
       <c r="Y121" s="14"/>
       <c r="Z121" s="15"/>
       <c r="AA121" s="16">
-        <f t="shared" si="1"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -15816,7 +15115,6 @@
       <c r="Y122" s="14"/>
       <c r="Z122" s="15"/>
       <c r="AA122" s="16">
-        <f t="shared" si="1"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -15884,7 +15182,6 @@
       <c r="Y123" s="14"/>
       <c r="Z123" s="15"/>
       <c r="AA123" s="16">
-        <f t="shared" si="1"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -15952,7 +15249,6 @@
       <c r="Y124" s="14"/>
       <c r="Z124" s="15"/>
       <c r="AA124" s="16">
-        <f t="shared" si="1"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -16020,7 +15316,6 @@
       <c r="Y125" s="14"/>
       <c r="Z125" s="15"/>
       <c r="AA125" s="16">
-        <f t="shared" si="1"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -16088,7 +15383,6 @@
       <c r="Y126" s="14"/>
       <c r="Z126" s="15"/>
       <c r="AA126" s="16">
-        <f t="shared" si="1"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -16156,7 +15450,6 @@
       <c r="Y127" s="14"/>
       <c r="Z127" s="15"/>
       <c r="AA127" s="16">
-        <f t="shared" si="1"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -16224,7 +15517,6 @@
       <c r="Y128" s="14"/>
       <c r="Z128" s="15"/>
       <c r="AA128" s="16">
-        <f t="shared" si="1"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -16292,7 +15584,6 @@
       <c r="Y129" s="14"/>
       <c r="Z129" s="15"/>
       <c r="AA129" s="16">
-        <f t="shared" si="1"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -16360,16 +15651,6 @@
       <c r="Y130" s="14"/>
       <c r="Z130" s="15"/>
       <c r="AA130" s="16">
-        <f t="shared" ref="AA130:AA165" si="2">(
-IF(R130="ENVIADO A LA CE/UM",1/3,IF(R130="ENTREGADO/REVISIÓN",2/3,IF(R130="ENVIADO A TICS",1,0)))+
-IF(S130="EN PROCESO",0,IF(S130="CONCLUIDO",1,0))+
-IF(T130="ENVIADO A LA CE/UM",1/3,IF(T130="EN REVISIÓN CENTRAL",2/3,IF(T130="CONCLUIDO",1,0)))+
-IF(U130="ENVIADO A LA CE/UM",1/3,IF(U130="EN REVISIÓN CENTRAL",2/3,IF(U130="CONCLUIDO",1,0)))+
-IF(V130="ENVIADO",1/3,IF(V130="EN PROCESO",2/3,IF(V130="CONCLUIDO",1,0)))+
-IF(W130="PROGRAMADAS",0,IF(W130="CONCLUIDAS",1,0))+
-IF(X130="SI",1,IF(X130="NO",0,0))+
-IF(Y130="SI",1,IF(Y130="NO",0,0))
-)/8</f>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -16437,7 +15718,6 @@
       <c r="Y131" s="14"/>
       <c r="Z131" s="15"/>
       <c r="AA131" s="16">
-        <f t="shared" si="2"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -16505,7 +15785,6 @@
       <c r="Y132" s="14"/>
       <c r="Z132" s="15"/>
       <c r="AA132" s="16">
-        <f t="shared" si="2"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -16573,7 +15852,6 @@
       <c r="Y133" s="14"/>
       <c r="Z133" s="15"/>
       <c r="AA133" s="16">
-        <f t="shared" si="2"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -16587,22 +15865,42 @@
       <c r="C134" s="6" t="s">
         <v>440</v>
       </c>
-      <c r="D134" s="6"/>
+      <c r="D134" s="6" t="s">
+        <v>1768</v>
+      </c>
       <c r="E134" s="6" t="s">
         <v>1751</v>
       </c>
-      <c r="F134" s="6"/>
-      <c r="G134" s="7"/>
-      <c r="H134" s="6"/>
-      <c r="I134" s="6"/>
-      <c r="J134" s="6"/>
-      <c r="K134" s="6"/>
-      <c r="L134" s="6"/>
+      <c r="F134" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G134" s="7">
+        <v>1</v>
+      </c>
+      <c r="H134" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="I134" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J134" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K134" s="6" t="s">
+        <v>1755</v>
+      </c>
+      <c r="L134" s="6" t="s">
+        <v>33</v>
+      </c>
       <c r="M134" s="10"/>
       <c r="N134" s="11"/>
       <c r="O134" s="12"/>
-      <c r="P134" s="13"/>
-      <c r="Q134" s="13"/>
+      <c r="P134" s="13" t="s">
+        <v>1769</v>
+      </c>
+      <c r="Q134" s="13" t="s">
+        <v>1770</v>
+      </c>
       <c r="R134" s="14" t="s">
         <v>34</v>
       </c>
@@ -16628,7 +15926,9 @@
         <v>74</v>
       </c>
       <c r="Z134" s="15"/>
-      <c r="AA134" s="16"/>
+      <c r="AA134" s="16">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="135" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A135" s="6" t="s">
@@ -16694,16 +15994,6 @@
       <c r="Y135" s="14"/>
       <c r="Z135" s="15"/>
       <c r="AA135" s="16">
-        <f t="shared" ref="AA135:AA198" si="3">(
-IF(R135="ENVIADO A LA CE/UM",1/3,IF(R135="ENTREGADO/REVISIÓN",2/3,IF(R135="ENVIADO A TICS",1,0)))+
-IF(S135="EN PROCESO",0,IF(S135="CONCLUIDO",1,0))+
-IF(T135="ENVIADO A LA CE/UM",1/3,IF(T135="EN REVISIÓN CENTRAL",2/3,IF(T135="CONCLUIDO",1,0)))+
-IF(U135="ENVIADO A LA CE/UM",1/3,IF(U135="EN REVISIÓN CENTRAL",2/3,IF(U135="CONCLUIDO",1,0)))+
-IF(V135="ENVIADO",1/3,IF(V135="EN PROCESO",2/3,IF(V135="CONCLUIDO",1,0)))+
-IF(W135="PROGRAMADAS",0,IF(W135="CONCLUIDAS",1,0))+
-IF(X135="SI",1,IF(X135="NO",0,0))+
-IF(Y135="SI",1,IF(Y135="NO",0,0))
-)/8</f>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -16771,7 +16061,6 @@
       <c r="Y136" s="14"/>
       <c r="Z136" s="15"/>
       <c r="AA136" s="16">
-        <f t="shared" si="3"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -16839,7 +16128,6 @@
       <c r="Y137" s="14"/>
       <c r="Z137" s="15"/>
       <c r="AA137" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -16907,7 +16195,6 @@
       <c r="Y138" s="14"/>
       <c r="Z138" s="15"/>
       <c r="AA138" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -16975,7 +16262,6 @@
       <c r="Y139" s="14"/>
       <c r="Z139" s="15"/>
       <c r="AA139" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -17043,7 +16329,6 @@
       <c r="Y140" s="14"/>
       <c r="Z140" s="15"/>
       <c r="AA140" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -17111,7 +16396,6 @@
       <c r="Y141" s="14"/>
       <c r="Z141" s="15"/>
       <c r="AA141" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -17179,7 +16463,6 @@
       <c r="Y142" s="14"/>
       <c r="Z142" s="15"/>
       <c r="AA142" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -17247,7 +16530,6 @@
       <c r="Y143" s="14"/>
       <c r="Z143" s="15"/>
       <c r="AA143" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -17315,7 +16597,6 @@
       <c r="Y144" s="14"/>
       <c r="Z144" s="15"/>
       <c r="AA144" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -17383,7 +16664,6 @@
       <c r="Y145" s="14"/>
       <c r="Z145" s="15"/>
       <c r="AA145" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -17451,7 +16731,6 @@
       <c r="Y146" s="14"/>
       <c r="Z146" s="15"/>
       <c r="AA146" s="16">
-        <f t="shared" si="3"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -17519,7 +16798,6 @@
       <c r="Y147" s="14"/>
       <c r="Z147" s="15"/>
       <c r="AA147" s="16">
-        <f t="shared" si="3"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -17587,7 +16865,6 @@
       <c r="Y148" s="14"/>
       <c r="Z148" s="15"/>
       <c r="AA148" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -17655,7 +16932,6 @@
       <c r="Y149" s="14"/>
       <c r="Z149" s="15"/>
       <c r="AA149" s="16">
-        <f t="shared" si="3"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -17723,7 +16999,6 @@
       <c r="Y150" s="14"/>
       <c r="Z150" s="15"/>
       <c r="AA150" s="16">
-        <f t="shared" si="3"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -17791,7 +17066,6 @@
       <c r="Y151" s="14"/>
       <c r="Z151" s="15"/>
       <c r="AA151" s="16">
-        <f t="shared" si="3"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -17859,7 +17133,6 @@
       <c r="Y152" s="14"/>
       <c r="Z152" s="15"/>
       <c r="AA152" s="16">
-        <f t="shared" si="3"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -17927,7 +17200,6 @@
       <c r="Y153" s="14"/>
       <c r="Z153" s="15"/>
       <c r="AA153" s="16">
-        <f t="shared" si="3"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -17995,7 +17267,6 @@
       <c r="Y154" s="14"/>
       <c r="Z154" s="15"/>
       <c r="AA154" s="16">
-        <f t="shared" si="3"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -18063,7 +17334,6 @@
       <c r="Y155" s="14"/>
       <c r="Z155" s="15"/>
       <c r="AA155" s="16">
-        <f t="shared" si="3"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -18131,7 +17401,6 @@
       <c r="Y156" s="14"/>
       <c r="Z156" s="15"/>
       <c r="AA156" s="16">
-        <f t="shared" si="3"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -18199,7 +17468,6 @@
       <c r="Y157" s="14"/>
       <c r="Z157" s="15"/>
       <c r="AA157" s="16">
-        <f t="shared" si="3"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -18267,7 +17535,6 @@
       <c r="Y158" s="14"/>
       <c r="Z158" s="15"/>
       <c r="AA158" s="16">
-        <f t="shared" si="3"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -18335,7 +17602,6 @@
       <c r="Y159" s="14"/>
       <c r="Z159" s="15"/>
       <c r="AA159" s="16">
-        <f t="shared" si="3"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -18403,7 +17669,6 @@
       <c r="Y160" s="14"/>
       <c r="Z160" s="15"/>
       <c r="AA160" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -18471,7 +17736,6 @@
       <c r="Y161" s="14"/>
       <c r="Z161" s="15"/>
       <c r="AA161" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -18539,7 +17803,6 @@
       <c r="Y162" s="14"/>
       <c r="Z162" s="15"/>
       <c r="AA162" s="16">
-        <f t="shared" si="3"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -18607,7 +17870,6 @@
       <c r="Y163" s="14"/>
       <c r="Z163" s="15"/>
       <c r="AA163" s="16">
-        <f t="shared" si="3"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -18675,7 +17937,6 @@
       <c r="Y164" s="14"/>
       <c r="Z164" s="15"/>
       <c r="AA164" s="16">
-        <f t="shared" si="3"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -18743,7 +18004,6 @@
       <c r="Y165" s="14"/>
       <c r="Z165" s="15"/>
       <c r="AA165" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -18811,7 +18071,6 @@
       <c r="Y166" s="14"/>
       <c r="Z166" s="15"/>
       <c r="AA166" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -18879,7 +18138,6 @@
       <c r="Y167" s="14"/>
       <c r="Z167" s="15"/>
       <c r="AA167" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -18947,7 +18205,6 @@
       <c r="Y168" s="14"/>
       <c r="Z168" s="15"/>
       <c r="AA168" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -19015,7 +18272,6 @@
       <c r="Y169" s="14"/>
       <c r="Z169" s="15"/>
       <c r="AA169" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -19083,7 +18339,6 @@
       <c r="Y170" s="14"/>
       <c r="Z170" s="15"/>
       <c r="AA170" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -19151,7 +18406,6 @@
       <c r="Y171" s="14"/>
       <c r="Z171" s="15"/>
       <c r="AA171" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -19219,7 +18473,6 @@
       <c r="Y172" s="14"/>
       <c r="Z172" s="15"/>
       <c r="AA172" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -19287,7 +18540,6 @@
       <c r="Y173" s="14"/>
       <c r="Z173" s="15"/>
       <c r="AA173" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -19355,7 +18607,6 @@
       <c r="Y174" s="14"/>
       <c r="Z174" s="15"/>
       <c r="AA174" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -19423,7 +18674,6 @@
       <c r="Y175" s="14"/>
       <c r="Z175" s="15"/>
       <c r="AA175" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -19491,7 +18741,6 @@
       <c r="Y176" s="14"/>
       <c r="Z176" s="15"/>
       <c r="AA176" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -19559,7 +18808,6 @@
       <c r="Y177" s="14"/>
       <c r="Z177" s="15"/>
       <c r="AA177" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -19627,7 +18875,6 @@
       <c r="Y178" s="14"/>
       <c r="Z178" s="15"/>
       <c r="AA178" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -19695,7 +18942,6 @@
       <c r="Y179" s="14"/>
       <c r="Z179" s="15"/>
       <c r="AA179" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -19763,7 +19009,6 @@
       <c r="Y180" s="14"/>
       <c r="Z180" s="15"/>
       <c r="AA180" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -19831,7 +19076,6 @@
       <c r="Y181" s="14"/>
       <c r="Z181" s="15"/>
       <c r="AA181" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -19899,7 +19143,6 @@
       <c r="Y182" s="14"/>
       <c r="Z182" s="15"/>
       <c r="AA182" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -19967,7 +19210,6 @@
       <c r="Y183" s="14"/>
       <c r="Z183" s="15"/>
       <c r="AA183" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -20035,7 +19277,6 @@
       <c r="Y184" s="14"/>
       <c r="Z184" s="15"/>
       <c r="AA184" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -20103,7 +19344,6 @@
       <c r="Y185" s="14"/>
       <c r="Z185" s="15"/>
       <c r="AA185" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -20171,7 +19411,6 @@
       <c r="Y186" s="14"/>
       <c r="Z186" s="15"/>
       <c r="AA186" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -20239,7 +19478,6 @@
       <c r="Y187" s="14"/>
       <c r="Z187" s="15"/>
       <c r="AA187" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -20307,7 +19545,6 @@
       <c r="Y188" s="14"/>
       <c r="Z188" s="15"/>
       <c r="AA188" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -20375,7 +19612,6 @@
       <c r="Y189" s="14"/>
       <c r="Z189" s="15"/>
       <c r="AA189" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -20443,7 +19679,6 @@
       <c r="Y190" s="14"/>
       <c r="Z190" s="15"/>
       <c r="AA190" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -20511,7 +19746,6 @@
       <c r="Y191" s="14"/>
       <c r="Z191" s="15"/>
       <c r="AA191" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -20579,7 +19813,6 @@
       <c r="Y192" s="14"/>
       <c r="Z192" s="15"/>
       <c r="AA192" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -20647,7 +19880,6 @@
       <c r="Y193" s="14"/>
       <c r="Z193" s="15"/>
       <c r="AA193" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -20715,7 +19947,6 @@
       <c r="Y194" s="14"/>
       <c r="Z194" s="15"/>
       <c r="AA194" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -20783,7 +20014,6 @@
       <c r="Y195" s="14"/>
       <c r="Z195" s="15"/>
       <c r="AA195" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -20851,7 +20081,6 @@
       <c r="Y196" s="14"/>
       <c r="Z196" s="15"/>
       <c r="AA196" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -20919,7 +20148,6 @@
       <c r="Y197" s="14"/>
       <c r="Z197" s="15"/>
       <c r="AA197" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -20987,7 +20215,6 @@
       <c r="Y198" s="14"/>
       <c r="Z198" s="15"/>
       <c r="AA198" s="16">
-        <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -21055,16 +20282,6 @@
       <c r="Y199" s="14"/>
       <c r="Z199" s="15"/>
       <c r="AA199" s="16">
-        <f t="shared" ref="AA199:AA262" si="4">(
-IF(R199="ENVIADO A LA CE/UM",1/3,IF(R199="ENTREGADO/REVISIÓN",2/3,IF(R199="ENVIADO A TICS",1,0)))+
-IF(S199="EN PROCESO",0,IF(S199="CONCLUIDO",1,0))+
-IF(T199="ENVIADO A LA CE/UM",1/3,IF(T199="EN REVISIÓN CENTRAL",2/3,IF(T199="CONCLUIDO",1,0)))+
-IF(U199="ENVIADO A LA CE/UM",1/3,IF(U199="EN REVISIÓN CENTRAL",2/3,IF(U199="CONCLUIDO",1,0)))+
-IF(V199="ENVIADO",1/3,IF(V199="EN PROCESO",2/3,IF(V199="CONCLUIDO",1,0)))+
-IF(W199="PROGRAMADAS",0,IF(W199="CONCLUIDAS",1,0))+
-IF(X199="SI",1,IF(X199="NO",0,0))+
-IF(Y199="SI",1,IF(Y199="NO",0,0))
-)/8</f>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -21132,7 +20349,6 @@
       <c r="Y200" s="14"/>
       <c r="Z200" s="15"/>
       <c r="AA200" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -21200,7 +20416,6 @@
       <c r="Y201" s="14"/>
       <c r="Z201" s="15"/>
       <c r="AA201" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -21268,7 +20483,6 @@
       <c r="Y202" s="14"/>
       <c r="Z202" s="15"/>
       <c r="AA202" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -21336,7 +20550,6 @@
       <c r="Y203" s="14"/>
       <c r="Z203" s="15"/>
       <c r="AA203" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -21404,7 +20617,6 @@
       <c r="Y204" s="14"/>
       <c r="Z204" s="15"/>
       <c r="AA204" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -21472,7 +20684,6 @@
       <c r="Y205" s="14"/>
       <c r="Z205" s="15"/>
       <c r="AA205" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -21540,7 +20751,6 @@
       <c r="Y206" s="14"/>
       <c r="Z206" s="15"/>
       <c r="AA206" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -21608,7 +20818,6 @@
       <c r="Y207" s="14"/>
       <c r="Z207" s="15"/>
       <c r="AA207" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -21676,7 +20885,6 @@
       <c r="Y208" s="14"/>
       <c r="Z208" s="15"/>
       <c r="AA208" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -21744,7 +20952,6 @@
       <c r="Y209" s="14"/>
       <c r="Z209" s="15"/>
       <c r="AA209" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -21812,7 +21019,6 @@
       <c r="Y210" s="14"/>
       <c r="Z210" s="15"/>
       <c r="AA210" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -21880,7 +21086,6 @@
       <c r="Y211" s="14"/>
       <c r="Z211" s="15"/>
       <c r="AA211" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -21948,7 +21153,6 @@
       <c r="Y212" s="14"/>
       <c r="Z212" s="15"/>
       <c r="AA212" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -22016,7 +21220,6 @@
       <c r="Y213" s="14"/>
       <c r="Z213" s="15"/>
       <c r="AA213" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -22084,7 +21287,6 @@
       <c r="Y214" s="14"/>
       <c r="Z214" s="15"/>
       <c r="AA214" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -22152,7 +21354,6 @@
       <c r="Y215" s="14"/>
       <c r="Z215" s="15"/>
       <c r="AA215" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -22220,7 +21421,6 @@
       <c r="Y216" s="14"/>
       <c r="Z216" s="15"/>
       <c r="AA216" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -22288,7 +21488,6 @@
       <c r="Y217" s="14"/>
       <c r="Z217" s="15"/>
       <c r="AA217" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -22356,7 +21555,6 @@
       <c r="Y218" s="14"/>
       <c r="Z218" s="15"/>
       <c r="AA218" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -22424,7 +21622,6 @@
       <c r="Y219" s="14"/>
       <c r="Z219" s="15"/>
       <c r="AA219" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -22492,7 +21689,6 @@
       <c r="Y220" s="14"/>
       <c r="Z220" s="15"/>
       <c r="AA220" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -22560,7 +21756,6 @@
       <c r="Y221" s="14"/>
       <c r="Z221" s="15"/>
       <c r="AA221" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -22634,7 +21829,6 @@
       <c r="Y222" s="14"/>
       <c r="Z222" s="15"/>
       <c r="AA222" s="16">
-        <f t="shared" si="4"/>
         <v>0.29166666666666663</v>
       </c>
     </row>
@@ -22708,7 +21902,6 @@
       <c r="Y223" s="14"/>
       <c r="Z223" s="15"/>
       <c r="AA223" s="16">
-        <f t="shared" si="4"/>
         <v>0.29166666666666663</v>
       </c>
     </row>
@@ -22782,7 +21975,6 @@
       <c r="Y224" s="14"/>
       <c r="Z224" s="15"/>
       <c r="AA224" s="16">
-        <f t="shared" si="4"/>
         <v>0.29166666666666663</v>
       </c>
     </row>
@@ -22856,7 +22048,6 @@
       <c r="Y225" s="14"/>
       <c r="Z225" s="15"/>
       <c r="AA225" s="16">
-        <f t="shared" si="4"/>
         <v>0.29166666666666663</v>
       </c>
     </row>
@@ -22930,7 +22121,6 @@
       <c r="Y226" s="14"/>
       <c r="Z226" s="15"/>
       <c r="AA226" s="16">
-        <f t="shared" si="4"/>
         <v>0.29166666666666663</v>
       </c>
     </row>
@@ -23004,7 +22194,6 @@
       <c r="Y227" s="14"/>
       <c r="Z227" s="15"/>
       <c r="AA227" s="16">
-        <f t="shared" si="4"/>
         <v>0.29166666666666663</v>
       </c>
     </row>
@@ -23070,7 +22259,6 @@
       <c r="Y228" s="14"/>
       <c r="Z228" s="15"/>
       <c r="AA228" s="16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -23136,7 +22324,6 @@
       <c r="Y229" s="14"/>
       <c r="Z229" s="15"/>
       <c r="AA229" s="16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -23202,7 +22389,6 @@
       <c r="Y230" s="14"/>
       <c r="Z230" s="15"/>
       <c r="AA230" s="16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -23268,7 +22454,6 @@
       <c r="Y231" s="14"/>
       <c r="Z231" s="15"/>
       <c r="AA231" s="16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -23334,7 +22519,6 @@
       <c r="Y232" s="14"/>
       <c r="Z232" s="15"/>
       <c r="AA232" s="16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -23400,7 +22584,6 @@
       <c r="Y233" s="14"/>
       <c r="Z233" s="15"/>
       <c r="AA233" s="16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -23466,7 +22649,6 @@
       <c r="Y234" s="14"/>
       <c r="Z234" s="15"/>
       <c r="AA234" s="16">
-        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -23534,7 +22716,6 @@
       <c r="Y235" s="14"/>
       <c r="Z235" s="15"/>
       <c r="AA235" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -23602,7 +22783,6 @@
       <c r="Y236" s="14"/>
       <c r="Z236" s="15"/>
       <c r="AA236" s="16">
-        <f t="shared" si="4"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -23670,7 +22850,6 @@
       <c r="Y237" s="14"/>
       <c r="Z237" s="15"/>
       <c r="AA237" s="16">
-        <f t="shared" si="4"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -23738,7 +22917,6 @@
       <c r="Y238" s="14"/>
       <c r="Z238" s="15"/>
       <c r="AA238" s="16">
-        <f t="shared" si="4"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -23806,7 +22984,6 @@
       <c r="Y239" s="14"/>
       <c r="Z239" s="15"/>
       <c r="AA239" s="16">
-        <f t="shared" si="4"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -23874,7 +23051,6 @@
       <c r="Y240" s="14"/>
       <c r="Z240" s="15"/>
       <c r="AA240" s="16">
-        <f t="shared" si="4"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -23942,7 +23118,6 @@
       <c r="Y241" s="14"/>
       <c r="Z241" s="15"/>
       <c r="AA241" s="16">
-        <f t="shared" si="4"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -24010,7 +23185,6 @@
       <c r="Y242" s="14"/>
       <c r="Z242" s="15"/>
       <c r="AA242" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -24078,7 +23252,6 @@
       <c r="Y243" s="14"/>
       <c r="Z243" s="15"/>
       <c r="AA243" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -24146,7 +23319,6 @@
       <c r="Y244" s="14"/>
       <c r="Z244" s="15"/>
       <c r="AA244" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -24214,7 +23386,6 @@
       <c r="Y245" s="14"/>
       <c r="Z245" s="15"/>
       <c r="AA245" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -24282,7 +23453,6 @@
       <c r="Y246" s="14"/>
       <c r="Z246" s="15"/>
       <c r="AA246" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -24350,7 +23520,6 @@
       <c r="Y247" s="14"/>
       <c r="Z247" s="15"/>
       <c r="AA247" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -24418,7 +23587,6 @@
       <c r="Y248" s="14"/>
       <c r="Z248" s="15"/>
       <c r="AA248" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -24486,7 +23654,6 @@
       <c r="Y249" s="14"/>
       <c r="Z249" s="15"/>
       <c r="AA249" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -24554,7 +23721,6 @@
       <c r="Y250" s="14"/>
       <c r="Z250" s="15"/>
       <c r="AA250" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -24622,7 +23788,6 @@
       <c r="Y251" s="14"/>
       <c r="Z251" s="15"/>
       <c r="AA251" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -24690,7 +23855,6 @@
       <c r="Y252" s="14"/>
       <c r="Z252" s="15"/>
       <c r="AA252" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -24758,7 +23922,6 @@
       <c r="Y253" s="14"/>
       <c r="Z253" s="15"/>
       <c r="AA253" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -24826,7 +23989,6 @@
       <c r="Y254" s="14"/>
       <c r="Z254" s="15"/>
       <c r="AA254" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -24894,7 +24056,6 @@
       <c r="Y255" s="14"/>
       <c r="Z255" s="15"/>
       <c r="AA255" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -24962,7 +24123,6 @@
       <c r="Y256" s="14"/>
       <c r="Z256" s="15"/>
       <c r="AA256" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -25030,7 +24190,6 @@
       <c r="Y257" s="14"/>
       <c r="Z257" s="15"/>
       <c r="AA257" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -25098,7 +24257,6 @@
       <c r="Y258" s="14"/>
       <c r="Z258" s="15"/>
       <c r="AA258" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -25166,7 +24324,6 @@
       <c r="Y259" s="14"/>
       <c r="Z259" s="15"/>
       <c r="AA259" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -25234,7 +24391,6 @@
       <c r="Y260" s="14"/>
       <c r="Z260" s="15"/>
       <c r="AA260" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -25302,7 +24458,6 @@
       <c r="Y261" s="14"/>
       <c r="Z261" s="15"/>
       <c r="AA261" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -25370,7 +24525,6 @@
       <c r="Y262" s="14"/>
       <c r="Z262" s="15"/>
       <c r="AA262" s="16">
-        <f t="shared" si="4"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -25438,16 +24592,6 @@
       <c r="Y263" s="14"/>
       <c r="Z263" s="15"/>
       <c r="AA263" s="16">
-        <f t="shared" ref="AA263:AA326" si="5">(
-IF(R263="ENVIADO A LA CE/UM",1/3,IF(R263="ENTREGADO/REVISIÓN",2/3,IF(R263="ENVIADO A TICS",1,0)))+
-IF(S263="EN PROCESO",0,IF(S263="CONCLUIDO",1,0))+
-IF(T263="ENVIADO A LA CE/UM",1/3,IF(T263="EN REVISIÓN CENTRAL",2/3,IF(T263="CONCLUIDO",1,0)))+
-IF(U263="ENVIADO A LA CE/UM",1/3,IF(U263="EN REVISIÓN CENTRAL",2/3,IF(U263="CONCLUIDO",1,0)))+
-IF(V263="ENVIADO",1/3,IF(V263="EN PROCESO",2/3,IF(V263="CONCLUIDO",1,0)))+
-IF(W263="PROGRAMADAS",0,IF(W263="CONCLUIDAS",1,0))+
-IF(X263="SI",1,IF(X263="NO",0,0))+
-IF(Y263="SI",1,IF(Y263="NO",0,0))
-)/8</f>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -25515,7 +24659,6 @@
       <c r="Y264" s="14"/>
       <c r="Z264" s="15"/>
       <c r="AA264" s="16">
-        <f t="shared" si="5"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -25583,7 +24726,6 @@
       <c r="Y265" s="14"/>
       <c r="Z265" s="15"/>
       <c r="AA265" s="16">
-        <f t="shared" si="5"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -25651,7 +24793,6 @@
       <c r="Y266" s="14"/>
       <c r="Z266" s="15"/>
       <c r="AA266" s="16">
-        <f t="shared" si="5"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -25719,7 +24860,6 @@
       <c r="Y267" s="14"/>
       <c r="Z267" s="15"/>
       <c r="AA267" s="16">
-        <f t="shared" si="5"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -25787,7 +24927,6 @@
       <c r="Y268" s="14"/>
       <c r="Z268" s="15"/>
       <c r="AA268" s="16">
-        <f t="shared" si="5"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -25855,7 +24994,6 @@
       <c r="Y269" s="14"/>
       <c r="Z269" s="15"/>
       <c r="AA269" s="16">
-        <f t="shared" si="5"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -25923,7 +25061,6 @@
       <c r="Y270" s="14"/>
       <c r="Z270" s="15"/>
       <c r="AA270" s="16">
-        <f t="shared" si="5"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -25991,7 +25128,6 @@
       <c r="Y271" s="14"/>
       <c r="Z271" s="15"/>
       <c r="AA271" s="16">
-        <f t="shared" si="5"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -26059,7 +25195,6 @@
       <c r="Y272" s="14"/>
       <c r="Z272" s="15"/>
       <c r="AA272" s="16">
-        <f t="shared" si="5"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -26127,7 +25262,6 @@
       <c r="Y273" s="14"/>
       <c r="Z273" s="15"/>
       <c r="AA273" s="16">
-        <f t="shared" si="5"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -26195,7 +25329,6 @@
       <c r="Y274" s="14"/>
       <c r="Z274" s="15"/>
       <c r="AA274" s="16">
-        <f t="shared" si="5"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -26263,7 +25396,6 @@
       <c r="Y275" s="14"/>
       <c r="Z275" s="15"/>
       <c r="AA275" s="16">
-        <f t="shared" si="5"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -26337,7 +25469,6 @@
       <c r="Y276" s="14"/>
       <c r="Z276" s="15"/>
       <c r="AA276" s="16">
-        <f t="shared" si="5"/>
         <v>0.20833333333333331</v>
       </c>
     </row>
@@ -26411,7 +25542,6 @@
       <c r="Y277" s="14"/>
       <c r="Z277" s="15"/>
       <c r="AA277" s="16">
-        <f t="shared" si="5"/>
         <v>0.20833333333333331</v>
       </c>
     </row>
@@ -26485,7 +25615,6 @@
       <c r="Y278" s="14"/>
       <c r="Z278" s="15"/>
       <c r="AA278" s="16">
-        <f t="shared" si="5"/>
         <v>0.20833333333333331</v>
       </c>
     </row>
@@ -26559,7 +25688,6 @@
       <c r="Y279" s="14"/>
       <c r="Z279" s="15"/>
       <c r="AA279" s="16">
-        <f t="shared" si="5"/>
         <v>0.20833333333333331</v>
       </c>
     </row>
@@ -26633,7 +25761,6 @@
       <c r="Y280" s="14"/>
       <c r="Z280" s="15"/>
       <c r="AA280" s="16">
-        <f t="shared" si="5"/>
         <v>0.20833333333333331</v>
       </c>
     </row>
@@ -26707,7 +25834,6 @@
       <c r="Y281" s="14"/>
       <c r="Z281" s="15"/>
       <c r="AA281" s="16">
-        <f t="shared" si="5"/>
         <v>0.20833333333333331</v>
       </c>
     </row>
@@ -26781,7 +25907,6 @@
       <c r="Y282" s="14"/>
       <c r="Z282" s="15"/>
       <c r="AA282" s="16">
-        <f t="shared" si="5"/>
         <v>0.20833333333333331</v>
       </c>
     </row>
@@ -26855,7 +25980,6 @@
       <c r="Y283" s="14"/>
       <c r="Z283" s="15"/>
       <c r="AA283" s="16">
-        <f t="shared" si="5"/>
         <v>0.29166666666666663</v>
       </c>
     </row>
@@ -26929,7 +26053,6 @@
       <c r="Y284" s="14"/>
       <c r="Z284" s="15"/>
       <c r="AA284" s="16">
-        <f t="shared" si="5"/>
         <v>0.29166666666666663</v>
       </c>
     </row>
@@ -27003,7 +26126,6 @@
       <c r="Y285" s="14"/>
       <c r="Z285" s="15"/>
       <c r="AA285" s="16">
-        <f t="shared" si="5"/>
         <v>0.20833333333333331</v>
       </c>
     </row>
@@ -27077,7 +26199,6 @@
       <c r="Y286" s="14"/>
       <c r="Z286" s="15"/>
       <c r="AA286" s="16">
-        <f t="shared" si="5"/>
         <v>0.20833333333333331</v>
       </c>
     </row>
@@ -27145,7 +26266,6 @@
       <c r="Y287" s="14"/>
       <c r="Z287" s="15"/>
       <c r="AA287" s="16">
-        <f t="shared" si="5"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -27213,7 +26333,6 @@
       <c r="Y288" s="14"/>
       <c r="Z288" s="15"/>
       <c r="AA288" s="16">
-        <f t="shared" si="5"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -27281,7 +26400,6 @@
       <c r="Y289" s="14"/>
       <c r="Z289" s="15"/>
       <c r="AA289" s="16">
-        <f t="shared" si="5"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -27349,7 +26467,6 @@
       <c r="Y290" s="14"/>
       <c r="Z290" s="15"/>
       <c r="AA290" s="16">
-        <f t="shared" si="5"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -27423,7 +26540,6 @@
       </c>
       <c r="Z291" s="15"/>
       <c r="AA291" s="16">
-        <f t="shared" si="5"/>
         <v>0.16666666666666666</v>
       </c>
     </row>
@@ -27497,7 +26613,6 @@
       </c>
       <c r="Z292" s="15"/>
       <c r="AA292" s="16">
-        <f t="shared" si="5"/>
         <v>0.16666666666666666</v>
       </c>
     </row>
@@ -27571,7 +26686,6 @@
       </c>
       <c r="Z293" s="15"/>
       <c r="AA293" s="16">
-        <f t="shared" si="5"/>
         <v>0.16666666666666666</v>
       </c>
     </row>
@@ -27645,7 +26759,6 @@
       </c>
       <c r="Z294" s="15"/>
       <c r="AA294" s="16">
-        <f t="shared" si="5"/>
         <v>0.16666666666666666</v>
       </c>
     </row>
@@ -27719,7 +26832,6 @@
       </c>
       <c r="Z295" s="15"/>
       <c r="AA295" s="16">
-        <f t="shared" si="5"/>
         <v>0.16666666666666666</v>
       </c>
     </row>
@@ -27793,7 +26905,6 @@
       </c>
       <c r="Z296" s="15"/>
       <c r="AA296" s="16">
-        <f t="shared" si="5"/>
         <v>0.16666666666666666</v>
       </c>
     </row>
@@ -27867,7 +26978,6 @@
       </c>
       <c r="Z297" s="15"/>
       <c r="AA297" s="16">
-        <f t="shared" si="5"/>
         <v>0.16666666666666666</v>
       </c>
     </row>
@@ -27941,7 +27051,6 @@
       </c>
       <c r="Z298" s="15"/>
       <c r="AA298" s="16">
-        <f t="shared" si="5"/>
         <v>0.16666666666666666</v>
       </c>
     </row>
@@ -28011,7 +27120,6 @@
       </c>
       <c r="Z299" s="15"/>
       <c r="AA299" s="16">
-        <f t="shared" si="5"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -28085,7 +27193,6 @@
       <c r="Y300" s="14"/>
       <c r="Z300" s="15"/>
       <c r="AA300" s="16">
-        <f t="shared" si="5"/>
         <v>0.29166666666666663</v>
       </c>
     </row>
@@ -28167,7 +27274,6 @@
         <v>1754</v>
       </c>
       <c r="AA301" s="16">
-        <f t="shared" si="5"/>
         <v>0.79166666666666663</v>
       </c>
     </row>
@@ -28237,7 +27343,6 @@
       <c r="Y302" s="14"/>
       <c r="Z302" s="15"/>
       <c r="AA302" s="16">
-        <f t="shared" si="5"/>
         <v>0.16666666666666666</v>
       </c>
     </row>
@@ -28305,7 +27410,6 @@
       <c r="Y303" s="14"/>
       <c r="Z303" s="15"/>
       <c r="AA303" s="16">
-        <f t="shared" si="5"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -28373,7 +27477,6 @@
       <c r="Y304" s="14"/>
       <c r="Z304" s="15"/>
       <c r="AA304" s="16">
-        <f t="shared" si="5"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -28441,7 +27544,6 @@
       <c r="Y305" s="14"/>
       <c r="Z305" s="15"/>
       <c r="AA305" s="16">
-        <f t="shared" si="5"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -28509,7 +27611,6 @@
       <c r="Y306" s="14"/>
       <c r="Z306" s="15"/>
       <c r="AA306" s="16">
-        <f t="shared" si="5"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -28577,7 +27678,6 @@
       <c r="Y307" s="14"/>
       <c r="Z307" s="15"/>
       <c r="AA307" s="16">
-        <f t="shared" si="5"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -28645,7 +27745,6 @@
       <c r="Y308" s="14"/>
       <c r="Z308" s="15"/>
       <c r="AA308" s="16">
-        <f t="shared" si="5"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -28719,7 +27818,6 @@
       <c r="Y309" s="14"/>
       <c r="Z309" s="15"/>
       <c r="AA309" s="16">
-        <f t="shared" si="5"/>
         <v>0.29166666666666663</v>
       </c>
     </row>
@@ -28793,7 +27891,6 @@
       <c r="Y310" s="14"/>
       <c r="Z310" s="15"/>
       <c r="AA310" s="16">
-        <f t="shared" si="5"/>
         <v>0.29166666666666663</v>
       </c>
     </row>
@@ -28867,7 +27964,6 @@
       <c r="Y311" s="14"/>
       <c r="Z311" s="15"/>
       <c r="AA311" s="16">
-        <f t="shared" si="5"/>
         <v>0.29166666666666663</v>
       </c>
     </row>
@@ -28941,7 +28037,6 @@
       <c r="Y312" s="14"/>
       <c r="Z312" s="15"/>
       <c r="AA312" s="16">
-        <f t="shared" si="5"/>
         <v>0.29166666666666663</v>
       </c>
     </row>
@@ -29015,7 +28110,6 @@
       <c r="Y313" s="14"/>
       <c r="Z313" s="15"/>
       <c r="AA313" s="16">
-        <f t="shared" si="5"/>
         <v>0.29166666666666663</v>
       </c>
     </row>
@@ -29083,7 +28177,6 @@
       <c r="Y314" s="14"/>
       <c r="Z314" s="15"/>
       <c r="AA314" s="16">
-        <f t="shared" si="5"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -29151,7 +28244,6 @@
       <c r="Y315" s="14"/>
       <c r="Z315" s="15"/>
       <c r="AA315" s="16">
-        <f t="shared" si="5"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -29219,7 +28311,6 @@
       <c r="Y316" s="14"/>
       <c r="Z316" s="15"/>
       <c r="AA316" s="16">
-        <f t="shared" si="5"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -29287,7 +28378,6 @@
       <c r="Y317" s="14"/>
       <c r="Z317" s="15"/>
       <c r="AA317" s="16">
-        <f t="shared" si="5"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -29355,7 +28445,6 @@
       <c r="Y318" s="14"/>
       <c r="Z318" s="15"/>
       <c r="AA318" s="16">
-        <f t="shared" si="5"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -29423,7 +28512,6 @@
       <c r="Y319" s="14"/>
       <c r="Z319" s="15"/>
       <c r="AA319" s="16">
-        <f t="shared" si="5"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -29491,7 +28579,6 @@
       <c r="Y320" s="14"/>
       <c r="Z320" s="15"/>
       <c r="AA320" s="16">
-        <f t="shared" si="5"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -29559,7 +28646,6 @@
       <c r="Y321" s="14"/>
       <c r="Z321" s="15"/>
       <c r="AA321" s="16">
-        <f t="shared" si="5"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -29627,7 +28713,6 @@
       <c r="Y322" s="14"/>
       <c r="Z322" s="15"/>
       <c r="AA322" s="16">
-        <f t="shared" si="5"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -29695,7 +28780,6 @@
       <c r="Y323" s="14"/>
       <c r="Z323" s="15"/>
       <c r="AA323" s="16">
-        <f t="shared" si="5"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -29763,7 +28847,6 @@
       <c r="Y324" s="14"/>
       <c r="Z324" s="15"/>
       <c r="AA324" s="16">
-        <f t="shared" si="5"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -29831,7 +28914,6 @@
       <c r="Y325" s="14"/>
       <c r="Z325" s="15"/>
       <c r="AA325" s="16">
-        <f t="shared" si="5"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -29899,7 +28981,6 @@
       <c r="Y326" s="14"/>
       <c r="Z326" s="15"/>
       <c r="AA326" s="16">
-        <f t="shared" si="5"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -29967,16 +29048,6 @@
       <c r="Y327" s="14"/>
       <c r="Z327" s="15"/>
       <c r="AA327" s="16">
-        <f t="shared" ref="AA327:AA390" si="6">(
-IF(R327="ENVIADO A LA CE/UM",1/3,IF(R327="ENTREGADO/REVISIÓN",2/3,IF(R327="ENVIADO A TICS",1,0)))+
-IF(S327="EN PROCESO",0,IF(S327="CONCLUIDO",1,0))+
-IF(T327="ENVIADO A LA CE/UM",1/3,IF(T327="EN REVISIÓN CENTRAL",2/3,IF(T327="CONCLUIDO",1,0)))+
-IF(U327="ENVIADO A LA CE/UM",1/3,IF(U327="EN REVISIÓN CENTRAL",2/3,IF(U327="CONCLUIDO",1,0)))+
-IF(V327="ENVIADO",1/3,IF(V327="EN PROCESO",2/3,IF(V327="CONCLUIDO",1,0)))+
-IF(W327="PROGRAMADAS",0,IF(W327="CONCLUIDAS",1,0))+
-IF(X327="SI",1,IF(X327="NO",0,0))+
-IF(Y327="SI",1,IF(Y327="NO",0,0))
-)/8</f>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -30054,7 +29125,6 @@
       <c r="Y328" s="14"/>
       <c r="Z328" s="15"/>
       <c r="AA328" s="16">
-        <f t="shared" si="6"/>
         <v>0.70833333333333337</v>
       </c>
     </row>
@@ -30132,7 +29202,6 @@
       <c r="Y329" s="14"/>
       <c r="Z329" s="15"/>
       <c r="AA329" s="16">
-        <f t="shared" si="6"/>
         <v>0.70833333333333337</v>
       </c>
     </row>
@@ -30210,7 +29279,6 @@
       <c r="Y330" s="14"/>
       <c r="Z330" s="15"/>
       <c r="AA330" s="16">
-        <f t="shared" si="6"/>
         <v>0.70833333333333337</v>
       </c>
     </row>
@@ -30288,7 +29356,6 @@
       <c r="Y331" s="14"/>
       <c r="Z331" s="15"/>
       <c r="AA331" s="16">
-        <f t="shared" si="6"/>
         <v>0.70833333333333337</v>
       </c>
     </row>
@@ -30370,7 +29437,6 @@
       </c>
       <c r="Z332" s="15"/>
       <c r="AA332" s="16">
-        <f t="shared" si="6"/>
         <v>0.75</v>
       </c>
     </row>
@@ -30452,7 +29518,6 @@
       </c>
       <c r="Z333" s="15"/>
       <c r="AA333" s="16">
-        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
@@ -30530,7 +29595,6 @@
       <c r="Y334" s="14"/>
       <c r="Z334" s="15"/>
       <c r="AA334" s="16">
-        <f t="shared" si="6"/>
         <v>0.70833333333333337</v>
       </c>
     </row>
@@ -30608,7 +29672,6 @@
       <c r="Y335" s="14"/>
       <c r="Z335" s="15"/>
       <c r="AA335" s="16">
-        <f t="shared" si="6"/>
         <v>0.70833333333333337</v>
       </c>
     </row>
@@ -30686,7 +29749,6 @@
       <c r="Y336" s="14"/>
       <c r="Z336" s="15"/>
       <c r="AA336" s="16">
-        <f t="shared" si="6"/>
         <v>0.70833333333333337</v>
       </c>
     </row>
@@ -30754,7 +29816,6 @@
       <c r="Y337" s="14"/>
       <c r="Z337" s="15"/>
       <c r="AA337" s="16">
-        <f t="shared" si="6"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -30822,7 +29883,6 @@
       <c r="Y338" s="14"/>
       <c r="Z338" s="15"/>
       <c r="AA338" s="16">
-        <f t="shared" si="6"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -30890,7 +29950,6 @@
       <c r="Y339" s="14"/>
       <c r="Z339" s="15"/>
       <c r="AA339" s="16">
-        <f t="shared" si="6"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -30958,7 +30017,6 @@
       <c r="Y340" s="14"/>
       <c r="Z340" s="15"/>
       <c r="AA340" s="16">
-        <f t="shared" si="6"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -31026,7 +30084,6 @@
       <c r="Y341" s="14"/>
       <c r="Z341" s="15"/>
       <c r="AA341" s="16">
-        <f t="shared" si="6"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -31094,7 +30151,6 @@
       <c r="Y342" s="14"/>
       <c r="Z342" s="15"/>
       <c r="AA342" s="16">
-        <f t="shared" si="6"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -31162,7 +30218,6 @@
       <c r="Y343" s="14"/>
       <c r="Z343" s="15"/>
       <c r="AA343" s="16">
-        <f t="shared" si="6"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -31230,7 +30285,6 @@
       <c r="Y344" s="14"/>
       <c r="Z344" s="15"/>
       <c r="AA344" s="16">
-        <f t="shared" si="6"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -31298,7 +30352,6 @@
       <c r="Y345" s="14"/>
       <c r="Z345" s="15"/>
       <c r="AA345" s="16">
-        <f t="shared" si="6"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -31366,7 +30419,6 @@
       <c r="Y346" s="14"/>
       <c r="Z346" s="15"/>
       <c r="AA346" s="16">
-        <f t="shared" si="6"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -31434,7 +30486,6 @@
       <c r="Y347" s="14"/>
       <c r="Z347" s="15"/>
       <c r="AA347" s="16">
-        <f t="shared" si="6"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -31502,7 +30553,6 @@
       <c r="Y348" s="14"/>
       <c r="Z348" s="15"/>
       <c r="AA348" s="16">
-        <f t="shared" si="6"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -31570,7 +30620,6 @@
       <c r="Y349" s="14"/>
       <c r="Z349" s="15"/>
       <c r="AA349" s="16">
-        <f t="shared" si="6"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -31638,7 +30687,6 @@
       <c r="Y350" s="14"/>
       <c r="Z350" s="15"/>
       <c r="AA350" s="16">
-        <f t="shared" si="6"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -31706,7 +30754,6 @@
       <c r="Y351" s="14"/>
       <c r="Z351" s="15"/>
       <c r="AA351" s="16">
-        <f t="shared" si="6"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -31774,7 +30821,6 @@
       <c r="Y352" s="14"/>
       <c r="Z352" s="15"/>
       <c r="AA352" s="16">
-        <f t="shared" si="6"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -31842,7 +30888,6 @@
       <c r="Y353" s="14"/>
       <c r="Z353" s="15"/>
       <c r="AA353" s="16">
-        <f t="shared" si="6"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -31910,7 +30955,6 @@
       <c r="Y354" s="14"/>
       <c r="Z354" s="15"/>
       <c r="AA354" s="16">
-        <f t="shared" si="6"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -31978,7 +31022,6 @@
       <c r="Y355" s="14"/>
       <c r="Z355" s="15"/>
       <c r="AA355" s="16">
-        <f t="shared" si="6"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -32046,7 +31089,6 @@
       <c r="Y356" s="14"/>
       <c r="Z356" s="15"/>
       <c r="AA356" s="16">
-        <f t="shared" si="6"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -32114,7 +31156,6 @@
       <c r="Y357" s="14"/>
       <c r="Z357" s="15"/>
       <c r="AA357" s="16">
-        <f t="shared" si="6"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -32182,7 +31223,6 @@
       <c r="Y358" s="14"/>
       <c r="Z358" s="15"/>
       <c r="AA358" s="16">
-        <f t="shared" si="6"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -32250,7 +31290,6 @@
       <c r="Y359" s="14"/>
       <c r="Z359" s="15"/>
       <c r="AA359" s="16">
-        <f t="shared" si="6"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -32318,7 +31357,6 @@
       <c r="Y360" s="14"/>
       <c r="Z360" s="15"/>
       <c r="AA360" s="16">
-        <f t="shared" si="6"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -32386,7 +31424,6 @@
       <c r="Y361" s="14"/>
       <c r="Z361" s="15"/>
       <c r="AA361" s="16">
-        <f t="shared" si="6"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -32454,7 +31491,6 @@
       <c r="Y362" s="14"/>
       <c r="Z362" s="15"/>
       <c r="AA362" s="16">
-        <f t="shared" si="6"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -32522,7 +31558,6 @@
       <c r="Y363" s="14"/>
       <c r="Z363" s="15"/>
       <c r="AA363" s="16">
-        <f t="shared" si="6"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -32590,7 +31625,6 @@
       <c r="Y364" s="14"/>
       <c r="Z364" s="15"/>
       <c r="AA364" s="16">
-        <f t="shared" si="6"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -32658,7 +31692,6 @@
       <c r="Y365" s="14"/>
       <c r="Z365" s="15"/>
       <c r="AA365" s="16">
-        <f t="shared" si="6"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -32732,7 +31765,6 @@
       <c r="Y366" s="14"/>
       <c r="Z366" s="15"/>
       <c r="AA366" s="16">
-        <f t="shared" si="6"/>
         <v>0.29166666666666663</v>
       </c>
     </row>
@@ -32800,7 +31832,6 @@
       <c r="Y367" s="14"/>
       <c r="Z367" s="15"/>
       <c r="AA367" s="16">
-        <f t="shared" si="6"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -32868,7 +31899,6 @@
       <c r="Y368" s="14"/>
       <c r="Z368" s="15"/>
       <c r="AA368" s="16">
-        <f t="shared" si="6"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -32936,7 +31966,6 @@
       <c r="Y369" s="14"/>
       <c r="Z369" s="15"/>
       <c r="AA369" s="16">
-        <f t="shared" si="6"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -33004,7 +32033,6 @@
       <c r="Y370" s="14"/>
       <c r="Z370" s="15"/>
       <c r="AA370" s="16">
-        <f t="shared" si="6"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -33072,7 +32100,6 @@
       <c r="Y371" s="14"/>
       <c r="Z371" s="15"/>
       <c r="AA371" s="16">
-        <f t="shared" si="6"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -33140,7 +32167,6 @@
       <c r="Y372" s="14"/>
       <c r="Z372" s="15"/>
       <c r="AA372" s="16">
-        <f t="shared" si="6"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -33208,7 +32234,6 @@
       <c r="Y373" s="14"/>
       <c r="Z373" s="15"/>
       <c r="AA373" s="16">
-        <f t="shared" si="6"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -33276,7 +32301,6 @@
       <c r="Y374" s="14"/>
       <c r="Z374" s="15"/>
       <c r="AA374" s="16">
-        <f t="shared" si="6"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -33344,7 +32368,6 @@
       <c r="Y375" s="14"/>
       <c r="Z375" s="15"/>
       <c r="AA375" s="16">
-        <f t="shared" si="6"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -33412,7 +32435,6 @@
       <c r="Y376" s="14"/>
       <c r="Z376" s="15"/>
       <c r="AA376" s="16">
-        <f t="shared" si="6"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -33480,7 +32502,6 @@
       <c r="Y377" s="14"/>
       <c r="Z377" s="15"/>
       <c r="AA377" s="16">
-        <f t="shared" si="6"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -33548,7 +32569,6 @@
       <c r="Y378" s="14"/>
       <c r="Z378" s="15"/>
       <c r="AA378" s="16">
-        <f t="shared" si="6"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -33616,7 +32636,6 @@
       <c r="Y379" s="14"/>
       <c r="Z379" s="15"/>
       <c r="AA379" s="16">
-        <f t="shared" si="6"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -33684,7 +32703,6 @@
       <c r="Y380" s="14"/>
       <c r="Z380" s="15"/>
       <c r="AA380" s="16">
-        <f t="shared" si="6"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -33752,7 +32770,6 @@
       <c r="Y381" s="14"/>
       <c r="Z381" s="15"/>
       <c r="AA381" s="16">
-        <f t="shared" si="6"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -33820,7 +32837,6 @@
       <c r="Y382" s="14"/>
       <c r="Z382" s="15"/>
       <c r="AA382" s="16">
-        <f t="shared" si="6"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -33888,7 +32904,6 @@
       <c r="Y383" s="14"/>
       <c r="Z383" s="15"/>
       <c r="AA383" s="16">
-        <f t="shared" si="6"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -33956,7 +32971,6 @@
       <c r="Y384" s="14"/>
       <c r="Z384" s="15"/>
       <c r="AA384" s="16">
-        <f t="shared" si="6"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -34024,7 +33038,6 @@
       <c r="Y385" s="14"/>
       <c r="Z385" s="15"/>
       <c r="AA385" s="16">
-        <f t="shared" si="6"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -34092,7 +33105,6 @@
       <c r="Y386" s="14"/>
       <c r="Z386" s="15"/>
       <c r="AA386" s="16">
-        <f t="shared" si="6"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -34160,7 +33172,6 @@
       <c r="Y387" s="14"/>
       <c r="Z387" s="15"/>
       <c r="AA387" s="16">
-        <f t="shared" si="6"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -34228,7 +33239,6 @@
       <c r="Y388" s="14"/>
       <c r="Z388" s="15"/>
       <c r="AA388" s="16">
-        <f t="shared" si="6"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -34296,7 +33306,6 @@
       <c r="Y389" s="14"/>
       <c r="Z389" s="15"/>
       <c r="AA389" s="16">
-        <f t="shared" si="6"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -34364,7 +33373,6 @@
       <c r="Y390" s="14"/>
       <c r="Z390" s="15"/>
       <c r="AA390" s="16">
-        <f t="shared" si="6"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -34432,16 +33440,6 @@
       <c r="Y391" s="14"/>
       <c r="Z391" s="15"/>
       <c r="AA391" s="16">
-        <f t="shared" ref="AA391:AA454" si="7">(
-IF(R391="ENVIADO A LA CE/UM",1/3,IF(R391="ENTREGADO/REVISIÓN",2/3,IF(R391="ENVIADO A TICS",1,0)))+
-IF(S391="EN PROCESO",0,IF(S391="CONCLUIDO",1,0))+
-IF(T391="ENVIADO A LA CE/UM",1/3,IF(T391="EN REVISIÓN CENTRAL",2/3,IF(T391="CONCLUIDO",1,0)))+
-IF(U391="ENVIADO A LA CE/UM",1/3,IF(U391="EN REVISIÓN CENTRAL",2/3,IF(U391="CONCLUIDO",1,0)))+
-IF(V391="ENVIADO",1/3,IF(V391="EN PROCESO",2/3,IF(V391="CONCLUIDO",1,0)))+
-IF(W391="PROGRAMADAS",0,IF(W391="CONCLUIDAS",1,0))+
-IF(X391="SI",1,IF(X391="NO",0,0))+
-IF(Y391="SI",1,IF(Y391="NO",0,0))
-)/8</f>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -34509,7 +33507,6 @@
       <c r="Y392" s="14"/>
       <c r="Z392" s="15"/>
       <c r="AA392" s="16">
-        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -34577,7 +33574,6 @@
       <c r="Y393" s="14"/>
       <c r="Z393" s="15"/>
       <c r="AA393" s="16">
-        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -34645,7 +33641,6 @@
       <c r="Y394" s="14"/>
       <c r="Z394" s="15"/>
       <c r="AA394" s="16">
-        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -34713,7 +33708,6 @@
       <c r="Y395" s="14"/>
       <c r="Z395" s="15"/>
       <c r="AA395" s="16">
-        <f t="shared" si="7"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -34781,7 +33775,6 @@
       <c r="Y396" s="14"/>
       <c r="Z396" s="15"/>
       <c r="AA396" s="16">
-        <f t="shared" si="7"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -34849,7 +33842,6 @@
       <c r="Y397" s="14"/>
       <c r="Z397" s="15"/>
       <c r="AA397" s="16">
-        <f t="shared" si="7"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -34917,7 +33909,6 @@
       <c r="Y398" s="14"/>
       <c r="Z398" s="15"/>
       <c r="AA398" s="16">
-        <f t="shared" si="7"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -34985,7 +33976,6 @@
       <c r="Y399" s="14"/>
       <c r="Z399" s="15"/>
       <c r="AA399" s="16">
-        <f t="shared" si="7"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -35053,7 +34043,6 @@
       <c r="Y400" s="14"/>
       <c r="Z400" s="15"/>
       <c r="AA400" s="16">
-        <f t="shared" si="7"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -35121,7 +34110,6 @@
       <c r="Y401" s="14"/>
       <c r="Z401" s="15"/>
       <c r="AA401" s="16">
-        <f t="shared" si="7"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -35189,7 +34177,6 @@
       <c r="Y402" s="14"/>
       <c r="Z402" s="15"/>
       <c r="AA402" s="16">
-        <f t="shared" si="7"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -35257,7 +34244,6 @@
       <c r="Y403" s="14"/>
       <c r="Z403" s="15"/>
       <c r="AA403" s="16">
-        <f t="shared" si="7"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -35325,7 +34311,6 @@
       <c r="Y404" s="14"/>
       <c r="Z404" s="15"/>
       <c r="AA404" s="16">
-        <f t="shared" si="7"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -35393,7 +34378,6 @@
       <c r="Y405" s="14"/>
       <c r="Z405" s="15"/>
       <c r="AA405" s="16">
-        <f t="shared" si="7"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -35461,7 +34445,6 @@
       <c r="Y406" s="14"/>
       <c r="Z406" s="15"/>
       <c r="AA406" s="16">
-        <f t="shared" si="7"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -35529,7 +34512,6 @@
       <c r="Y407" s="14"/>
       <c r="Z407" s="15"/>
       <c r="AA407" s="16">
-        <f t="shared" si="7"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -35597,7 +34579,6 @@
       <c r="Y408" s="14"/>
       <c r="Z408" s="15"/>
       <c r="AA408" s="16">
-        <f t="shared" si="7"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -35665,7 +34646,6 @@
       <c r="Y409" s="14"/>
       <c r="Z409" s="15"/>
       <c r="AA409" s="16">
-        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -35733,7 +34713,6 @@
       <c r="Y410" s="14"/>
       <c r="Z410" s="15"/>
       <c r="AA410" s="16">
-        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -35801,7 +34780,6 @@
       <c r="Y411" s="14"/>
       <c r="Z411" s="15"/>
       <c r="AA411" s="16">
-        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -35869,7 +34847,6 @@
       <c r="Y412" s="14"/>
       <c r="Z412" s="15"/>
       <c r="AA412" s="16">
-        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -35937,7 +34914,6 @@
       <c r="Y413" s="14"/>
       <c r="Z413" s="15"/>
       <c r="AA413" s="16">
-        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -36005,7 +34981,6 @@
       <c r="Y414" s="14"/>
       <c r="Z414" s="15"/>
       <c r="AA414" s="16">
-        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -36073,7 +35048,6 @@
       <c r="Y415" s="14"/>
       <c r="Z415" s="15"/>
       <c r="AA415" s="16">
-        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -36141,7 +35115,6 @@
       <c r="Y416" s="14"/>
       <c r="Z416" s="15"/>
       <c r="AA416" s="16">
-        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -36209,7 +35182,6 @@
       <c r="Y417" s="14"/>
       <c r="Z417" s="15"/>
       <c r="AA417" s="16">
-        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -36277,7 +35249,6 @@
       <c r="Y418" s="14"/>
       <c r="Z418" s="15"/>
       <c r="AA418" s="16">
-        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -36345,7 +35316,6 @@
       <c r="Y419" s="14"/>
       <c r="Z419" s="15"/>
       <c r="AA419" s="16">
-        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -36413,7 +35383,6 @@
       <c r="Y420" s="14"/>
       <c r="Z420" s="15"/>
       <c r="AA420" s="16">
-        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -36481,7 +35450,6 @@
       <c r="Y421" s="14"/>
       <c r="Z421" s="15"/>
       <c r="AA421" s="16">
-        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -36549,7 +35517,6 @@
       <c r="Y422" s="14"/>
       <c r="Z422" s="15"/>
       <c r="AA422" s="16">
-        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -36617,7 +35584,6 @@
       <c r="Y423" s="14"/>
       <c r="Z423" s="15"/>
       <c r="AA423" s="16">
-        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -36685,7 +35651,6 @@
       <c r="Y424" s="14"/>
       <c r="Z424" s="15"/>
       <c r="AA424" s="16">
-        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -36753,7 +35718,6 @@
       <c r="Y425" s="14"/>
       <c r="Z425" s="15"/>
       <c r="AA425" s="16">
-        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -36821,7 +35785,6 @@
       <c r="Y426" s="14"/>
       <c r="Z426" s="15"/>
       <c r="AA426" s="16">
-        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -36889,7 +35852,6 @@
       <c r="Y427" s="14"/>
       <c r="Z427" s="15"/>
       <c r="AA427" s="16">
-        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -36957,7 +35919,6 @@
       <c r="Y428" s="14"/>
       <c r="Z428" s="15"/>
       <c r="AA428" s="16">
-        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -37025,7 +35986,6 @@
       <c r="Y429" s="14"/>
       <c r="Z429" s="15"/>
       <c r="AA429" s="16">
-        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -37093,7 +36053,6 @@
       <c r="Y430" s="14"/>
       <c r="Z430" s="15"/>
       <c r="AA430" s="16">
-        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -37161,7 +36120,6 @@
       <c r="Y431" s="14"/>
       <c r="Z431" s="15"/>
       <c r="AA431" s="16">
-        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -37229,7 +36187,6 @@
       <c r="Y432" s="14"/>
       <c r="Z432" s="15"/>
       <c r="AA432" s="16">
-        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -37297,7 +36254,6 @@
       <c r="Y433" s="14"/>
       <c r="Z433" s="15"/>
       <c r="AA433" s="16">
-        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -37365,7 +36321,6 @@
       <c r="Y434" s="14"/>
       <c r="Z434" s="15"/>
       <c r="AA434" s="16">
-        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -37433,7 +36388,6 @@
       <c r="Y435" s="14"/>
       <c r="Z435" s="15"/>
       <c r="AA435" s="16">
-        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -37501,7 +36455,6 @@
       <c r="Y436" s="14"/>
       <c r="Z436" s="15"/>
       <c r="AA436" s="16">
-        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -37569,7 +36522,6 @@
       <c r="Y437" s="14"/>
       <c r="Z437" s="15"/>
       <c r="AA437" s="16">
-        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -37637,7 +36589,6 @@
       <c r="Y438" s="14"/>
       <c r="Z438" s="15"/>
       <c r="AA438" s="16">
-        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -37705,7 +36656,6 @@
       <c r="Y439" s="14"/>
       <c r="Z439" s="15"/>
       <c r="AA439" s="16">
-        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -37773,7 +36723,6 @@
       <c r="Y440" s="14"/>
       <c r="Z440" s="15"/>
       <c r="AA440" s="16">
-        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -37841,7 +36790,6 @@
       <c r="Y441" s="14"/>
       <c r="Z441" s="15"/>
       <c r="AA441" s="16">
-        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -37909,7 +36857,6 @@
       <c r="Y442" s="14"/>
       <c r="Z442" s="15"/>
       <c r="AA442" s="16">
-        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -37977,7 +36924,6 @@
       <c r="Y443" s="14"/>
       <c r="Z443" s="15"/>
       <c r="AA443" s="16">
-        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -38045,7 +36991,6 @@
       <c r="Y444" s="14"/>
       <c r="Z444" s="15"/>
       <c r="AA444" s="16">
-        <f t="shared" si="7"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -38119,7 +37064,6 @@
       <c r="Y445" s="14"/>
       <c r="Z445" s="15"/>
       <c r="AA445" s="16">
-        <f t="shared" si="7"/>
         <v>0.29166666666666663</v>
       </c>
     </row>
@@ -38193,7 +37137,6 @@
       <c r="Y446" s="14"/>
       <c r="Z446" s="15"/>
       <c r="AA446" s="16">
-        <f t="shared" si="7"/>
         <v>0.29166666666666663</v>
       </c>
     </row>
@@ -38267,7 +37210,6 @@
       <c r="Y447" s="14"/>
       <c r="Z447" s="15"/>
       <c r="AA447" s="16">
-        <f t="shared" si="7"/>
         <v>0.29166666666666663</v>
       </c>
     </row>
@@ -38341,7 +37283,6 @@
       <c r="Y448" s="14"/>
       <c r="Z448" s="15"/>
       <c r="AA448" s="16">
-        <f t="shared" si="7"/>
         <v>0.29166666666666663</v>
       </c>
     </row>
@@ -38415,7 +37356,6 @@
       <c r="Y449" s="14"/>
       <c r="Z449" s="15"/>
       <c r="AA449" s="16">
-        <f t="shared" si="7"/>
         <v>0.29166666666666663</v>
       </c>
     </row>
@@ -38489,7 +37429,6 @@
       <c r="Y450" s="14"/>
       <c r="Z450" s="15"/>
       <c r="AA450" s="16">
-        <f t="shared" si="7"/>
         <v>0.29166666666666663</v>
       </c>
     </row>
@@ -38563,7 +37502,6 @@
       <c r="Y451" s="14"/>
       <c r="Z451" s="15"/>
       <c r="AA451" s="16">
-        <f t="shared" si="7"/>
         <v>0.29166666666666663</v>
       </c>
     </row>
@@ -38637,7 +37575,6 @@
       <c r="Y452" s="14"/>
       <c r="Z452" s="15"/>
       <c r="AA452" s="16">
-        <f t="shared" si="7"/>
         <v>0.29166666666666663</v>
       </c>
     </row>
@@ -38711,7 +37648,6 @@
       <c r="Y453" s="14"/>
       <c r="Z453" s="15"/>
       <c r="AA453" s="16">
-        <f t="shared" si="7"/>
         <v>0.29166666666666663</v>
       </c>
     </row>
@@ -38785,7 +37721,6 @@
       <c r="Y454" s="14"/>
       <c r="Z454" s="15"/>
       <c r="AA454" s="16">
-        <f t="shared" si="7"/>
         <v>0.29166666666666663</v>
       </c>
     </row>
@@ -38851,16 +37786,6 @@
       <c r="Y455" s="14"/>
       <c r="Z455" s="15"/>
       <c r="AA455" s="16">
-        <f t="shared" ref="AA455:AA518" si="8">(
-IF(R455="ENVIADO A LA CE/UM",1/3,IF(R455="ENTREGADO/REVISIÓN",2/3,IF(R455="ENVIADO A TICS",1,0)))+
-IF(S455="EN PROCESO",0,IF(S455="CONCLUIDO",1,0))+
-IF(T455="ENVIADO A LA CE/UM",1/3,IF(T455="EN REVISIÓN CENTRAL",2/3,IF(T455="CONCLUIDO",1,0)))+
-IF(U455="ENVIADO A LA CE/UM",1/3,IF(U455="EN REVISIÓN CENTRAL",2/3,IF(U455="CONCLUIDO",1,0)))+
-IF(V455="ENVIADO",1/3,IF(V455="EN PROCESO",2/3,IF(V455="CONCLUIDO",1,0)))+
-IF(W455="PROGRAMADAS",0,IF(W455="CONCLUIDAS",1,0))+
-IF(X455="SI",1,IF(X455="NO",0,0))+
-IF(Y455="SI",1,IF(Y455="NO",0,0))
-)/8</f>
         <v>0</v>
       </c>
     </row>
@@ -38926,7 +37851,6 @@
       <c r="Y456" s="14"/>
       <c r="Z456" s="15"/>
       <c r="AA456" s="16">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -38992,7 +37916,6 @@
       <c r="Y457" s="14"/>
       <c r="Z457" s="15"/>
       <c r="AA457" s="16">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -39058,7 +37981,6 @@
       <c r="Y458" s="14"/>
       <c r="Z458" s="15"/>
       <c r="AA458" s="16">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -39124,7 +38046,6 @@
       <c r="Y459" s="14"/>
       <c r="Z459" s="15"/>
       <c r="AA459" s="16">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -39190,7 +38111,6 @@
       <c r="Y460" s="14"/>
       <c r="Z460" s="15"/>
       <c r="AA460" s="16">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -39256,7 +38176,6 @@
       <c r="Y461" s="14"/>
       <c r="Z461" s="15"/>
       <c r="AA461" s="16">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -39322,7 +38241,6 @@
       <c r="Y462" s="14"/>
       <c r="Z462" s="15"/>
       <c r="AA462" s="16">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -39388,7 +38306,6 @@
       <c r="Y463" s="14"/>
       <c r="Z463" s="15"/>
       <c r="AA463" s="16">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -39454,7 +38371,6 @@
       <c r="Y464" s="14"/>
       <c r="Z464" s="15"/>
       <c r="AA464" s="16">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -39520,7 +38436,6 @@
       <c r="Y465" s="14"/>
       <c r="Z465" s="15"/>
       <c r="AA465" s="16">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -39586,7 +38501,6 @@
       <c r="Y466" s="14"/>
       <c r="Z466" s="15"/>
       <c r="AA466" s="16">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -39652,7 +38566,6 @@
       <c r="Y467" s="14"/>
       <c r="Z467" s="15"/>
       <c r="AA467" s="16">
-        <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
@@ -39720,7 +38633,6 @@
       <c r="Y468" s="14"/>
       <c r="Z468" s="15"/>
       <c r="AA468" s="16">
-        <f t="shared" si="8"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -39788,7 +38700,6 @@
       <c r="Y469" s="14"/>
       <c r="Z469" s="15"/>
       <c r="AA469" s="16">
-        <f t="shared" si="8"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -39856,7 +38767,6 @@
       <c r="Y470" s="14"/>
       <c r="Z470" s="15"/>
       <c r="AA470" s="16">
-        <f t="shared" si="8"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -39924,7 +38834,6 @@
       <c r="Y471" s="14"/>
       <c r="Z471" s="15"/>
       <c r="AA471" s="16">
-        <f t="shared" si="8"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -39992,7 +38901,6 @@
       <c r="Y472" s="14"/>
       <c r="Z472" s="15"/>
       <c r="AA472" s="16">
-        <f t="shared" si="8"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -40060,7 +38968,6 @@
       <c r="Y473" s="14"/>
       <c r="Z473" s="15"/>
       <c r="AA473" s="16">
-        <f t="shared" si="8"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -40128,7 +39035,6 @@
       <c r="Y474" s="14"/>
       <c r="Z474" s="15"/>
       <c r="AA474" s="16">
-        <f t="shared" si="8"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -40196,7 +39102,6 @@
       <c r="Y475" s="14"/>
       <c r="Z475" s="15"/>
       <c r="AA475" s="16">
-        <f t="shared" si="8"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -40264,7 +39169,6 @@
       <c r="Y476" s="14"/>
       <c r="Z476" s="15"/>
       <c r="AA476" s="16">
-        <f t="shared" si="8"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -40332,7 +39236,6 @@
       <c r="Y477" s="14"/>
       <c r="Z477" s="15"/>
       <c r="AA477" s="16">
-        <f t="shared" si="8"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -40400,7 +39303,6 @@
       <c r="Y478" s="14"/>
       <c r="Z478" s="15"/>
       <c r="AA478" s="16">
-        <f t="shared" si="8"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -40468,7 +39370,6 @@
       <c r="Y479" s="14"/>
       <c r="Z479" s="15"/>
       <c r="AA479" s="16">
-        <f t="shared" si="8"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -40536,7 +39437,6 @@
       <c r="Y480" s="14"/>
       <c r="Z480" s="15"/>
       <c r="AA480" s="16">
-        <f t="shared" si="8"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -40604,7 +39504,6 @@
       <c r="Y481" s="14"/>
       <c r="Z481" s="15"/>
       <c r="AA481" s="16">
-        <f t="shared" si="8"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -40672,7 +39571,6 @@
       <c r="Y482" s="14"/>
       <c r="Z482" s="15"/>
       <c r="AA482" s="16">
-        <f t="shared" si="8"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -40740,7 +39638,6 @@
       <c r="Y483" s="14"/>
       <c r="Z483" s="15"/>
       <c r="AA483" s="16">
-        <f t="shared" si="8"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -40808,7 +39705,6 @@
       <c r="Y484" s="14"/>
       <c r="Z484" s="15"/>
       <c r="AA484" s="16">
-        <f t="shared" si="8"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -40876,7 +39772,6 @@
       <c r="Y485" s="14"/>
       <c r="Z485" s="15"/>
       <c r="AA485" s="16">
-        <f t="shared" si="8"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -40944,7 +39839,6 @@
       <c r="Y486" s="14"/>
       <c r="Z486" s="15"/>
       <c r="AA486" s="16">
-        <f t="shared" si="8"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -41012,7 +39906,6 @@
       <c r="Y487" s="14"/>
       <c r="Z487" s="15"/>
       <c r="AA487" s="16">
-        <f t="shared" si="8"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -41080,7 +39973,6 @@
       <c r="Y488" s="14"/>
       <c r="Z488" s="15"/>
       <c r="AA488" s="16">
-        <f t="shared" si="8"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -41148,7 +40040,6 @@
       <c r="Y489" s="14"/>
       <c r="Z489" s="15"/>
       <c r="AA489" s="16">
-        <f t="shared" si="8"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -41216,7 +40107,6 @@
       <c r="Y490" s="14"/>
       <c r="Z490" s="15"/>
       <c r="AA490" s="16">
-        <f t="shared" si="8"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -41284,7 +40174,6 @@
       <c r="Y491" s="14"/>
       <c r="Z491" s="15"/>
       <c r="AA491" s="16">
-        <f t="shared" si="8"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -41352,7 +40241,6 @@
       <c r="Y492" s="14"/>
       <c r="Z492" s="15"/>
       <c r="AA492" s="16">
-        <f t="shared" si="8"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -41420,7 +40308,6 @@
       <c r="Y493" s="14"/>
       <c r="Z493" s="15"/>
       <c r="AA493" s="16">
-        <f t="shared" si="8"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -41488,7 +40375,6 @@
       <c r="Y494" s="14"/>
       <c r="Z494" s="15"/>
       <c r="AA494" s="16">
-        <f t="shared" si="8"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -41556,7 +40442,6 @@
       <c r="Y495" s="14"/>
       <c r="Z495" s="15"/>
       <c r="AA495" s="16">
-        <f t="shared" si="8"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -41624,7 +40509,6 @@
       <c r="Y496" s="14"/>
       <c r="Z496" s="15"/>
       <c r="AA496" s="16">
-        <f t="shared" si="8"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -41692,7 +40576,6 @@
       <c r="Y497" s="14"/>
       <c r="Z497" s="15"/>
       <c r="AA497" s="16">
-        <f t="shared" si="8"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -41760,7 +40643,6 @@
       <c r="Y498" s="14"/>
       <c r="Z498" s="15"/>
       <c r="AA498" s="16">
-        <f t="shared" si="8"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -41828,7 +40710,6 @@
       <c r="Y499" s="14"/>
       <c r="Z499" s="15"/>
       <c r="AA499" s="16">
-        <f t="shared" si="8"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -41896,7 +40777,6 @@
       <c r="Y500" s="14"/>
       <c r="Z500" s="15"/>
       <c r="AA500" s="16">
-        <f t="shared" si="8"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -41964,7 +40844,6 @@
       <c r="Y501" s="14"/>
       <c r="Z501" s="15"/>
       <c r="AA501" s="16">
-        <f t="shared" si="8"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -42032,7 +40911,6 @@
       <c r="Y502" s="14"/>
       <c r="Z502" s="15"/>
       <c r="AA502" s="16">
-        <f t="shared" si="8"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -42100,7 +40978,6 @@
       <c r="Y503" s="14"/>
       <c r="Z503" s="15"/>
       <c r="AA503" s="16">
-        <f t="shared" si="8"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -42168,7 +41045,6 @@
       <c r="Y504" s="14"/>
       <c r="Z504" s="15"/>
       <c r="AA504" s="16">
-        <f t="shared" si="8"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -42236,7 +41112,6 @@
       <c r="Y505" s="14"/>
       <c r="Z505" s="15"/>
       <c r="AA505" s="16">
-        <f t="shared" si="8"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -42304,7 +41179,6 @@
       <c r="Y506" s="14"/>
       <c r="Z506" s="15"/>
       <c r="AA506" s="16">
-        <f t="shared" si="8"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -42372,7 +41246,6 @@
       <c r="Y507" s="14"/>
       <c r="Z507" s="15"/>
       <c r="AA507" s="16">
-        <f t="shared" si="8"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -42440,7 +41313,6 @@
       <c r="Y508" s="14"/>
       <c r="Z508" s="15"/>
       <c r="AA508" s="16">
-        <f t="shared" si="8"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -42508,7 +41380,6 @@
       <c r="Y509" s="14"/>
       <c r="Z509" s="15"/>
       <c r="AA509" s="16">
-        <f t="shared" si="8"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -42576,7 +41447,6 @@
       <c r="Y510" s="14"/>
       <c r="Z510" s="15"/>
       <c r="AA510" s="16">
-        <f t="shared" si="8"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -42644,7 +41514,6 @@
       <c r="Y511" s="14"/>
       <c r="Z511" s="15"/>
       <c r="AA511" s="16">
-        <f t="shared" si="8"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -42712,7 +41581,6 @@
       <c r="Y512" s="14"/>
       <c r="Z512" s="15"/>
       <c r="AA512" s="16">
-        <f t="shared" si="8"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -42780,7 +41648,6 @@
       <c r="Y513" s="14"/>
       <c r="Z513" s="15"/>
       <c r="AA513" s="16">
-        <f t="shared" si="8"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -42848,7 +41715,6 @@
       <c r="Y514" s="14"/>
       <c r="Z514" s="15"/>
       <c r="AA514" s="16">
-        <f t="shared" si="8"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -42916,7 +41782,6 @@
       <c r="Y515" s="14"/>
       <c r="Z515" s="15"/>
       <c r="AA515" s="16">
-        <f t="shared" si="8"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -42984,7 +41849,6 @@
       <c r="Y516" s="14"/>
       <c r="Z516" s="15"/>
       <c r="AA516" s="16">
-        <f t="shared" si="8"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -43052,7 +41916,6 @@
       <c r="Y517" s="14"/>
       <c r="Z517" s="15"/>
       <c r="AA517" s="16">
-        <f t="shared" si="8"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -43120,7 +41983,6 @@
       <c r="Y518" s="14"/>
       <c r="Z518" s="15"/>
       <c r="AA518" s="16">
-        <f t="shared" si="8"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -43188,16 +42050,6 @@
       <c r="Y519" s="14"/>
       <c r="Z519" s="15"/>
       <c r="AA519" s="16">
-        <f t="shared" ref="AA519:AA582" si="9">(
-IF(R519="ENVIADO A LA CE/UM",1/3,IF(R519="ENTREGADO/REVISIÓN",2/3,IF(R519="ENVIADO A TICS",1,0)))+
-IF(S519="EN PROCESO",0,IF(S519="CONCLUIDO",1,0))+
-IF(T519="ENVIADO A LA CE/UM",1/3,IF(T519="EN REVISIÓN CENTRAL",2/3,IF(T519="CONCLUIDO",1,0)))+
-IF(U519="ENVIADO A LA CE/UM",1/3,IF(U519="EN REVISIÓN CENTRAL",2/3,IF(U519="CONCLUIDO",1,0)))+
-IF(V519="ENVIADO",1/3,IF(V519="EN PROCESO",2/3,IF(V519="CONCLUIDO",1,0)))+
-IF(W519="PROGRAMADAS",0,IF(W519="CONCLUIDAS",1,0))+
-IF(X519="SI",1,IF(X519="NO",0,0))+
-IF(Y519="SI",1,IF(Y519="NO",0,0))
-)/8</f>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -43265,7 +42117,6 @@
       <c r="Y520" s="14"/>
       <c r="Z520" s="15"/>
       <c r="AA520" s="16">
-        <f t="shared" si="9"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -43333,7 +42184,6 @@
       <c r="Y521" s="14"/>
       <c r="Z521" s="15"/>
       <c r="AA521" s="16">
-        <f t="shared" si="9"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -43401,7 +42251,6 @@
       <c r="Y522" s="14"/>
       <c r="Z522" s="15"/>
       <c r="AA522" s="16">
-        <f t="shared" si="9"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -43469,7 +42318,6 @@
       <c r="Y523" s="14"/>
       <c r="Z523" s="15"/>
       <c r="AA523" s="16">
-        <f t="shared" si="9"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -43537,7 +42385,6 @@
       <c r="Y524" s="14"/>
       <c r="Z524" s="15"/>
       <c r="AA524" s="16">
-        <f t="shared" si="9"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -43605,7 +42452,6 @@
       <c r="Y525" s="14"/>
       <c r="Z525" s="15"/>
       <c r="AA525" s="16">
-        <f t="shared" si="9"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -43673,7 +42519,6 @@
       <c r="Y526" s="14"/>
       <c r="Z526" s="15"/>
       <c r="AA526" s="16">
-        <f t="shared" si="9"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -43741,7 +42586,6 @@
       <c r="Y527" s="14"/>
       <c r="Z527" s="15"/>
       <c r="AA527" s="16">
-        <f t="shared" si="9"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -43809,7 +42653,6 @@
       <c r="Y528" s="14"/>
       <c r="Z528" s="15"/>
       <c r="AA528" s="16">
-        <f t="shared" si="9"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -43877,7 +42720,6 @@
       <c r="Y529" s="14"/>
       <c r="Z529" s="15"/>
       <c r="AA529" s="16">
-        <f t="shared" si="9"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -43945,7 +42787,6 @@
       <c r="Y530" s="14"/>
       <c r="Z530" s="15"/>
       <c r="AA530" s="16">
-        <f t="shared" si="9"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -44013,7 +42854,6 @@
       <c r="Y531" s="14"/>
       <c r="Z531" s="15"/>
       <c r="AA531" s="16">
-        <f t="shared" si="9"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -44081,7 +42921,6 @@
       <c r="Y532" s="14"/>
       <c r="Z532" s="15"/>
       <c r="AA532" s="16">
-        <f t="shared" si="9"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -44149,7 +42988,6 @@
       <c r="Y533" s="14"/>
       <c r="Z533" s="15"/>
       <c r="AA533" s="16">
-        <f t="shared" si="9"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -44217,7 +43055,6 @@
       <c r="Y534" s="14"/>
       <c r="Z534" s="15"/>
       <c r="AA534" s="16">
-        <f t="shared" si="9"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -44285,7 +43122,6 @@
       <c r="Y535" s="14"/>
       <c r="Z535" s="15"/>
       <c r="AA535" s="16">
-        <f t="shared" si="9"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -44353,7 +43189,6 @@
       <c r="Y536" s="14"/>
       <c r="Z536" s="15"/>
       <c r="AA536" s="16">
-        <f t="shared" si="9"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -44421,7 +43256,6 @@
       <c r="Y537" s="14"/>
       <c r="Z537" s="15"/>
       <c r="AA537" s="16">
-        <f t="shared" si="9"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -44489,7 +43323,6 @@
       <c r="Y538" s="14"/>
       <c r="Z538" s="15"/>
       <c r="AA538" s="16">
-        <f t="shared" si="9"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -44557,7 +43390,6 @@
       <c r="Y539" s="14"/>
       <c r="Z539" s="15"/>
       <c r="AA539" s="16">
-        <f t="shared" si="9"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -44631,7 +43463,6 @@
       <c r="Y540" s="14"/>
       <c r="Z540" s="15"/>
       <c r="AA540" s="16">
-        <f t="shared" si="9"/>
         <v>0.29166666666666663</v>
       </c>
     </row>
@@ -44699,7 +43530,6 @@
       <c r="Y541" s="14"/>
       <c r="Z541" s="15"/>
       <c r="AA541" s="16">
-        <f t="shared" si="9"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -44773,7 +43603,6 @@
       <c r="Y542" s="14"/>
       <c r="Z542" s="15"/>
       <c r="AA542" s="16">
-        <f t="shared" si="9"/>
         <v>0.29166666666666663</v>
       </c>
     </row>
@@ -44847,7 +43676,6 @@
       <c r="Y543" s="14"/>
       <c r="Z543" s="15"/>
       <c r="AA543" s="16">
-        <f t="shared" si="9"/>
         <v>0.29166666666666663</v>
       </c>
     </row>
@@ -44925,7 +43753,6 @@
       <c r="Y544" s="14"/>
       <c r="Z544" s="15"/>
       <c r="AA544" s="16">
-        <f t="shared" si="9"/>
         <v>0.70833333333333337</v>
       </c>
     </row>
@@ -44993,7 +43820,6 @@
       <c r="Y545" s="14"/>
       <c r="Z545" s="15"/>
       <c r="AA545" s="16">
-        <f t="shared" si="9"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -45067,7 +43893,6 @@
       <c r="Y546" s="14"/>
       <c r="Z546" s="15"/>
       <c r="AA546" s="16">
-        <f t="shared" si="9"/>
         <v>0.29166666666666663</v>
       </c>
     </row>
@@ -45135,7 +43960,6 @@
       <c r="Y547" s="14"/>
       <c r="Z547" s="15"/>
       <c r="AA547" s="16">
-        <f t="shared" si="9"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -45209,7 +44033,6 @@
       <c r="Y548" s="14"/>
       <c r="Z548" s="15"/>
       <c r="AA548" s="16">
-        <f t="shared" si="9"/>
         <v>0.29166666666666663</v>
       </c>
     </row>
@@ -45277,7 +44100,6 @@
       <c r="Y549" s="14"/>
       <c r="Z549" s="15"/>
       <c r="AA549" s="16">
-        <f t="shared" si="9"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -45351,7 +44173,6 @@
       <c r="Y550" s="14"/>
       <c r="Z550" s="15"/>
       <c r="AA550" s="16">
-        <f t="shared" si="9"/>
         <v>0.29166666666666663</v>
       </c>
     </row>
@@ -45419,7 +44240,6 @@
       <c r="Y551" s="14"/>
       <c r="Z551" s="15"/>
       <c r="AA551" s="16">
-        <f t="shared" si="9"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -45487,7 +44307,6 @@
       <c r="Y552" s="14"/>
       <c r="Z552" s="15"/>
       <c r="AA552" s="16">
-        <f t="shared" si="9"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -45555,7 +44374,6 @@
       <c r="Y553" s="14"/>
       <c r="Z553" s="15"/>
       <c r="AA553" s="16">
-        <f t="shared" si="9"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -45623,7 +44441,6 @@
       <c r="Y554" s="14"/>
       <c r="Z554" s="15"/>
       <c r="AA554" s="16">
-        <f t="shared" si="9"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -45691,7 +44508,6 @@
       <c r="Y555" s="14"/>
       <c r="Z555" s="15"/>
       <c r="AA555" s="16">
-        <f t="shared" si="9"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -45759,7 +44575,6 @@
       <c r="Y556" s="14"/>
       <c r="Z556" s="15"/>
       <c r="AA556" s="16">
-        <f t="shared" si="9"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -45827,7 +44642,6 @@
       <c r="Y557" s="14"/>
       <c r="Z557" s="15"/>
       <c r="AA557" s="16">
-        <f t="shared" si="9"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -45895,7 +44709,6 @@
       <c r="Y558" s="14"/>
       <c r="Z558" s="15"/>
       <c r="AA558" s="16">
-        <f t="shared" si="9"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -45963,7 +44776,6 @@
       <c r="Y559" s="14"/>
       <c r="Z559" s="15"/>
       <c r="AA559" s="16">
-        <f t="shared" si="9"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -46031,7 +44843,6 @@
       <c r="Y560" s="14"/>
       <c r="Z560" s="15"/>
       <c r="AA560" s="16">
-        <f t="shared" si="9"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -46099,7 +44910,6 @@
       <c r="Y561" s="14"/>
       <c r="Z561" s="15"/>
       <c r="AA561" s="16">
-        <f t="shared" si="9"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -46165,7 +44975,6 @@
       <c r="Y562" s="14"/>
       <c r="Z562" s="15"/>
       <c r="AA562" s="16">
-        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -46233,7 +45042,6 @@
       <c r="Y563" s="14"/>
       <c r="Z563" s="15"/>
       <c r="AA563" s="16">
-        <f t="shared" si="9"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -46301,7 +45109,6 @@
       <c r="Y564" s="14"/>
       <c r="Z564" s="15"/>
       <c r="AA564" s="16">
-        <f t="shared" si="9"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -46369,7 +45176,6 @@
       <c r="Y565" s="14"/>
       <c r="Z565" s="15"/>
       <c r="AA565" s="16">
-        <f t="shared" si="9"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -46437,7 +45243,6 @@
       <c r="Y566" s="14"/>
       <c r="Z566" s="15"/>
       <c r="AA566" s="16">
-        <f t="shared" si="9"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -46505,7 +45310,6 @@
       <c r="Y567" s="14"/>
       <c r="Z567" s="15"/>
       <c r="AA567" s="16">
-        <f t="shared" si="9"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -46573,7 +45377,6 @@
       <c r="Y568" s="14"/>
       <c r="Z568" s="15"/>
       <c r="AA568" s="16">
-        <f t="shared" si="9"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -46641,7 +45444,6 @@
       <c r="Y569" s="14"/>
       <c r="Z569" s="15"/>
       <c r="AA569" s="16">
-        <f t="shared" si="9"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -46709,7 +45511,6 @@
       <c r="Y570" s="14"/>
       <c r="Z570" s="15"/>
       <c r="AA570" s="16">
-        <f t="shared" si="9"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -46777,7 +45578,6 @@
       <c r="Y571" s="14"/>
       <c r="Z571" s="15"/>
       <c r="AA571" s="16">
-        <f t="shared" si="9"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -46845,7 +45645,6 @@
       <c r="Y572" s="14"/>
       <c r="Z572" s="15"/>
       <c r="AA572" s="16">
-        <f t="shared" si="9"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -46913,7 +45712,6 @@
       <c r="Y573" s="14"/>
       <c r="Z573" s="15"/>
       <c r="AA573" s="16">
-        <f t="shared" si="9"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -46981,7 +45779,6 @@
       <c r="Y574" s="14"/>
       <c r="Z574" s="15"/>
       <c r="AA574" s="16">
-        <f t="shared" si="9"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -47049,7 +45846,6 @@
       <c r="Y575" s="14"/>
       <c r="Z575" s="15"/>
       <c r="AA575" s="16">
-        <f t="shared" si="9"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -47117,7 +45913,6 @@
       <c r="Y576" s="14"/>
       <c r="Z576" s="15"/>
       <c r="AA576" s="16">
-        <f t="shared" si="9"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -47183,7 +45978,6 @@
       <c r="Y577" s="14"/>
       <c r="Z577" s="15"/>
       <c r="AA577" s="16">
-        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -47257,7 +46051,6 @@
       <c r="Y578" s="14"/>
       <c r="Z578" s="15"/>
       <c r="AA578" s="16">
-        <f t="shared" si="9"/>
         <v>0.29166666666666663</v>
       </c>
     </row>
@@ -47325,7 +46118,6 @@
       <c r="Y579" s="14"/>
       <c r="Z579" s="15"/>
       <c r="AA579" s="16">
-        <f t="shared" si="9"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -47393,7 +46185,6 @@
       <c r="Y580" s="14"/>
       <c r="Z580" s="15"/>
       <c r="AA580" s="16">
-        <f t="shared" si="9"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -47471,7 +46262,6 @@
       <c r="Y581" s="14"/>
       <c r="Z581" s="15"/>
       <c r="AA581" s="16">
-        <f t="shared" si="9"/>
         <v>0.70833333333333337</v>
       </c>
     </row>
@@ -47539,7 +46329,6 @@
       <c r="Y582" s="14"/>
       <c r="Z582" s="15"/>
       <c r="AA582" s="16">
-        <f t="shared" si="9"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -47607,16 +46396,6 @@
       <c r="Y583" s="14"/>
       <c r="Z583" s="15"/>
       <c r="AA583" s="16">
-        <f t="shared" ref="AA583:AA596" si="10">(
-IF(R583="ENVIADO A LA CE/UM",1/3,IF(R583="ENTREGADO/REVISIÓN",2/3,IF(R583="ENVIADO A TICS",1,0)))+
-IF(S583="EN PROCESO",0,IF(S583="CONCLUIDO",1,0))+
-IF(T583="ENVIADO A LA CE/UM",1/3,IF(T583="EN REVISIÓN CENTRAL",2/3,IF(T583="CONCLUIDO",1,0)))+
-IF(U583="ENVIADO A LA CE/UM",1/3,IF(U583="EN REVISIÓN CENTRAL",2/3,IF(U583="CONCLUIDO",1,0)))+
-IF(V583="ENVIADO",1/3,IF(V583="EN PROCESO",2/3,IF(V583="CONCLUIDO",1,0)))+
-IF(W583="PROGRAMADAS",0,IF(W583="CONCLUIDAS",1,0))+
-IF(X583="SI",1,IF(X583="NO",0,0))+
-IF(Y583="SI",1,IF(Y583="NO",0,0))
-)/8</f>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -47684,7 +46463,6 @@
       <c r="Y584" s="14"/>
       <c r="Z584" s="15"/>
       <c r="AA584" s="16">
-        <f t="shared" si="10"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -47752,7 +46530,6 @@
       <c r="Y585" s="14"/>
       <c r="Z585" s="15"/>
       <c r="AA585" s="16">
-        <f t="shared" si="10"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -47820,7 +46597,6 @@
       <c r="Y586" s="14"/>
       <c r="Z586" s="15"/>
       <c r="AA586" s="16">
-        <f t="shared" si="10"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -47888,7 +46664,6 @@
       <c r="Y587" s="14"/>
       <c r="Z587" s="15"/>
       <c r="AA587" s="16">
-        <f t="shared" si="10"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -47956,7 +46731,6 @@
       <c r="Y588" s="14"/>
       <c r="Z588" s="15"/>
       <c r="AA588" s="16">
-        <f t="shared" si="10"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -48024,7 +46798,6 @@
       <c r="Y589" s="14"/>
       <c r="Z589" s="15"/>
       <c r="AA589" s="16">
-        <f t="shared" si="10"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -48098,7 +46871,6 @@
       <c r="Y590" s="14"/>
       <c r="Z590" s="15"/>
       <c r="AA590" s="16">
-        <f t="shared" si="10"/>
         <v>0.29166666666666663</v>
       </c>
     </row>
@@ -48172,7 +46944,6 @@
       <c r="Y591" s="14"/>
       <c r="Z591" s="15"/>
       <c r="AA591" s="16">
-        <f t="shared" si="10"/>
         <v>0.29166666666666663</v>
       </c>
     </row>
@@ -48238,11 +47009,10 @@
       <c r="Y592" s="14"/>
       <c r="Z592" s="15"/>
       <c r="AA592" s="16">
-        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
-    <row r="593" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A593" s="6" t="s">
         <v>1707</v>
       </c>
@@ -48306,11 +47076,10 @@
       <c r="Y593" s="14"/>
       <c r="Z593" s="15"/>
       <c r="AA593" s="16">
-        <f t="shared" si="10"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
-    <row r="594" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A594" s="6" t="s">
         <v>1709</v>
       </c>
@@ -48374,11 +47143,10 @@
       <c r="Y594" s="14"/>
       <c r="Z594" s="15"/>
       <c r="AA594" s="16">
-        <f t="shared" si="10"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="595" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A595" s="19" t="s">
         <v>1711</v>
       </c>
@@ -48448,11 +47216,10 @@
       <c r="Y595" s="14"/>
       <c r="Z595" s="15"/>
       <c r="AA595" s="16">
-        <f t="shared" si="10"/>
         <v>0.29166666666666663</v>
       </c>
     </row>
-    <row r="596" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A596" s="6" t="s">
         <v>1713</v>
       </c>
@@ -48516,11 +47283,10 @@
       <c r="Y596" s="14"/>
       <c r="Z596" s="15"/>
       <c r="AA596" s="16">
-        <f t="shared" si="10"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
-    <row r="597" spans="1:27" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:30" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A597" s="6" t="s">
         <v>1759</v>
       </c>
@@ -48565,9 +47331,11 @@
       <c r="X597" s="14"/>
       <c r="Y597" s="14"/>
       <c r="Z597" s="15"/>
-      <c r="AA597" s="16"/>
-    </row>
-    <row r="598" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AA597" s="16">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="598" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A598" s="6" t="s">
         <v>1715</v>
       </c>
@@ -48629,20 +47397,10 @@
       <c r="Y598" s="14"/>
       <c r="Z598" s="15"/>
       <c r="AA598" s="16">
-        <f t="shared" ref="AA598:AA610" si="11">(
-IF(R598="ENVIADO A LA CE/UM",1/3,IF(R598="ENTREGADO/REVISIÓN",2/3,IF(R598="ENVIADO A TICS",1,0)))+
-IF(S598="EN PROCESO",0,IF(S598="CONCLUIDO",1,0))+
-IF(T598="ENVIADO A LA CE/UM",1/3,IF(T598="EN REVISIÓN CENTRAL",2/3,IF(T598="CONCLUIDO",1,0)))+
-IF(U598="ENVIADO A LA CE/UM",1/3,IF(U598="EN REVISIÓN CENTRAL",2/3,IF(U598="CONCLUIDO",1,0)))+
-IF(V598="ENVIADO",1/3,IF(V598="EN PROCESO",2/3,IF(V598="CONCLUIDO",1,0)))+
-IF(W598="PROGRAMADAS",0,IF(W598="CONCLUIDAS",1,0))+
-IF(X598="SI",1,IF(X598="NO",0,0))+
-IF(Y598="SI",1,IF(Y598="NO",0,0))
-)/8</f>
         <v>0</v>
       </c>
     </row>
-    <row r="599" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A599" s="23" t="s">
         <v>1719</v>
       </c>
@@ -48706,11 +47464,10 @@
       <c r="Y599" s="14"/>
       <c r="Z599" s="15"/>
       <c r="AA599" s="16">
-        <f t="shared" si="11"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
-    <row r="600" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A600" s="23" t="s">
         <v>1724</v>
       </c>
@@ -48774,11 +47531,10 @@
       <c r="Y600" s="14"/>
       <c r="Z600" s="15"/>
       <c r="AA600" s="16">
-        <f t="shared" si="11"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
-    <row r="601" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A601" s="23" t="s">
         <v>1726</v>
       </c>
@@ -48842,11 +47598,11 @@
       <c r="Y601" s="14"/>
       <c r="Z601" s="15"/>
       <c r="AA601" s="16">
-        <f t="shared" si="11"/>
         <v>4.1666666666666664E-2</v>
       </c>
-    </row>
-    <row r="602" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AD601" s="29"/>
+    </row>
+    <row r="602" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A602" s="6" t="s">
         <v>1728</v>
       </c>
@@ -48916,11 +47672,10 @@
       <c r="Y602" s="14"/>
       <c r="Z602" s="15"/>
       <c r="AA602" s="16">
-        <f t="shared" si="11"/>
         <v>0.29166666666666663</v>
       </c>
     </row>
-    <row r="603" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A603" s="23" t="s">
         <v>1730</v>
       </c>
@@ -48984,11 +47739,10 @@
       <c r="Y603" s="14"/>
       <c r="Z603" s="15"/>
       <c r="AA603" s="16">
-        <f t="shared" si="11"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="604" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A604" s="23" t="s">
         <v>1732</v>
       </c>
@@ -49052,11 +47806,10 @@
       <c r="Y604" s="14"/>
       <c r="Z604" s="15"/>
       <c r="AA604" s="16">
-        <f t="shared" si="11"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="605" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A605" s="23" t="s">
         <v>1734</v>
       </c>
@@ -49126,11 +47879,10 @@
       <c r="Y605" s="14"/>
       <c r="Z605" s="15"/>
       <c r="AA605" s="16">
-        <f t="shared" si="11"/>
         <v>0.29166666666666663</v>
       </c>
     </row>
-    <row r="606" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A606" s="23" t="s">
         <v>1736</v>
       </c>
@@ -49194,11 +47946,10 @@
       <c r="Y606" s="14"/>
       <c r="Z606" s="15"/>
       <c r="AA606" s="16">
-        <f t="shared" si="11"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
-    <row r="607" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A607" s="23" t="s">
         <v>1738</v>
       </c>
@@ -49262,11 +48013,10 @@
       <c r="Y607" s="14"/>
       <c r="Z607" s="15"/>
       <c r="AA607" s="16">
-        <f t="shared" si="11"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
-    <row r="608" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A608" s="23" t="s">
         <v>1740</v>
       </c>
@@ -49330,7 +48080,6 @@
       <c r="Y608" s="14"/>
       <c r="Z608" s="15"/>
       <c r="AA608" s="16">
-        <f t="shared" si="11"/>
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -49398,7 +48147,6 @@
       <c r="Y609" s="14"/>
       <c r="Z609" s="15"/>
       <c r="AA609" s="16">
-        <f t="shared" si="11"/>
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
@@ -49465,8 +48213,7 @@
       <c r="X610" s="14"/>
       <c r="Y610" s="14"/>
       <c r="Z610" s="15"/>
-      <c r="AA610" s="16">
-        <f t="shared" si="11"/>
+      <c r="AA610" s="30">
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
@@ -49539,63 +48286,119 @@
       <c r="X611" s="14"/>
       <c r="Y611" s="14"/>
       <c r="Z611" s="15"/>
-      <c r="AA611" s="29">
-        <v>0</v>
+      <c r="AA611" s="30">
+        <v>0.20833333333333331</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="S1:V1">
-    <cfRule type="containsText" dxfId="90" priority="33" operator="containsText" text="CONCLUIDO">
-      <formula>NOT(ISERROR(SEARCH("CONCLUIDO",S1)))</formula>
+  <conditionalFormatting sqref="A598:A609">
+    <cfRule type="duplicateValues" dxfId="26" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P611">
+    <cfRule type="containsText" dxfId="25" priority="10" operator="containsText" text="ENVIADO A TICS">
+      <formula>NOT(ISERROR(SEARCH("ENVIADO A TICS",P611)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="24" priority="11" operator="containsText" text="ENTREGADO/REVISIÓN">
+      <formula>NOT(ISERROR(SEARCH("ENTREGADO/REVISIÓN",P611)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="23" priority="12" operator="containsText" text="ENVIADO A LA CE/UM">
+      <formula>NOT(ISERROR(SEARCH("ENVIADO A LA CE/UM",P611)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1">
-    <cfRule type="containsText" dxfId="89" priority="39" operator="containsText" text="ENVIADO A TICS">
+  <conditionalFormatting sqref="Q611">
+    <cfRule type="containsText" dxfId="22" priority="9" operator="containsText" text="EN PROCESO">
+      <formula>NOT(ISERROR(SEARCH("EN PROCESO",Q611)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q611:T611 S1:V610">
+    <cfRule type="containsText" dxfId="21" priority="18" operator="containsText" text="CONCLUIDO">
+      <formula>NOT(ISERROR(SEARCH("CONCLUIDO",Q1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R1:R610">
+    <cfRule type="containsText" dxfId="20" priority="24" operator="containsText" text="ENVIADO A TICS">
       <formula>NOT(ISERROR(SEARCH("ENVIADO A TICS",R1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="88" priority="40" operator="containsText" text="ENTREGADO/REVISIÓN">
+    <cfRule type="containsText" dxfId="19" priority="25" operator="containsText" text="ENTREGADO/REVISIÓN">
       <formula>NOT(ISERROR(SEARCH("ENTREGADO/REVISIÓN",R1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="87" priority="41" operator="containsText" text="ENVIADO A LA CE/UM">
+    <cfRule type="containsText" dxfId="18" priority="26" operator="containsText" text="ENVIADO A LA CE/UM">
       <formula>NOT(ISERROR(SEARCH("ENVIADO A LA CE/UM",R1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S1">
-    <cfRule type="containsText" dxfId="86" priority="38" operator="containsText" text="EN PROCESO">
+  <conditionalFormatting sqref="R611:S611">
+    <cfRule type="containsText" dxfId="17" priority="7" operator="containsText" text="EN REVISIÓN CENTRAL">
+      <formula>NOT(ISERROR(SEARCH("EN REVISIÓN CENTRAL",R611)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="16" priority="8" operator="containsText" text="ENVIADO A LA CE/UM">
+      <formula>NOT(ISERROR(SEARCH("ENVIADO A LA CE/UM",R611)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S1:S610">
+    <cfRule type="containsText" dxfId="15" priority="23" operator="containsText" text="EN PROCESO">
       <formula>NOT(ISERROR(SEARCH("EN PROCESO",S1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1">
-    <cfRule type="containsText" dxfId="85" priority="37" operator="containsText" text="ENVIADO A LA CE/UM">
+    <cfRule type="containsText" dxfId="14" priority="37" operator="containsText" text="ENVIADO A LA CE/UM">
       <formula>NOT(ISERROR(SEARCH("ENVIADO A LA CE/UM",T1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T1:U1">
-    <cfRule type="containsText" dxfId="84" priority="36" operator="containsText" text="EN REVISIÓN CENTRAL">
+  <conditionalFormatting sqref="T611">
+    <cfRule type="containsText" dxfId="13" priority="5" operator="containsText" text="EN PROCESO">
+      <formula>NOT(ISERROR(SEARCH("EN PROCESO",T611)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="12" priority="6" operator="containsText" text="ENVIADO">
+      <formula>NOT(ISERROR(SEARCH("ENVIADO",T611)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T1:U610">
+    <cfRule type="containsText" dxfId="11" priority="21" operator="containsText" text="EN REVISIÓN CENTRAL">
       <formula>NOT(ISERROR(SEARCH("EN REVISIÓN CENTRAL",T1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V1">
-    <cfRule type="containsText" dxfId="83" priority="34" operator="containsText" text="EN PROCESO">
+  <conditionalFormatting sqref="T2:U610">
+    <cfRule type="containsText" dxfId="10" priority="22" operator="containsText" text="ENVIADO A LA CE/UM">
+      <formula>NOT(ISERROR(SEARCH("ENVIADO A LA CE/UM",T2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U611">
+    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="CONCLUIDAS">
+      <formula>NOT(ISERROR(SEARCH("CONCLUIDAS",U611)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="8" priority="4" operator="containsText" text="PROGRAMADAS">
+      <formula>NOT(ISERROR(SEARCH("PROGRAMADAS",U611)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V1:V610">
+    <cfRule type="containsText" dxfId="7" priority="19" operator="containsText" text="EN PROCESO">
       <formula>NOT(ISERROR(SEARCH("EN PROCESO",V1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="82" priority="35" operator="containsText" text="ENVIADO">
+    <cfRule type="containsText" dxfId="6" priority="20" operator="containsText" text="ENVIADO">
       <formula>NOT(ISERROR(SEARCH("ENVIADO",V1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W1">
-    <cfRule type="containsText" dxfId="81" priority="31" operator="containsText" text="CONCLUIDAS">
+  <conditionalFormatting sqref="V611:Y611">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="SI">
+      <formula>NOT(ISERROR(SEARCH("SI",V611)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="NO">
+      <formula>NOT(ISERROR(SEARCH("NO",V611)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W1:W610">
+    <cfRule type="containsText" dxfId="3" priority="16" operator="containsText" text="CONCLUIDAS">
       <formula>NOT(ISERROR(SEARCH("CONCLUIDAS",W1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="80" priority="32" operator="containsText" text="PROGRAMADAS">
+    <cfRule type="containsText" dxfId="2" priority="17" operator="containsText" text="PROGRAMADAS">
       <formula>NOT(ISERROR(SEARCH("PROGRAMADAS",W1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X1:Y1">
-    <cfRule type="containsText" dxfId="79" priority="29" operator="containsText" text="SI">
+  <conditionalFormatting sqref="X1:Y610">
+    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="SI">
       <formula>NOT(ISERROR(SEARCH("SI",X1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="78" priority="30" operator="containsText" text="NO">
+    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",X1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -49613,112 +48416,6 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A598:A609">
-    <cfRule type="duplicateValues" dxfId="25" priority="27"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P611">
-    <cfRule type="containsText" dxfId="24" priority="10" operator="containsText" text="ENVIADO A TICS">
-      <formula>NOT(ISERROR(SEARCH("ENVIADO A TICS",P611)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="23" priority="11" operator="containsText" text="ENTREGADO/REVISIÓN">
-      <formula>NOT(ISERROR(SEARCH("ENTREGADO/REVISIÓN",P611)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="12" operator="containsText" text="ENVIADO A LA CE/UM">
-      <formula>NOT(ISERROR(SEARCH("ENVIADO A LA CE/UM",P611)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q611">
-    <cfRule type="containsText" dxfId="21" priority="9" operator="containsText" text="EN PROCESO">
-      <formula>NOT(ISERROR(SEARCH("EN PROCESO",Q611)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q611:T611 S2:V610">
-    <cfRule type="containsText" dxfId="20" priority="18" operator="containsText" text="CONCLUIDO">
-      <formula>NOT(ISERROR(SEARCH("CONCLUIDO",Q2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R610">
-    <cfRule type="containsText" dxfId="19" priority="24" operator="containsText" text="ENVIADO A TICS">
-      <formula>NOT(ISERROR(SEARCH("ENVIADO A TICS",R2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="25" operator="containsText" text="ENTREGADO/REVISIÓN">
-      <formula>NOT(ISERROR(SEARCH("ENTREGADO/REVISIÓN",R2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="17" priority="26" operator="containsText" text="ENVIADO A LA CE/UM">
-      <formula>NOT(ISERROR(SEARCH("ENVIADO A LA CE/UM",R2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R611:S611">
-    <cfRule type="containsText" dxfId="16" priority="7" operator="containsText" text="EN REVISIÓN CENTRAL">
-      <formula>NOT(ISERROR(SEARCH("EN REVISIÓN CENTRAL",R611)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="15" priority="8" operator="containsText" text="ENVIADO A LA CE/UM">
-      <formula>NOT(ISERROR(SEARCH("ENVIADO A LA CE/UM",R611)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S610">
-    <cfRule type="containsText" dxfId="14" priority="23" operator="containsText" text="EN PROCESO">
-      <formula>NOT(ISERROR(SEARCH("EN PROCESO",S2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T2:U610">
-    <cfRule type="containsText" dxfId="13" priority="22" operator="containsText" text="ENVIADO A LA CE/UM">
-      <formula>NOT(ISERROR(SEARCH("ENVIADO A LA CE/UM",T2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T611">
-    <cfRule type="containsText" dxfId="12" priority="5" operator="containsText" text="EN PROCESO">
-      <formula>NOT(ISERROR(SEARCH("EN PROCESO",T611)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="6" operator="containsText" text="ENVIADO">
-      <formula>NOT(ISERROR(SEARCH("ENVIADO",T611)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T2:U610">
-    <cfRule type="containsText" dxfId="10" priority="21" operator="containsText" text="EN REVISIÓN CENTRAL">
-      <formula>NOT(ISERROR(SEARCH("EN REVISIÓN CENTRAL",T2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U611">
-    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="CONCLUIDAS">
-      <formula>NOT(ISERROR(SEARCH("CONCLUIDAS",U611)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="4" operator="containsText" text="PROGRAMADAS">
-      <formula>NOT(ISERROR(SEARCH("PROGRAMADAS",U611)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V610">
-    <cfRule type="containsText" dxfId="7" priority="19" operator="containsText" text="EN PROCESO">
-      <formula>NOT(ISERROR(SEARCH("EN PROCESO",V2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="20" operator="containsText" text="ENVIADO">
-      <formula>NOT(ISERROR(SEARCH("ENVIADO",V2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V611:Y611">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="SI">
-      <formula>NOT(ISERROR(SEARCH("SI",V611)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="NO">
-      <formula>NOT(ISERROR(SEARCH("NO",V611)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W2:W610">
-    <cfRule type="containsText" dxfId="3" priority="16" operator="containsText" text="CONCLUIDAS">
-      <formula>NOT(ISERROR(SEARCH("CONCLUIDAS",W2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="17" operator="containsText" text="PROGRAMADAS">
-      <formula>NOT(ISERROR(SEARCH("PROGRAMADAS",W2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X2:Y610">
-    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="SI">
-      <formula>NOT(ISERROR(SEARCH("SI",X2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="NO">
-      <formula>NOT(ISERROR(SEARCH("NO",X2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="AA2:AA611">
     <cfRule type="dataBar" priority="13">
       <dataBar>
@@ -49734,22 +48431,22 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V610 T611" xr:uid="{E182C281-8D99-4250-9672-8DF000BCCDDF}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V610 T611" xr:uid="{1C9486F6-8D0D-4A38-8FD8-8BC1FACE1A7B}">
       <formula1>"ENVIADO,EN PROCESO,CONCLUIDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R611:S611 T2:U610" xr:uid="{0D841925-00F0-48C3-82B0-5C8AA227DA19}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R611:S611 T2:U610" xr:uid="{2FA95037-028E-4376-9982-B44E5DD112F1}">
       <formula1>"ENVIADO A LA CE/UM,EN REVISIÓN CENTRAL,CONCLUIDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S610 Q611" xr:uid="{D2F206EF-FC7E-4FDE-9046-1C62198CBB51}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S610 Q611" xr:uid="{AE0DEDFC-13F6-40BA-BF00-44396BDF1740}">
       <formula1>"EN PROCESO,CONCLUIDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P611 R2:R610" xr:uid="{2BA40F43-2B04-4770-B578-B1B99B01F353}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P611 R2:R610" xr:uid="{61991F0D-90D9-4210-9723-5F3260BED9A8}">
       <formula1>"ENVIADO A LA CE/UM,ENTREGADO/REVISIÓN,ENVIADO A TICS"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W610 U611" xr:uid="{2181B86A-4E55-47D7-A43E-43268A4D518E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W610 U611" xr:uid="{93D09A22-3806-427E-A1A6-DE87934522C3}">
       <formula1>"PROGRAMADAS,CONCLUIDAS"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:Y610 V611:Y611" xr:uid="{3D099820-6040-405E-B9CA-AB7E11640952}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:Y610 V611:Y611" xr:uid="{698981F1-D065-4917-AB40-600ACA84DACE}">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
   </dataValidations>

--- a/excel/unidades.xlsx
+++ b/excel/unidades.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daniel.jimenez\Documents\dev\implementacion_eds_imb\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{410D42FE-D3D2-4321-990A-B6F64A290D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B13F07-013F-4956-B917-C8427A5EA86B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{A71EBC0A-EF77-4480-B2A6-100C25EC669C}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$AA$611</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7955" uniqueCount="1771">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7990" uniqueCount="1771">
   <si>
     <t>CLUES</t>
   </si>
@@ -5629,14 +5632,161 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="48">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7C80"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7C80"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7C80"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7C80"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7C80"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7C80"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7C80"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7C80"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7C80"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF7C80"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -15372,7 +15522,7 @@
         <v>-102.289435</v>
       </c>
       <c r="R126" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S126" s="14"/>
       <c r="T126" s="14"/>
@@ -15383,7 +15533,7 @@
       <c r="Y126" s="14"/>
       <c r="Z126" s="15"/>
       <c r="AA126" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="127" spans="1:27" x14ac:dyDescent="0.3">
@@ -15439,7 +15589,7 @@
         <v>-103.663438</v>
       </c>
       <c r="R127" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S127" s="14"/>
       <c r="T127" s="14"/>
@@ -15450,7 +15600,7 @@
       <c r="Y127" s="14"/>
       <c r="Z127" s="15"/>
       <c r="AA127" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="128" spans="1:27" x14ac:dyDescent="0.3">
@@ -15506,7 +15656,7 @@
         <v>-102.08839500000001</v>
       </c>
       <c r="R128" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S128" s="14"/>
       <c r="T128" s="14"/>
@@ -15517,7 +15667,7 @@
       <c r="Y128" s="14"/>
       <c r="Z128" s="15"/>
       <c r="AA128" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="129" spans="1:27" x14ac:dyDescent="0.3">
@@ -15573,7 +15723,7 @@
         <v>-100.551917</v>
       </c>
       <c r="R129" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S129" s="14"/>
       <c r="T129" s="14"/>
@@ -15584,7 +15734,7 @@
       <c r="Y129" s="14"/>
       <c r="Z129" s="15"/>
       <c r="AA129" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="130" spans="1:27" x14ac:dyDescent="0.3">
@@ -15640,7 +15790,7 @@
         <v>-101.139718</v>
       </c>
       <c r="R130" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S130" s="14"/>
       <c r="T130" s="14"/>
@@ -15651,7 +15801,7 @@
       <c r="Y130" s="14"/>
       <c r="Z130" s="15"/>
       <c r="AA130" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="131" spans="1:27" x14ac:dyDescent="0.3">
@@ -15707,7 +15857,7 @@
         <v>-101.819063</v>
       </c>
       <c r="R131" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S131" s="14"/>
       <c r="T131" s="14"/>
@@ -15718,7 +15868,7 @@
       <c r="Y131" s="14"/>
       <c r="Z131" s="15"/>
       <c r="AA131" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="132" spans="1:27" x14ac:dyDescent="0.3">
@@ -15774,7 +15924,7 @@
         <v>-103.341942</v>
       </c>
       <c r="R132" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S132" s="14"/>
       <c r="T132" s="14"/>
@@ -15785,7 +15935,7 @@
       <c r="Y132" s="14"/>
       <c r="Z132" s="15"/>
       <c r="AA132" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="133" spans="1:27" x14ac:dyDescent="0.3">
@@ -16117,7 +16267,7 @@
         <v>-105.3677335</v>
       </c>
       <c r="R137" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S137" s="14"/>
       <c r="T137" s="14"/>
@@ -16128,7 +16278,7 @@
       <c r="Y137" s="14"/>
       <c r="Z137" s="15"/>
       <c r="AA137" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="138" spans="1:27" x14ac:dyDescent="0.3">
@@ -16184,7 +16334,7 @@
         <v>-104.3780574</v>
       </c>
       <c r="R138" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S138" s="14"/>
       <c r="T138" s="14"/>
@@ -16195,7 +16345,7 @@
       <c r="Y138" s="14"/>
       <c r="Z138" s="15"/>
       <c r="AA138" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="139" spans="1:27" x14ac:dyDescent="0.3">
@@ -16251,7 +16401,7 @@
         <v>-104.5171004</v>
       </c>
       <c r="R139" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S139" s="14"/>
       <c r="T139" s="14"/>
@@ -16262,7 +16412,7 @@
       <c r="Y139" s="14"/>
       <c r="Z139" s="15"/>
       <c r="AA139" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="140" spans="1:27" x14ac:dyDescent="0.3">
@@ -16318,7 +16468,7 @@
         <v>-104.08296</v>
       </c>
       <c r="R140" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S140" s="14"/>
       <c r="T140" s="14"/>
@@ -16329,7 +16479,7 @@
       <c r="Y140" s="14"/>
       <c r="Z140" s="15"/>
       <c r="AA140" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="141" spans="1:27" x14ac:dyDescent="0.3">
@@ -16385,7 +16535,7 @@
         <v>-105.29866920000001</v>
       </c>
       <c r="R141" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S141" s="14"/>
       <c r="T141" s="14"/>
@@ -16396,7 +16546,7 @@
       <c r="Y141" s="14"/>
       <c r="Z141" s="15"/>
       <c r="AA141" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="142" spans="1:27" x14ac:dyDescent="0.3">
@@ -16452,7 +16602,7 @@
         <v>-104.8913778</v>
       </c>
       <c r="R142" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S142" s="14"/>
       <c r="T142" s="14"/>
@@ -16463,7 +16613,7 @@
       <c r="Y142" s="14"/>
       <c r="Z142" s="15"/>
       <c r="AA142" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="143" spans="1:27" x14ac:dyDescent="0.3">
@@ -16519,7 +16669,7 @@
         <v>-105.45058400000001</v>
       </c>
       <c r="R143" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S143" s="14"/>
       <c r="T143" s="14"/>
@@ -16530,7 +16680,7 @@
       <c r="Y143" s="14"/>
       <c r="Z143" s="15"/>
       <c r="AA143" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="144" spans="1:27" x14ac:dyDescent="0.3">
@@ -16586,7 +16736,7 @@
         <v>-105.134699</v>
       </c>
       <c r="R144" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S144" s="14"/>
       <c r="T144" s="14"/>
@@ -16597,7 +16747,7 @@
       <c r="Y144" s="14"/>
       <c r="Z144" s="15"/>
       <c r="AA144" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="145" spans="1:27" x14ac:dyDescent="0.3">
@@ -16653,7 +16803,7 @@
         <v>-105.3119832</v>
       </c>
       <c r="R145" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S145" s="14"/>
       <c r="T145" s="14"/>
@@ -16664,7 +16814,7 @@
       <c r="Y145" s="14"/>
       <c r="Z145" s="15"/>
       <c r="AA145" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="146" spans="1:27" x14ac:dyDescent="0.3">
@@ -17993,7 +18143,7 @@
         <v>-97.855073500000003</v>
       </c>
       <c r="R165" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S165" s="14"/>
       <c r="T165" s="14"/>
@@ -18004,7 +18154,7 @@
       <c r="Y165" s="14"/>
       <c r="Z165" s="15"/>
       <c r="AA165" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="166" spans="1:27" x14ac:dyDescent="0.3">
@@ -18060,7 +18210,7 @@
         <v>-97.409838399999998</v>
       </c>
       <c r="R166" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S166" s="14"/>
       <c r="T166" s="14"/>
@@ -18071,7 +18221,7 @@
       <c r="Y166" s="14"/>
       <c r="Z166" s="15"/>
       <c r="AA166" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="167" spans="1:27" x14ac:dyDescent="0.3">
@@ -18127,7 +18277,7 @@
         <v>-97.157081899999994</v>
       </c>
       <c r="R167" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S167" s="14"/>
       <c r="T167" s="14"/>
@@ -18138,7 +18288,7 @@
       <c r="Y167" s="14"/>
       <c r="Z167" s="15"/>
       <c r="AA167" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="168" spans="1:27" x14ac:dyDescent="0.3">
@@ -18194,7 +18344,7 @@
         <v>-97.615153500000005</v>
       </c>
       <c r="R168" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S168" s="14"/>
       <c r="T168" s="14"/>
@@ -18205,7 +18355,7 @@
       <c r="Y168" s="14"/>
       <c r="Z168" s="15"/>
       <c r="AA168" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="169" spans="1:27" x14ac:dyDescent="0.3">
@@ -18261,7 +18411,7 @@
         <v>-97.624335200000004</v>
       </c>
       <c r="R169" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S169" s="14"/>
       <c r="T169" s="14"/>
@@ -18272,7 +18422,7 @@
       <c r="Y169" s="14"/>
       <c r="Z169" s="15"/>
       <c r="AA169" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="170" spans="1:27" x14ac:dyDescent="0.3">
@@ -18328,7 +18478,7 @@
         <v>-97.818262300000001</v>
       </c>
       <c r="R170" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S170" s="14"/>
       <c r="T170" s="14"/>
@@ -18339,7 +18489,7 @@
       <c r="Y170" s="14"/>
       <c r="Z170" s="15"/>
       <c r="AA170" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="171" spans="1:27" x14ac:dyDescent="0.3">
@@ -18395,7 +18545,7 @@
         <v>-97.509792000000004</v>
       </c>
       <c r="R171" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S171" s="14"/>
       <c r="T171" s="14"/>
@@ -18406,7 +18556,7 @@
       <c r="Y171" s="14"/>
       <c r="Z171" s="15"/>
       <c r="AA171" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="172" spans="1:27" x14ac:dyDescent="0.3">
@@ -18462,7 +18612,7 @@
         <v>-98.434539999999998</v>
       </c>
       <c r="R172" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S172" s="14"/>
       <c r="T172" s="14"/>
@@ -18473,7 +18623,7 @@
       <c r="Y172" s="14"/>
       <c r="Z172" s="15"/>
       <c r="AA172" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="173" spans="1:27" x14ac:dyDescent="0.3">
@@ -18529,7 +18679,7 @@
         <v>-98.313500899999994</v>
       </c>
       <c r="R173" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S173" s="14"/>
       <c r="T173" s="14"/>
@@ -18540,7 +18690,7 @@
       <c r="Y173" s="14"/>
       <c r="Z173" s="15"/>
       <c r="AA173" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="174" spans="1:27" x14ac:dyDescent="0.3">
@@ -18596,7 +18746,7 @@
         <v>-98.445998900000006</v>
       </c>
       <c r="R174" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S174" s="14"/>
       <c r="T174" s="14"/>
@@ -18607,7 +18757,7 @@
       <c r="Y174" s="14"/>
       <c r="Z174" s="15"/>
       <c r="AA174" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="175" spans="1:27" x14ac:dyDescent="0.3">
@@ -18663,7 +18813,7 @@
         <v>-97.721253099999998</v>
       </c>
       <c r="R175" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S175" s="14"/>
       <c r="T175" s="14"/>
@@ -18674,7 +18824,7 @@
       <c r="Y175" s="14"/>
       <c r="Z175" s="15"/>
       <c r="AA175" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="176" spans="1:27" x14ac:dyDescent="0.3">
@@ -18730,7 +18880,7 @@
         <v>-97.034808100000006</v>
       </c>
       <c r="R176" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S176" s="14"/>
       <c r="T176" s="14"/>
@@ -18741,7 +18891,7 @@
       <c r="Y176" s="14"/>
       <c r="Z176" s="15"/>
       <c r="AA176" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="177" spans="1:27" x14ac:dyDescent="0.3">
@@ -18797,7 +18947,7 @@
         <v>-97.928800100000004</v>
       </c>
       <c r="R177" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S177" s="14"/>
       <c r="T177" s="14"/>
@@ -18808,7 +18958,7 @@
       <c r="Y177" s="14"/>
       <c r="Z177" s="15"/>
       <c r="AA177" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="178" spans="1:27" x14ac:dyDescent="0.3">
@@ -18864,7 +19014,7 @@
         <v>-97.799322900000007</v>
       </c>
       <c r="R178" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S178" s="14"/>
       <c r="T178" s="14"/>
@@ -18875,7 +19025,7 @@
       <c r="Y178" s="14"/>
       <c r="Z178" s="15"/>
       <c r="AA178" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="179" spans="1:27" x14ac:dyDescent="0.3">
@@ -18931,7 +19081,7 @@
         <v>-97.274599199999997</v>
       </c>
       <c r="R179" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S179" s="14"/>
       <c r="T179" s="14"/>
@@ -18942,7 +19092,7 @@
       <c r="Y179" s="14"/>
       <c r="Z179" s="15"/>
       <c r="AA179" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="180" spans="1:27" x14ac:dyDescent="0.3">
@@ -18998,7 +19148,7 @@
         <v>-97.631644100000003</v>
       </c>
       <c r="R180" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S180" s="14"/>
       <c r="T180" s="14"/>
@@ -19009,7 +19159,7 @@
       <c r="Y180" s="14"/>
       <c r="Z180" s="15"/>
       <c r="AA180" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="181" spans="1:27" x14ac:dyDescent="0.3">
@@ -19065,7 +19215,7 @@
         <v>-97.851676299999994</v>
       </c>
       <c r="R181" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S181" s="14"/>
       <c r="T181" s="14"/>
@@ -19076,7 +19226,7 @@
       <c r="Y181" s="14"/>
       <c r="Z181" s="15"/>
       <c r="AA181" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="182" spans="1:27" x14ac:dyDescent="0.3">
@@ -19132,7 +19282,7 @@
         <v>-97.206224300000002</v>
       </c>
       <c r="R182" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S182" s="14"/>
       <c r="T182" s="14"/>
@@ -19143,7 +19293,7 @@
       <c r="Y182" s="14"/>
       <c r="Z182" s="15"/>
       <c r="AA182" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="183" spans="1:27" x14ac:dyDescent="0.3">
@@ -19199,7 +19349,7 @@
         <v>-96.864161100000004</v>
       </c>
       <c r="R183" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S183" s="14"/>
       <c r="T183" s="14"/>
@@ -19210,7 +19360,7 @@
       <c r="Y183" s="14"/>
       <c r="Z183" s="15"/>
       <c r="AA183" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="184" spans="1:27" x14ac:dyDescent="0.3">
@@ -19266,7 +19416,7 @@
         <v>-97.332424200000005</v>
       </c>
       <c r="R184" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S184" s="14"/>
       <c r="T184" s="14"/>
@@ -19277,7 +19427,7 @@
       <c r="Y184" s="14"/>
       <c r="Z184" s="15"/>
       <c r="AA184" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="185" spans="1:27" x14ac:dyDescent="0.3">
@@ -19333,7 +19483,7 @@
         <v>-97.589125199999998</v>
       </c>
       <c r="R185" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S185" s="14"/>
       <c r="T185" s="14"/>
@@ -19344,7 +19494,7 @@
       <c r="Y185" s="14"/>
       <c r="Z185" s="15"/>
       <c r="AA185" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="186" spans="1:27" x14ac:dyDescent="0.3">
@@ -19400,7 +19550,7 @@
         <v>-97.756586400000003</v>
       </c>
       <c r="R186" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S186" s="14"/>
       <c r="T186" s="14"/>
@@ -19411,7 +19561,7 @@
       <c r="Y186" s="14"/>
       <c r="Z186" s="15"/>
       <c r="AA186" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="187" spans="1:27" x14ac:dyDescent="0.3">
@@ -19467,7 +19617,7 @@
         <v>-97.947517199999993</v>
       </c>
       <c r="R187" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S187" s="14"/>
       <c r="T187" s="14"/>
@@ -19478,7 +19628,7 @@
       <c r="Y187" s="14"/>
       <c r="Z187" s="15"/>
       <c r="AA187" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="188" spans="1:27" x14ac:dyDescent="0.3">
@@ -19534,7 +19684,7 @@
         <v>-97.537684200000001</v>
       </c>
       <c r="R188" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S188" s="14"/>
       <c r="T188" s="14"/>
@@ -19545,7 +19695,7 @@
       <c r="Y188" s="14"/>
       <c r="Z188" s="15"/>
       <c r="AA188" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="189" spans="1:27" x14ac:dyDescent="0.3">
@@ -19601,7 +19751,7 @@
         <v>-97.965180399999994</v>
       </c>
       <c r="R189" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S189" s="14"/>
       <c r="T189" s="14"/>
@@ -19612,7 +19762,7 @@
       <c r="Y189" s="14"/>
       <c r="Z189" s="15"/>
       <c r="AA189" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="190" spans="1:27" x14ac:dyDescent="0.3">
@@ -19668,7 +19818,7 @@
         <v>-97.1398923</v>
       </c>
       <c r="R190" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S190" s="14"/>
       <c r="T190" s="14"/>
@@ -19679,7 +19829,7 @@
       <c r="Y190" s="14"/>
       <c r="Z190" s="15"/>
       <c r="AA190" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="191" spans="1:27" x14ac:dyDescent="0.3">
@@ -19735,7 +19885,7 @@
         <v>-97.832876900000002</v>
       </c>
       <c r="R191" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S191" s="14"/>
       <c r="T191" s="14"/>
@@ -19746,7 +19896,7 @@
       <c r="Y191" s="14"/>
       <c r="Z191" s="15"/>
       <c r="AA191" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="192" spans="1:27" x14ac:dyDescent="0.3">
@@ -19802,7 +19952,7 @@
         <v>-98.065132500000004</v>
       </c>
       <c r="R192" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S192" s="14"/>
       <c r="T192" s="14"/>
@@ -19813,7 +19963,7 @@
       <c r="Y192" s="14"/>
       <c r="Z192" s="15"/>
       <c r="AA192" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="193" spans="1:27" x14ac:dyDescent="0.3">
@@ -19869,7 +20019,7 @@
         <v>-97.813686000000004</v>
       </c>
       <c r="R193" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S193" s="14"/>
       <c r="T193" s="14"/>
@@ -19880,7 +20030,7 @@
       <c r="Y193" s="14"/>
       <c r="Z193" s="15"/>
       <c r="AA193" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="194" spans="1:27" x14ac:dyDescent="0.3">
@@ -19936,7 +20086,7 @@
         <v>-98.1575433</v>
       </c>
       <c r="R194" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S194" s="14"/>
       <c r="T194" s="14"/>
@@ -19947,7 +20097,7 @@
       <c r="Y194" s="14"/>
       <c r="Z194" s="15"/>
       <c r="AA194" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="195" spans="1:27" x14ac:dyDescent="0.3">
@@ -20003,7 +20153,7 @@
         <v>-97.685379999999995</v>
       </c>
       <c r="R195" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S195" s="14"/>
       <c r="T195" s="14"/>
@@ -20014,7 +20164,7 @@
       <c r="Y195" s="14"/>
       <c r="Z195" s="15"/>
       <c r="AA195" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="196" spans="1:27" x14ac:dyDescent="0.3">
@@ -20472,7 +20622,7 @@
         <v>-99.016046000000003</v>
       </c>
       <c r="R202" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S202" s="14"/>
       <c r="T202" s="14"/>
@@ -20483,7 +20633,7 @@
       <c r="Y202" s="14"/>
       <c r="Z202" s="15"/>
       <c r="AA202" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="203" spans="1:27" x14ac:dyDescent="0.3">
@@ -20539,7 +20689,7 @@
         <v>-99.606881999999999</v>
       </c>
       <c r="R203" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S203" s="14"/>
       <c r="T203" s="14"/>
@@ -20550,7 +20700,7 @@
       <c r="Y203" s="14"/>
       <c r="Z203" s="15"/>
       <c r="AA203" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="204" spans="1:27" x14ac:dyDescent="0.3">
@@ -20606,7 +20756,7 @@
         <v>-101.72011999999999</v>
       </c>
       <c r="R204" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S204" s="14"/>
       <c r="T204" s="14"/>
@@ -20617,7 +20767,7 @@
       <c r="Y204" s="14"/>
       <c r="Z204" s="15"/>
       <c r="AA204" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="205" spans="1:27" x14ac:dyDescent="0.3">
@@ -20673,7 +20823,7 @@
         <v>-98.75067</v>
       </c>
       <c r="R205" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S205" s="14"/>
       <c r="T205" s="14"/>
@@ -20684,7 +20834,7 @@
       <c r="Y205" s="14"/>
       <c r="Z205" s="15"/>
       <c r="AA205" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="206" spans="1:27" x14ac:dyDescent="0.3">
@@ -20740,7 +20890,7 @@
         <v>-100.83897</v>
       </c>
       <c r="R206" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S206" s="14"/>
       <c r="T206" s="14"/>
@@ -20751,7 +20901,7 @@
       <c r="Y206" s="14"/>
       <c r="Z206" s="15"/>
       <c r="AA206" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="207" spans="1:27" x14ac:dyDescent="0.3">
@@ -20807,7 +20957,7 @@
         <v>-98.379060999999993</v>
       </c>
       <c r="R207" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S207" s="14"/>
       <c r="T207" s="14"/>
@@ -20818,7 +20968,7 @@
       <c r="Y207" s="14"/>
       <c r="Z207" s="15"/>
       <c r="AA207" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="208" spans="1:27" x14ac:dyDescent="0.3">
@@ -20874,7 +21024,7 @@
         <v>-98.788833299999993</v>
       </c>
       <c r="R208" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S208" s="14"/>
       <c r="T208" s="14"/>
@@ -20885,7 +21035,7 @@
       <c r="Y208" s="14"/>
       <c r="Z208" s="15"/>
       <c r="AA208" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="209" spans="1:27" x14ac:dyDescent="0.3">
@@ -20941,7 +21091,7 @@
         <v>-99.006029999999996</v>
       </c>
       <c r="R209" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S209" s="14"/>
       <c r="T209" s="14"/>
@@ -20952,7 +21102,7 @@
       <c r="Y209" s="14"/>
       <c r="Z209" s="15"/>
       <c r="AA209" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="210" spans="1:27" x14ac:dyDescent="0.3">
@@ -21008,7 +21158,7 @@
         <v>-108.1564539</v>
       </c>
       <c r="R210" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S210" s="14"/>
       <c r="T210" s="14"/>
@@ -21019,7 +21169,7 @@
       <c r="Y210" s="14"/>
       <c r="Z210" s="15"/>
       <c r="AA210" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="211" spans="1:27" x14ac:dyDescent="0.3">
@@ -21075,7 +21225,7 @@
         <v>-107.5551293</v>
       </c>
       <c r="R211" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S211" s="14"/>
       <c r="T211" s="14"/>
@@ -21086,7 +21236,7 @@
       <c r="Y211" s="14"/>
       <c r="Z211" s="15"/>
       <c r="AA211" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="212" spans="1:27" x14ac:dyDescent="0.3">
@@ -21142,7 +21292,7 @@
         <v>-106.066862</v>
       </c>
       <c r="R212" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S212" s="14"/>
       <c r="T212" s="14"/>
@@ -21153,7 +21303,7 @@
       <c r="Y212" s="14"/>
       <c r="Z212" s="15"/>
       <c r="AA212" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="213" spans="1:27" x14ac:dyDescent="0.3">
@@ -21209,7 +21359,7 @@
         <v>-106.6910791</v>
       </c>
       <c r="R213" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S213" s="14"/>
       <c r="T213" s="14"/>
@@ -21220,7 +21370,7 @@
       <c r="Y213" s="14"/>
       <c r="Z213" s="15"/>
       <c r="AA213" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="214" spans="1:27" x14ac:dyDescent="0.3">
@@ -21276,7 +21426,7 @@
         <v>-108.3234903</v>
       </c>
       <c r="R214" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S214" s="14"/>
       <c r="T214" s="14"/>
@@ -21287,7 +21437,7 @@
       <c r="Y214" s="14"/>
       <c r="Z214" s="15"/>
       <c r="AA214" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="215" spans="1:27" x14ac:dyDescent="0.3">
@@ -21343,7 +21493,7 @@
         <v>-107.92313729999999</v>
       </c>
       <c r="R215" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S215" s="14"/>
       <c r="T215" s="14"/>
@@ -21354,7 +21504,7 @@
       <c r="Y215" s="14"/>
       <c r="Z215" s="15"/>
       <c r="AA215" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="216" spans="1:27" x14ac:dyDescent="0.3">
@@ -21410,7 +21560,7 @@
         <v>-105.8566385</v>
       </c>
       <c r="R216" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S216" s="14"/>
       <c r="T216" s="14"/>
@@ -21421,7 +21571,7 @@
       <c r="Y216" s="14"/>
       <c r="Z216" s="15"/>
       <c r="AA216" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="217" spans="1:27" x14ac:dyDescent="0.3">
@@ -21477,7 +21627,7 @@
         <v>-108.2297748</v>
       </c>
       <c r="R217" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S217" s="14"/>
       <c r="T217" s="14"/>
@@ -21488,7 +21638,7 @@
       <c r="Y217" s="14"/>
       <c r="Z217" s="15"/>
       <c r="AA217" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="218" spans="1:27" x14ac:dyDescent="0.3">
@@ -21544,7 +21694,7 @@
         <v>-107.68260789999999</v>
       </c>
       <c r="R218" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S218" s="14"/>
       <c r="T218" s="14"/>
@@ -21555,7 +21705,7 @@
       <c r="Y218" s="14"/>
       <c r="Z218" s="15"/>
       <c r="AA218" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="219" spans="1:27" x14ac:dyDescent="0.3">
@@ -21611,7 +21761,7 @@
         <v>-109.03464200000001</v>
       </c>
       <c r="R219" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S219" s="14"/>
       <c r="T219" s="14"/>
@@ -21622,7 +21772,7 @@
       <c r="Y219" s="14"/>
       <c r="Z219" s="15"/>
       <c r="AA219" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="220" spans="1:27" x14ac:dyDescent="0.3">
@@ -21678,7 +21828,7 @@
         <v>-106.4231693</v>
       </c>
       <c r="R220" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S220" s="14"/>
       <c r="T220" s="14"/>
@@ -21689,7 +21839,7 @@
       <c r="Y220" s="14"/>
       <c r="Z220" s="15"/>
       <c r="AA220" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="221" spans="1:27" x14ac:dyDescent="0.3">
@@ -21745,7 +21895,7 @@
         <v>-107.1508884</v>
       </c>
       <c r="R221" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S221" s="14"/>
       <c r="T221" s="14"/>
@@ -21756,7 +21906,7 @@
       <c r="Y221" s="14"/>
       <c r="Z221" s="15"/>
       <c r="AA221" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="222" spans="1:27" x14ac:dyDescent="0.3">
@@ -22249,7 +22399,9 @@
       <c r="Q228" s="13">
         <v>-92.813005099999998</v>
       </c>
-      <c r="R228" s="14"/>
+      <c r="R228" s="14" t="s">
+        <v>176</v>
+      </c>
       <c r="S228" s="14"/>
       <c r="T228" s="14"/>
       <c r="U228" s="14"/>
@@ -22259,7 +22411,7 @@
       <c r="Y228" s="14"/>
       <c r="Z228" s="15"/>
       <c r="AA228" s="16">
-        <v>0</v>
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="229" spans="1:27" x14ac:dyDescent="0.3">
@@ -22314,7 +22466,9 @@
       <c r="Q229" s="13">
         <v>-93.058869799999997</v>
       </c>
-      <c r="R229" s="14"/>
+      <c r="R229" s="14" t="s">
+        <v>176</v>
+      </c>
       <c r="S229" s="14"/>
       <c r="T229" s="14"/>
       <c r="U229" s="14"/>
@@ -22324,7 +22478,7 @@
       <c r="Y229" s="14"/>
       <c r="Z229" s="15"/>
       <c r="AA229" s="16">
-        <v>0</v>
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="230" spans="1:27" x14ac:dyDescent="0.3">
@@ -22379,7 +22533,9 @@
       <c r="Q230" s="13">
         <v>-93.016657199999997</v>
       </c>
-      <c r="R230" s="14"/>
+      <c r="R230" s="14" t="s">
+        <v>176</v>
+      </c>
       <c r="S230" s="14"/>
       <c r="T230" s="14"/>
       <c r="U230" s="14"/>
@@ -22389,7 +22545,7 @@
       <c r="Y230" s="14"/>
       <c r="Z230" s="15"/>
       <c r="AA230" s="16">
-        <v>0</v>
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="231" spans="1:27" x14ac:dyDescent="0.3">
@@ -22444,7 +22600,9 @@
       <c r="Q231" s="13">
         <v>-92.830547600000003</v>
       </c>
-      <c r="R231" s="14"/>
+      <c r="R231" s="14" t="s">
+        <v>176</v>
+      </c>
       <c r="S231" s="14"/>
       <c r="T231" s="14"/>
       <c r="U231" s="14"/>
@@ -22454,7 +22612,7 @@
       <c r="Y231" s="14"/>
       <c r="Z231" s="15"/>
       <c r="AA231" s="16">
-        <v>0</v>
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="232" spans="1:27" x14ac:dyDescent="0.3">
@@ -22509,7 +22667,9 @@
       <c r="Q232" s="13">
         <v>-94.040238000000002</v>
       </c>
-      <c r="R232" s="14"/>
+      <c r="R232" s="14" t="s">
+        <v>176</v>
+      </c>
       <c r="S232" s="14"/>
       <c r="T232" s="14"/>
       <c r="U232" s="14"/>
@@ -22519,7 +22679,7 @@
       <c r="Y232" s="14"/>
       <c r="Z232" s="15"/>
       <c r="AA232" s="16">
-        <v>0</v>
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="233" spans="1:27" x14ac:dyDescent="0.3">
@@ -22574,7 +22734,9 @@
       <c r="Q233" s="13">
         <v>-92.128299999999996</v>
       </c>
-      <c r="R233" s="14"/>
+      <c r="R233" s="14" t="s">
+        <v>176</v>
+      </c>
       <c r="S233" s="14"/>
       <c r="T233" s="14"/>
       <c r="U233" s="14"/>
@@ -22584,7 +22746,7 @@
       <c r="Y233" s="14"/>
       <c r="Z233" s="15"/>
       <c r="AA233" s="16">
-        <v>0</v>
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="234" spans="1:27" x14ac:dyDescent="0.3">
@@ -22639,7 +22801,9 @@
       <c r="Q234" s="13">
         <v>-92.644352999999995</v>
       </c>
-      <c r="R234" s="14"/>
+      <c r="R234" s="14" t="s">
+        <v>176</v>
+      </c>
       <c r="S234" s="14"/>
       <c r="T234" s="14"/>
       <c r="U234" s="14"/>
@@ -22649,7 +22813,7 @@
       <c r="Y234" s="14"/>
       <c r="Z234" s="15"/>
       <c r="AA234" s="16">
-        <v>0</v>
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="235" spans="1:27" x14ac:dyDescent="0.3">
@@ -22906,9 +23070,11 @@
         <v>-97.647458900000004</v>
       </c>
       <c r="R238" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="S238" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="S238" s="14" t="s">
+        <v>175</v>
+      </c>
       <c r="T238" s="14"/>
       <c r="U238" s="14"/>
       <c r="V238" s="14"/>
@@ -22917,7 +23083,7 @@
       <c r="Y238" s="14"/>
       <c r="Z238" s="15"/>
       <c r="AA238" s="16">
-        <v>8.3333333333333329E-2</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="239" spans="1:27" x14ac:dyDescent="0.3">
@@ -22973,9 +23139,11 @@
         <v>-98.1694806</v>
       </c>
       <c r="R239" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="S239" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="S239" s="14" t="s">
+        <v>175</v>
+      </c>
       <c r="T239" s="14"/>
       <c r="U239" s="14"/>
       <c r="V239" s="14"/>
@@ -22984,7 +23152,7 @@
       <c r="Y239" s="14"/>
       <c r="Z239" s="15"/>
       <c r="AA239" s="16">
-        <v>8.3333333333333329E-2</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="240" spans="1:27" x14ac:dyDescent="0.3">
@@ -23040,9 +23208,11 @@
         <v>-98.249111099999993</v>
       </c>
       <c r="R240" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="S240" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="S240" s="14" t="s">
+        <v>175</v>
+      </c>
       <c r="T240" s="14"/>
       <c r="U240" s="14"/>
       <c r="V240" s="14"/>
@@ -23051,7 +23221,7 @@
       <c r="Y240" s="14"/>
       <c r="Z240" s="15"/>
       <c r="AA240" s="16">
-        <v>8.3333333333333329E-2</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="241" spans="1:27" x14ac:dyDescent="0.3">
@@ -23107,9 +23277,11 @@
         <v>-98.127930599999999</v>
       </c>
       <c r="R241" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="S241" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="S241" s="14" t="s">
+        <v>175</v>
+      </c>
       <c r="T241" s="14"/>
       <c r="U241" s="14"/>
       <c r="V241" s="14"/>
@@ -23118,7 +23290,7 @@
       <c r="Y241" s="14"/>
       <c r="Z241" s="15"/>
       <c r="AA241" s="16">
-        <v>8.3333333333333329E-2</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="242" spans="1:27" x14ac:dyDescent="0.3">
@@ -31888,7 +32060,7 @@
         <v>-101.95326</v>
       </c>
       <c r="R368" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S368" s="14"/>
       <c r="T368" s="14"/>
@@ -31899,7 +32071,7 @@
       <c r="Y368" s="14"/>
       <c r="Z368" s="15"/>
       <c r="AA368" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="369" spans="1:27" x14ac:dyDescent="0.3">
@@ -31955,7 +32127,7 @@
         <v>-102.20205</v>
       </c>
       <c r="R369" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S369" s="14"/>
       <c r="T369" s="14"/>
@@ -31966,7 +32138,7 @@
       <c r="Y369" s="14"/>
       <c r="Z369" s="15"/>
       <c r="AA369" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="370" spans="1:27" x14ac:dyDescent="0.3">
@@ -32022,7 +32194,7 @@
         <v>-101.1825135</v>
       </c>
       <c r="R370" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S370" s="14"/>
       <c r="T370" s="14"/>
@@ -32033,7 +32205,7 @@
       <c r="Y370" s="14"/>
       <c r="Z370" s="15"/>
       <c r="AA370" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="371" spans="1:27" x14ac:dyDescent="0.3">
@@ -32089,7 +32261,7 @@
         <v>-102.718266</v>
       </c>
       <c r="R371" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S371" s="14"/>
       <c r="T371" s="14"/>
@@ -32100,7 +32272,7 @@
       <c r="Y371" s="14"/>
       <c r="Z371" s="15"/>
       <c r="AA371" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="372" spans="1:27" x14ac:dyDescent="0.3">
@@ -32156,7 +32328,7 @@
         <v>-101.455314</v>
       </c>
       <c r="R372" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S372" s="14"/>
       <c r="T372" s="14"/>
@@ -32167,7 +32339,7 @@
       <c r="Y372" s="14"/>
       <c r="Z372" s="15"/>
       <c r="AA372" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="373" spans="1:27" x14ac:dyDescent="0.3">
@@ -32223,7 +32395,7 @@
         <v>-102.024055</v>
       </c>
       <c r="R373" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S373" s="14"/>
       <c r="T373" s="14"/>
@@ -32234,7 +32406,7 @@
       <c r="Y373" s="14"/>
       <c r="Z373" s="15"/>
       <c r="AA373" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="374" spans="1:27" x14ac:dyDescent="0.3">
@@ -32290,7 +32462,7 @@
         <v>-102.279183</v>
       </c>
       <c r="R374" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S374" s="14"/>
       <c r="T374" s="14"/>
@@ -32301,7 +32473,7 @@
       <c r="Y374" s="14"/>
       <c r="Z374" s="15"/>
       <c r="AA374" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="375" spans="1:27" x14ac:dyDescent="0.3">
@@ -32357,7 +32529,7 @@
         <v>-100.36944269999999</v>
       </c>
       <c r="R375" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S375" s="14"/>
       <c r="T375" s="14"/>
@@ -32368,7 +32540,7 @@
       <c r="Y375" s="14"/>
       <c r="Z375" s="15"/>
       <c r="AA375" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="376" spans="1:27" x14ac:dyDescent="0.3">
@@ -32424,7 +32596,7 @@
         <v>-101.752934</v>
       </c>
       <c r="R376" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S376" s="14"/>
       <c r="T376" s="14"/>
@@ -32435,7 +32607,7 @@
       <c r="Y376" s="14"/>
       <c r="Z376" s="15"/>
       <c r="AA376" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="377" spans="1:27" x14ac:dyDescent="0.3">
@@ -32491,7 +32663,7 @@
         <v>-101.577988</v>
       </c>
       <c r="R377" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S377" s="14"/>
       <c r="T377" s="14"/>
@@ -32502,7 +32674,7 @@
       <c r="Y377" s="14"/>
       <c r="Z377" s="15"/>
       <c r="AA377" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="378" spans="1:27" x14ac:dyDescent="0.3">
@@ -32558,7 +32730,7 @@
         <v>-101.105271</v>
       </c>
       <c r="R378" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S378" s="14"/>
       <c r="T378" s="14"/>
@@ -32569,7 +32741,7 @@
       <c r="Y378" s="14"/>
       <c r="Z378" s="15"/>
       <c r="AA378" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="379" spans="1:27" x14ac:dyDescent="0.3">
@@ -32625,7 +32797,7 @@
         <v>-100.4513</v>
       </c>
       <c r="R379" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S379" s="14"/>
       <c r="T379" s="14"/>
@@ -32636,7 +32808,7 @@
       <c r="Y379" s="14"/>
       <c r="Z379" s="15"/>
       <c r="AA379" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="380" spans="1:27" x14ac:dyDescent="0.3">
@@ -32692,7 +32864,7 @@
         <v>-101.52354800000001</v>
       </c>
       <c r="R380" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S380" s="14"/>
       <c r="T380" s="14"/>
@@ -32703,7 +32875,7 @@
       <c r="Y380" s="14"/>
       <c r="Z380" s="15"/>
       <c r="AA380" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="381" spans="1:27" x14ac:dyDescent="0.3">
@@ -32759,7 +32931,7 @@
         <v>-100.517276</v>
       </c>
       <c r="R381" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S381" s="14"/>
       <c r="T381" s="14"/>
@@ -32770,7 +32942,7 @@
       <c r="Y381" s="14"/>
       <c r="Z381" s="15"/>
       <c r="AA381" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="382" spans="1:27" x14ac:dyDescent="0.3">
@@ -32826,7 +32998,7 @@
         <v>-102.475351</v>
       </c>
       <c r="R382" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S382" s="14"/>
       <c r="T382" s="14"/>
@@ -32837,7 +33009,7 @@
       <c r="Y382" s="14"/>
       <c r="Z382" s="15"/>
       <c r="AA382" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="383" spans="1:27" x14ac:dyDescent="0.3">
@@ -32893,7 +33065,7 @@
         <v>-102.018441</v>
       </c>
       <c r="R383" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S383" s="14"/>
       <c r="T383" s="14"/>
@@ -32904,7 +33076,7 @@
       <c r="Y383" s="14"/>
       <c r="Z383" s="15"/>
       <c r="AA383" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="384" spans="1:27" x14ac:dyDescent="0.3">
@@ -32960,7 +33132,7 @@
         <v>-102.325361</v>
       </c>
       <c r="R384" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S384" s="14"/>
       <c r="T384" s="14"/>
@@ -32971,7 +33143,7 @@
       <c r="Y384" s="14"/>
       <c r="Z384" s="15"/>
       <c r="AA384" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="385" spans="1:27" x14ac:dyDescent="0.3">
@@ -33429,7 +33601,7 @@
         <v>-105.2094934</v>
       </c>
       <c r="R391" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S391" s="14"/>
       <c r="T391" s="14"/>
@@ -33440,7 +33612,7 @@
       <c r="Y391" s="14"/>
       <c r="Z391" s="15"/>
       <c r="AA391" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="392" spans="1:27" x14ac:dyDescent="0.3">
@@ -33496,7 +33668,7 @@
         <v>-104.89762899999999</v>
       </c>
       <c r="R392" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S392" s="14"/>
       <c r="T392" s="14"/>
@@ -33507,7 +33679,7 @@
       <c r="Y392" s="14"/>
       <c r="Z392" s="15"/>
       <c r="AA392" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="393" spans="1:27" x14ac:dyDescent="0.3">
@@ -33563,7 +33735,7 @@
         <v>-105.4103064</v>
       </c>
       <c r="R393" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S393" s="14"/>
       <c r="T393" s="14"/>
@@ -33574,7 +33746,7 @@
       <c r="Y393" s="14"/>
       <c r="Z393" s="15"/>
       <c r="AA393" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="394" spans="1:27" x14ac:dyDescent="0.3">
@@ -33630,7 +33802,7 @@
         <v>-105.20890110000001</v>
       </c>
       <c r="R394" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S394" s="14"/>
       <c r="T394" s="14"/>
@@ -33641,7 +33813,7 @@
       <c r="Y394" s="14"/>
       <c r="Z394" s="15"/>
       <c r="AA394" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="395" spans="1:27" x14ac:dyDescent="0.3">
@@ -34635,7 +34807,7 @@
         <v>-97.449621899999997</v>
       </c>
       <c r="R409" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S409" s="14"/>
       <c r="T409" s="14"/>
@@ -34646,7 +34818,7 @@
       <c r="Y409" s="14"/>
       <c r="Z409" s="15"/>
       <c r="AA409" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="410" spans="1:27" x14ac:dyDescent="0.3">
@@ -34702,7 +34874,7 @@
         <v>-97.680264800000003</v>
       </c>
       <c r="R410" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S410" s="14"/>
       <c r="T410" s="14"/>
@@ -34713,7 +34885,7 @@
       <c r="Y410" s="14"/>
       <c r="Z410" s="15"/>
       <c r="AA410" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="411" spans="1:27" x14ac:dyDescent="0.3">
@@ -34769,7 +34941,7 @@
         <v>-98.242134199999995</v>
       </c>
       <c r="R411" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S411" s="14"/>
       <c r="T411" s="14"/>
@@ -34780,7 +34952,7 @@
       <c r="Y411" s="14"/>
       <c r="Z411" s="15"/>
       <c r="AA411" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="412" spans="1:27" x14ac:dyDescent="0.3">
@@ -34836,7 +35008,7 @@
         <v>-97.419533000000001</v>
       </c>
       <c r="R412" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S412" s="14"/>
       <c r="T412" s="14"/>
@@ -34847,7 +35019,7 @@
       <c r="Y412" s="14"/>
       <c r="Z412" s="15"/>
       <c r="AA412" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="413" spans="1:27" x14ac:dyDescent="0.3">
@@ -34903,7 +35075,7 @@
         <v>-98.265913800000007</v>
       </c>
       <c r="R413" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S413" s="14"/>
       <c r="T413" s="14"/>
@@ -34914,7 +35086,7 @@
       <c r="Y413" s="14"/>
       <c r="Z413" s="15"/>
       <c r="AA413" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="414" spans="1:27" x14ac:dyDescent="0.3">
@@ -34970,7 +35142,7 @@
         <v>-97.376941599999995</v>
       </c>
       <c r="R414" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S414" s="14"/>
       <c r="T414" s="14"/>
@@ -34981,7 +35153,7 @@
       <c r="Y414" s="14"/>
       <c r="Z414" s="15"/>
       <c r="AA414" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="415" spans="1:27" x14ac:dyDescent="0.3">
@@ -35037,7 +35209,7 @@
         <v>-98.056408899999994</v>
       </c>
       <c r="R415" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S415" s="14"/>
       <c r="T415" s="14"/>
@@ -35048,7 +35220,7 @@
       <c r="Y415" s="14"/>
       <c r="Z415" s="15"/>
       <c r="AA415" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="416" spans="1:27" x14ac:dyDescent="0.3">
@@ -35104,7 +35276,7 @@
         <v>-97.498489199999995</v>
       </c>
       <c r="R416" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S416" s="14"/>
       <c r="T416" s="14"/>
@@ -35115,7 +35287,7 @@
       <c r="Y416" s="14"/>
       <c r="Z416" s="15"/>
       <c r="AA416" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="417" spans="1:27" x14ac:dyDescent="0.3">
@@ -35171,7 +35343,7 @@
         <v>-98.380429399999997</v>
       </c>
       <c r="R417" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S417" s="14"/>
       <c r="T417" s="14"/>
@@ -35182,7 +35354,7 @@
       <c r="Y417" s="14"/>
       <c r="Z417" s="15"/>
       <c r="AA417" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="418" spans="1:27" x14ac:dyDescent="0.3">
@@ -35238,7 +35410,7 @@
         <v>-98.415797999999995</v>
       </c>
       <c r="R418" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S418" s="14"/>
       <c r="T418" s="14"/>
@@ -35249,7 +35421,7 @@
       <c r="Y418" s="14"/>
       <c r="Z418" s="15"/>
       <c r="AA418" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="419" spans="1:27" x14ac:dyDescent="0.3">
@@ -35305,7 +35477,7 @@
         <v>-98.198704899999996</v>
       </c>
       <c r="R419" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S419" s="14"/>
       <c r="T419" s="14"/>
@@ -35316,7 +35488,7 @@
       <c r="Y419" s="14"/>
       <c r="Z419" s="15"/>
       <c r="AA419" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="420" spans="1:27" x14ac:dyDescent="0.3">
@@ -35372,7 +35544,7 @@
         <v>-98.185216600000004</v>
       </c>
       <c r="R420" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S420" s="14"/>
       <c r="T420" s="14"/>
@@ -35383,7 +35555,7 @@
       <c r="Y420" s="14"/>
       <c r="Z420" s="15"/>
       <c r="AA420" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="421" spans="1:27" x14ac:dyDescent="0.3">
@@ -35439,7 +35611,7 @@
         <v>-97.904352900000006</v>
       </c>
       <c r="R421" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S421" s="14"/>
       <c r="T421" s="14"/>
@@ -35450,7 +35622,7 @@
       <c r="Y421" s="14"/>
       <c r="Z421" s="15"/>
       <c r="AA421" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="422" spans="1:27" x14ac:dyDescent="0.3">
@@ -35506,7 +35678,7 @@
         <v>-97.962584399999997</v>
       </c>
       <c r="R422" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S422" s="14"/>
       <c r="T422" s="14"/>
@@ -35517,7 +35689,7 @@
       <c r="Y422" s="14"/>
       <c r="Z422" s="15"/>
       <c r="AA422" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="423" spans="1:27" x14ac:dyDescent="0.3">
@@ -35573,7 +35745,7 @@
         <v>-98.069181200000003</v>
       </c>
       <c r="R423" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S423" s="14"/>
       <c r="T423" s="14"/>
@@ -35584,7 +35756,7 @@
       <c r="Y423" s="14"/>
       <c r="Z423" s="15"/>
       <c r="AA423" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="424" spans="1:27" x14ac:dyDescent="0.3">
@@ -35640,7 +35812,7 @@
         <v>-98.451244700000004</v>
       </c>
       <c r="R424" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S424" s="14"/>
       <c r="T424" s="14"/>
@@ -35651,7 +35823,7 @@
       <c r="Y424" s="14"/>
       <c r="Z424" s="15"/>
       <c r="AA424" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="425" spans="1:27" x14ac:dyDescent="0.3">
@@ -35707,7 +35879,7 @@
         <v>-97.531135000000006</v>
       </c>
       <c r="R425" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S425" s="14"/>
       <c r="T425" s="14"/>
@@ -35718,7 +35890,7 @@
       <c r="Y425" s="14"/>
       <c r="Z425" s="15"/>
       <c r="AA425" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="426" spans="1:27" x14ac:dyDescent="0.3">
@@ -35774,7 +35946,7 @@
         <v>-97.714111700000004</v>
       </c>
       <c r="R426" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S426" s="14"/>
       <c r="T426" s="14"/>
@@ -35785,7 +35957,7 @@
       <c r="Y426" s="14"/>
       <c r="Z426" s="15"/>
       <c r="AA426" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="427" spans="1:27" x14ac:dyDescent="0.3">
@@ -36243,7 +36415,7 @@
         <v>-98.993797999999998</v>
       </c>
       <c r="R433" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S433" s="14"/>
       <c r="T433" s="14"/>
@@ -36254,7 +36426,7 @@
       <c r="Y433" s="14"/>
       <c r="Z433" s="15"/>
       <c r="AA433" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="434" spans="1:27" x14ac:dyDescent="0.3">
@@ -36310,7 +36482,7 @@
         <v>-99.991885100000005</v>
       </c>
       <c r="R434" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S434" s="14"/>
       <c r="T434" s="14"/>
@@ -36321,7 +36493,7 @@
       <c r="Y434" s="14"/>
       <c r="Z434" s="15"/>
       <c r="AA434" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="435" spans="1:27" x14ac:dyDescent="0.3">
@@ -36377,7 +36549,7 @@
         <v>-100.653531</v>
       </c>
       <c r="R435" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S435" s="14"/>
       <c r="T435" s="14"/>
@@ -36388,7 +36560,7 @@
       <c r="Y435" s="14"/>
       <c r="Z435" s="15"/>
       <c r="AA435" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="436" spans="1:27" x14ac:dyDescent="0.3">
@@ -36444,7 +36616,7 @@
         <v>-101.014679</v>
       </c>
       <c r="R436" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S436" s="14"/>
       <c r="T436" s="14"/>
@@ -36455,7 +36627,7 @@
       <c r="Y436" s="14"/>
       <c r="Z436" s="15"/>
       <c r="AA436" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="437" spans="1:27" x14ac:dyDescent="0.3">
@@ -36511,7 +36683,7 @@
         <v>-100.938266</v>
       </c>
       <c r="R437" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S437" s="14"/>
       <c r="T437" s="14"/>
@@ -36522,7 +36694,7 @@
       <c r="Y437" s="14"/>
       <c r="Z437" s="15"/>
       <c r="AA437" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="438" spans="1:27" x14ac:dyDescent="0.3">
@@ -36578,7 +36750,7 @@
         <v>-107.3660201</v>
       </c>
       <c r="R438" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S438" s="14"/>
       <c r="T438" s="14"/>
@@ -36589,7 +36761,7 @@
       <c r="Y438" s="14"/>
       <c r="Z438" s="15"/>
       <c r="AA438" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="439" spans="1:27" x14ac:dyDescent="0.3">
@@ -36645,7 +36817,7 @@
         <v>-108.988561</v>
       </c>
       <c r="R439" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S439" s="14"/>
       <c r="T439" s="14"/>
@@ -36656,7 +36828,7 @@
       <c r="Y439" s="14"/>
       <c r="Z439" s="15"/>
       <c r="AA439" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="440" spans="1:27" x14ac:dyDescent="0.3">
@@ -36712,7 +36884,7 @@
         <v>-108.4751021</v>
       </c>
       <c r="R440" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S440" s="14"/>
       <c r="T440" s="14"/>
@@ -36723,7 +36895,7 @@
       <c r="Y440" s="14"/>
       <c r="Z440" s="15"/>
       <c r="AA440" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="441" spans="1:27" x14ac:dyDescent="0.3">
@@ -36779,7 +36951,7 @@
         <v>-106.45269999999999</v>
       </c>
       <c r="R441" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S441" s="14"/>
       <c r="T441" s="14"/>
@@ -36790,7 +36962,7 @@
       <c r="Y441" s="14"/>
       <c r="Z441" s="15"/>
       <c r="AA441" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="442" spans="1:27" x14ac:dyDescent="0.3">
@@ -36846,7 +37018,7 @@
         <v>-106.8759673</v>
       </c>
       <c r="R442" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S442" s="14"/>
       <c r="T442" s="14"/>
@@ -36857,7 +37029,7 @@
       <c r="Y442" s="14"/>
       <c r="Z442" s="15"/>
       <c r="AA442" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="443" spans="1:27" x14ac:dyDescent="0.3">
@@ -36913,7 +37085,7 @@
         <v>-105.77733449999999</v>
       </c>
       <c r="R443" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S443" s="14"/>
       <c r="T443" s="14"/>
@@ -36924,7 +37096,7 @@
       <c r="Y443" s="14"/>
       <c r="Z443" s="15"/>
       <c r="AA443" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="444" spans="1:27" x14ac:dyDescent="0.3">
@@ -36980,7 +37152,7 @@
         <v>-107.36495909999999</v>
       </c>
       <c r="R444" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S444" s="14"/>
       <c r="T444" s="14"/>
@@ -36991,7 +37163,7 @@
       <c r="Y444" s="14"/>
       <c r="Z444" s="15"/>
       <c r="AA444" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="445" spans="1:27" x14ac:dyDescent="0.3">
@@ -37776,7 +37948,9 @@
       <c r="Q455" s="13">
         <v>-91.533500000000004</v>
       </c>
-      <c r="R455" s="14"/>
+      <c r="R455" s="14" t="s">
+        <v>176</v>
+      </c>
       <c r="S455" s="14"/>
       <c r="T455" s="14"/>
       <c r="U455" s="14"/>
@@ -37786,7 +37960,7 @@
       <c r="Y455" s="14"/>
       <c r="Z455" s="15"/>
       <c r="AA455" s="16">
-        <v>0</v>
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="456" spans="1:27" x14ac:dyDescent="0.3">
@@ -37841,7 +38015,9 @@
       <c r="Q456" s="13">
         <v>-93.382786300000006</v>
       </c>
-      <c r="R456" s="14"/>
+      <c r="R456" s="14" t="s">
+        <v>176</v>
+      </c>
       <c r="S456" s="14"/>
       <c r="T456" s="14"/>
       <c r="U456" s="14"/>
@@ -37851,7 +38027,7 @@
       <c r="Y456" s="14"/>
       <c r="Z456" s="15"/>
       <c r="AA456" s="16">
-        <v>0</v>
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="457" spans="1:27" x14ac:dyDescent="0.3">
@@ -37906,7 +38082,9 @@
       <c r="Q457" s="13">
         <v>-92.924240699999999</v>
       </c>
-      <c r="R457" s="14"/>
+      <c r="R457" s="14" t="s">
+        <v>176</v>
+      </c>
       <c r="S457" s="14"/>
       <c r="T457" s="14"/>
       <c r="U457" s="14"/>
@@ -37916,7 +38094,7 @@
       <c r="Y457" s="14"/>
       <c r="Z457" s="15"/>
       <c r="AA457" s="16">
-        <v>0</v>
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="458" spans="1:27" x14ac:dyDescent="0.3">
@@ -37971,7 +38149,9 @@
       <c r="Q458" s="13">
         <v>-92.986235699999995</v>
       </c>
-      <c r="R458" s="14"/>
+      <c r="R458" s="14" t="s">
+        <v>176</v>
+      </c>
       <c r="S458" s="14"/>
       <c r="T458" s="14"/>
       <c r="U458" s="14"/>
@@ -37981,7 +38161,7 @@
       <c r="Y458" s="14"/>
       <c r="Z458" s="15"/>
       <c r="AA458" s="16">
-        <v>0</v>
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="459" spans="1:27" x14ac:dyDescent="0.3">
@@ -38036,7 +38216,9 @@
       <c r="Q459" s="13">
         <v>-93.172695599999997</v>
       </c>
-      <c r="R459" s="14"/>
+      <c r="R459" s="14" t="s">
+        <v>176</v>
+      </c>
       <c r="S459" s="14"/>
       <c r="T459" s="14"/>
       <c r="U459" s="14"/>
@@ -38046,7 +38228,7 @@
       <c r="Y459" s="14"/>
       <c r="Z459" s="15"/>
       <c r="AA459" s="16">
-        <v>0</v>
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="460" spans="1:27" x14ac:dyDescent="0.3">
@@ -38101,7 +38283,9 @@
       <c r="Q460" s="13">
         <v>-91.782673000000003</v>
       </c>
-      <c r="R460" s="14"/>
+      <c r="R460" s="14" t="s">
+        <v>176</v>
+      </c>
       <c r="S460" s="14"/>
       <c r="T460" s="14"/>
       <c r="U460" s="14"/>
@@ -38111,7 +38295,7 @@
       <c r="Y460" s="14"/>
       <c r="Z460" s="15"/>
       <c r="AA460" s="16">
-        <v>0</v>
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="461" spans="1:27" x14ac:dyDescent="0.3">
@@ -38166,7 +38350,9 @@
       <c r="Q461" s="13">
         <v>-93.395583000000002</v>
       </c>
-      <c r="R461" s="14"/>
+      <c r="R461" s="14" t="s">
+        <v>176</v>
+      </c>
       <c r="S461" s="14"/>
       <c r="T461" s="14"/>
       <c r="U461" s="14"/>
@@ -38176,7 +38362,7 @@
       <c r="Y461" s="14"/>
       <c r="Z461" s="15"/>
       <c r="AA461" s="16">
-        <v>0</v>
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="462" spans="1:27" x14ac:dyDescent="0.3">
@@ -38231,7 +38417,9 @@
       <c r="Q462" s="13">
         <v>-92.592980600000004</v>
       </c>
-      <c r="R462" s="14"/>
+      <c r="R462" s="14" t="s">
+        <v>176</v>
+      </c>
       <c r="S462" s="14"/>
       <c r="T462" s="14"/>
       <c r="U462" s="14"/>
@@ -38241,7 +38429,7 @@
       <c r="Y462" s="14"/>
       <c r="Z462" s="15"/>
       <c r="AA462" s="16">
-        <v>0</v>
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="463" spans="1:27" x14ac:dyDescent="0.3">
@@ -38296,7 +38484,9 @@
       <c r="Q463" s="13">
         <v>-92.529300000000006</v>
       </c>
-      <c r="R463" s="14"/>
+      <c r="R463" s="14" t="s">
+        <v>176</v>
+      </c>
       <c r="S463" s="14"/>
       <c r="T463" s="14"/>
       <c r="U463" s="14"/>
@@ -38306,7 +38496,7 @@
       <c r="Y463" s="14"/>
       <c r="Z463" s="15"/>
       <c r="AA463" s="16">
-        <v>0</v>
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="464" spans="1:27" x14ac:dyDescent="0.3">
@@ -38361,7 +38551,9 @@
       <c r="Q464" s="13">
         <v>-93.212299999999999</v>
       </c>
-      <c r="R464" s="14"/>
+      <c r="R464" s="14" t="s">
+        <v>176</v>
+      </c>
       <c r="S464" s="14"/>
       <c r="T464" s="14"/>
       <c r="U464" s="14"/>
@@ -38371,7 +38563,7 @@
       <c r="Y464" s="14"/>
       <c r="Z464" s="15"/>
       <c r="AA464" s="16">
-        <v>0</v>
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="465" spans="1:27" x14ac:dyDescent="0.3">
@@ -38426,7 +38618,9 @@
       <c r="Q465" s="13">
         <v>-92.950222199999999</v>
       </c>
-      <c r="R465" s="14"/>
+      <c r="R465" s="14" t="s">
+        <v>176</v>
+      </c>
       <c r="S465" s="14"/>
       <c r="T465" s="14"/>
       <c r="U465" s="14"/>
@@ -38436,7 +38630,7 @@
       <c r="Y465" s="14"/>
       <c r="Z465" s="15"/>
       <c r="AA465" s="16">
-        <v>0</v>
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="466" spans="1:27" x14ac:dyDescent="0.3">
@@ -38491,7 +38685,9 @@
       <c r="Q466" s="13">
         <v>-91.4114</v>
       </c>
-      <c r="R466" s="14"/>
+      <c r="R466" s="14" t="s">
+        <v>176</v>
+      </c>
       <c r="S466" s="14"/>
       <c r="T466" s="14"/>
       <c r="U466" s="14"/>
@@ -38501,7 +38697,7 @@
       <c r="Y466" s="14"/>
       <c r="Z466" s="15"/>
       <c r="AA466" s="16">
-        <v>0</v>
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="467" spans="1:27" x14ac:dyDescent="0.3">
@@ -38556,7 +38752,9 @@
       <c r="Q467" s="13">
         <v>-93.231950100000006</v>
       </c>
-      <c r="R467" s="14"/>
+      <c r="R467" s="14" t="s">
+        <v>176</v>
+      </c>
       <c r="S467" s="14"/>
       <c r="T467" s="14"/>
       <c r="U467" s="14"/>
@@ -38566,7 +38764,7 @@
       <c r="Y467" s="14"/>
       <c r="Z467" s="15"/>
       <c r="AA467" s="16">
-        <v>0</v>
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="468" spans="1:27" x14ac:dyDescent="0.3">
@@ -39426,9 +39624,11 @@
         <v>-98.117972199999997</v>
       </c>
       <c r="R480" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="S480" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="S480" s="14" t="s">
+        <v>175</v>
+      </c>
       <c r="T480" s="14"/>
       <c r="U480" s="14"/>
       <c r="V480" s="14"/>
@@ -39437,7 +39637,7 @@
       <c r="Y480" s="14"/>
       <c r="Z480" s="15"/>
       <c r="AA480" s="16">
-        <v>8.3333333333333329E-2</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="481" spans="1:27" x14ac:dyDescent="0.3">
@@ -39493,9 +39693,11 @@
         <v>-98.200689600000004</v>
       </c>
       <c r="R481" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="S481" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="S481" s="14" t="s">
+        <v>175</v>
+      </c>
       <c r="T481" s="14"/>
       <c r="U481" s="14"/>
       <c r="V481" s="14"/>
@@ -39504,7 +39706,7 @@
       <c r="Y481" s="14"/>
       <c r="Z481" s="15"/>
       <c r="AA481" s="16">
-        <v>8.3333333333333329E-2</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="482" spans="1:27" x14ac:dyDescent="0.3">
@@ -39560,9 +39762,11 @@
         <v>-98.216435399999995</v>
       </c>
       <c r="R482" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="S482" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="S482" s="14" t="s">
+        <v>175</v>
+      </c>
       <c r="T482" s="14"/>
       <c r="U482" s="14"/>
       <c r="V482" s="14"/>
@@ -39571,7 +39775,7 @@
       <c r="Y482" s="14"/>
       <c r="Z482" s="15"/>
       <c r="AA482" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="483" spans="1:27" x14ac:dyDescent="0.3">
@@ -39627,9 +39831,11 @@
         <v>-98.536741599999999</v>
       </c>
       <c r="R483" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="S483" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="S483" s="14" t="s">
+        <v>175</v>
+      </c>
       <c r="T483" s="14"/>
       <c r="U483" s="14"/>
       <c r="V483" s="14"/>
@@ -39638,7 +39844,7 @@
       <c r="Y483" s="14"/>
       <c r="Z483" s="15"/>
       <c r="AA483" s="16">
-        <v>8.3333333333333329E-2</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="484" spans="1:27" x14ac:dyDescent="0.3">
@@ -39694,9 +39900,11 @@
         <v>-98.317484800000003</v>
       </c>
       <c r="R484" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="S484" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="S484" s="14" t="s">
+        <v>175</v>
+      </c>
       <c r="T484" s="14"/>
       <c r="U484" s="14"/>
       <c r="V484" s="14"/>
@@ -39705,7 +39913,7 @@
       <c r="Y484" s="14"/>
       <c r="Z484" s="15"/>
       <c r="AA484" s="16">
-        <v>8.3333333333333329E-2</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="485" spans="1:27" x14ac:dyDescent="0.3">
@@ -39761,9 +39969,11 @@
         <v>-97.940791700000005</v>
       </c>
       <c r="R485" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="S485" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="S485" s="14" t="s">
+        <v>175</v>
+      </c>
       <c r="T485" s="14"/>
       <c r="U485" s="14"/>
       <c r="V485" s="14"/>
@@ -39772,7 +39982,7 @@
       <c r="Y485" s="14"/>
       <c r="Z485" s="15"/>
       <c r="AA485" s="16">
-        <v>8.3333333333333329E-2</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="486" spans="1:27" x14ac:dyDescent="0.3">
@@ -42105,9 +42315,7 @@
       <c r="Q520" s="13">
         <v>-98.855389000000002</v>
       </c>
-      <c r="R520" s="14" t="s">
-        <v>190</v>
-      </c>
+      <c r="R520" s="14"/>
       <c r="S520" s="14"/>
       <c r="T520" s="14"/>
       <c r="U520" s="14"/>
@@ -42117,7 +42325,7 @@
       <c r="Y520" s="14"/>
       <c r="Z520" s="15"/>
       <c r="AA520" s="16">
-        <v>8.3333333333333329E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="521" spans="1:27" x14ac:dyDescent="0.3">
@@ -42508,7 +42716,7 @@
         <v>-101.154067</v>
       </c>
       <c r="R526" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S526" s="14"/>
       <c r="T526" s="14"/>
@@ -42519,7 +42727,7 @@
       <c r="Y526" s="14"/>
       <c r="Z526" s="15"/>
       <c r="AA526" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="527" spans="1:27" x14ac:dyDescent="0.3">
@@ -42642,7 +42850,7 @@
         <v>-104.84592790000001</v>
       </c>
       <c r="R528" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S528" s="14"/>
       <c r="T528" s="14"/>
@@ -42653,7 +42861,7 @@
       <c r="Y528" s="14"/>
       <c r="Z528" s="15"/>
       <c r="AA528" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="529" spans="1:27" x14ac:dyDescent="0.3">
@@ -42709,7 +42917,7 @@
         <v>-98.240833499999994</v>
       </c>
       <c r="R529" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S529" s="14"/>
       <c r="T529" s="14"/>
@@ -42720,7 +42928,7 @@
       <c r="Y529" s="14"/>
       <c r="Z529" s="15"/>
       <c r="AA529" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="530" spans="1:27" x14ac:dyDescent="0.3">
@@ -42776,7 +42984,7 @@
         <v>-107.45043200000001</v>
       </c>
       <c r="R530" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S530" s="14"/>
       <c r="T530" s="14"/>
@@ -42787,7 +42995,7 @@
       <c r="Y530" s="14"/>
       <c r="Z530" s="15"/>
       <c r="AA530" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="531" spans="1:27" x14ac:dyDescent="0.3">
@@ -42843,9 +43051,11 @@
         <v>-98.212519900000004</v>
       </c>
       <c r="R531" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="S531" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="S531" s="14" t="s">
+        <v>175</v>
+      </c>
       <c r="T531" s="14"/>
       <c r="U531" s="14"/>
       <c r="V531" s="14"/>
@@ -42854,7 +43064,7 @@
       <c r="Y531" s="14"/>
       <c r="Z531" s="15"/>
       <c r="AA531" s="16">
-        <v>8.3333333333333329E-2</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="532" spans="1:27" x14ac:dyDescent="0.3">
@@ -42977,7 +43187,7 @@
         <v>-97.439687599999999</v>
       </c>
       <c r="R533" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S533" s="14"/>
       <c r="T533" s="14"/>
@@ -42988,7 +43198,7 @@
       <c r="Y533" s="14"/>
       <c r="Z533" s="15"/>
       <c r="AA533" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="534" spans="1:27" x14ac:dyDescent="0.3">
@@ -43044,7 +43254,7 @@
         <v>-100.98585</v>
       </c>
       <c r="R534" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S534" s="14"/>
       <c r="T534" s="14"/>
@@ -43055,7 +43265,7 @@
       <c r="Y534" s="14"/>
       <c r="Z534" s="15"/>
       <c r="AA534" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="535" spans="1:27" x14ac:dyDescent="0.3">
@@ -43245,7 +43455,7 @@
         <v>-101.102766</v>
       </c>
       <c r="R537" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S537" s="14"/>
       <c r="T537" s="14"/>
@@ -43256,7 +43466,7 @@
       <c r="Y537" s="14"/>
       <c r="Z537" s="15"/>
       <c r="AA537" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="538" spans="1:27" x14ac:dyDescent="0.3">
@@ -43379,9 +43589,11 @@
         <v>-98.211333300000007</v>
       </c>
       <c r="R539" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="S539" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="S539" s="14" t="s">
+        <v>175</v>
+      </c>
       <c r="T539" s="14"/>
       <c r="U539" s="14"/>
       <c r="V539" s="14"/>
@@ -43390,7 +43602,7 @@
       <c r="Y539" s="14"/>
       <c r="Z539" s="15"/>
       <c r="AA539" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="540" spans="1:27" x14ac:dyDescent="0.3">
@@ -44965,7 +45177,9 @@
       <c r="Q562" s="13">
         <v>-92.953389999999999</v>
       </c>
-      <c r="R562" s="14"/>
+      <c r="R562" s="14" t="s">
+        <v>176</v>
+      </c>
       <c r="S562" s="14"/>
       <c r="T562" s="14"/>
       <c r="U562" s="14"/>
@@ -44975,7 +45189,7 @@
       <c r="Y562" s="14"/>
       <c r="Z562" s="15"/>
       <c r="AA562" s="16">
-        <v>0</v>
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="563" spans="1:27" x14ac:dyDescent="0.3">
@@ -45098,7 +45312,7 @@
         <v>-98.244393900000006</v>
       </c>
       <c r="R564" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S564" s="14"/>
       <c r="T564" s="14"/>
@@ -45109,7 +45323,7 @@
       <c r="Y564" s="14"/>
       <c r="Z564" s="15"/>
       <c r="AA564" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="565" spans="1:27" x14ac:dyDescent="0.3">
@@ -45433,7 +45647,7 @@
         <v>-107.39942449999999</v>
       </c>
       <c r="R569" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S569" s="14"/>
       <c r="T569" s="14"/>
@@ -45444,7 +45658,7 @@
       <c r="Y569" s="14"/>
       <c r="Z569" s="15"/>
       <c r="AA569" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="570" spans="1:27" x14ac:dyDescent="0.3">
@@ -45968,7 +46182,9 @@
       <c r="Q577" s="13">
         <v>-92.952872999999997</v>
       </c>
-      <c r="R577" s="14"/>
+      <c r="R577" s="14" t="s">
+        <v>176</v>
+      </c>
       <c r="S577" s="14"/>
       <c r="T577" s="14"/>
       <c r="U577" s="14"/>
@@ -45978,7 +46194,7 @@
       <c r="Y577" s="14"/>
       <c r="Z577" s="15"/>
       <c r="AA577" s="16">
-        <v>0</v>
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="578" spans="1:27" x14ac:dyDescent="0.3">
@@ -46519,7 +46735,7 @@
         <v>-101.1554807</v>
       </c>
       <c r="R585" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S585" s="14"/>
       <c r="T585" s="14"/>
@@ -46530,7 +46746,7 @@
       <c r="Y585" s="14"/>
       <c r="Z585" s="15"/>
       <c r="AA585" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="586" spans="1:27" x14ac:dyDescent="0.3">
@@ -46653,7 +46869,7 @@
         <v>-98.182584800000001</v>
       </c>
       <c r="R587" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S587" s="14"/>
       <c r="T587" s="14"/>
@@ -46664,7 +46880,7 @@
       <c r="Y587" s="14"/>
       <c r="Z587" s="15"/>
       <c r="AA587" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="588" spans="1:27" x14ac:dyDescent="0.3">
@@ -46720,7 +46936,7 @@
         <v>-100.9015162</v>
       </c>
       <c r="R588" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S588" s="14"/>
       <c r="T588" s="14"/>
@@ -46731,7 +46947,7 @@
       <c r="Y588" s="14"/>
       <c r="Z588" s="15"/>
       <c r="AA588" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="589" spans="1:27" x14ac:dyDescent="0.3">
@@ -46787,7 +47003,7 @@
         <v>-107.4280536</v>
       </c>
       <c r="R589" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S589" s="14"/>
       <c r="T589" s="14"/>
@@ -46798,7 +47014,7 @@
       <c r="Y589" s="14"/>
       <c r="Z589" s="15"/>
       <c r="AA589" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="590" spans="1:27" x14ac:dyDescent="0.3">
@@ -46999,7 +47215,9 @@
       <c r="Q592" s="13">
         <v>-92.920878999999999</v>
       </c>
-      <c r="R592" s="14"/>
+      <c r="R592" s="14" t="s">
+        <v>176</v>
+      </c>
       <c r="S592" s="14"/>
       <c r="T592" s="14"/>
       <c r="U592" s="14"/>
@@ -47009,7 +47227,7 @@
       <c r="Y592" s="14"/>
       <c r="Z592" s="15"/>
       <c r="AA592" s="16">
-        <v>0</v>
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="593" spans="1:30" x14ac:dyDescent="0.3">
@@ -47587,7 +47805,7 @@
         <v>-98.241913999999994</v>
       </c>
       <c r="R601" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S601" s="14"/>
       <c r="T601" s="14"/>
@@ -47598,7 +47816,7 @@
       <c r="Y601" s="14"/>
       <c r="Z601" s="15"/>
       <c r="AA601" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="AD601" s="29"/>
     </row>
@@ -47728,7 +47946,7 @@
         <v>-104.89738389999999</v>
       </c>
       <c r="R603" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S603" s="14"/>
       <c r="T603" s="14"/>
@@ -47739,7 +47957,7 @@
       <c r="Y603" s="14"/>
       <c r="Z603" s="15"/>
       <c r="AA603" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="604" spans="1:30" x14ac:dyDescent="0.3">
@@ -47795,7 +48013,7 @@
         <v>-107.405</v>
       </c>
       <c r="R604" s="14" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="S604" s="14"/>
       <c r="T604" s="14"/>
@@ -47806,7 +48024,7 @@
       <c r="Y604" s="14"/>
       <c r="Z604" s="15"/>
       <c r="AA604" s="16">
-        <v>4.1666666666666664E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="605" spans="1:30" x14ac:dyDescent="0.3">
@@ -48069,9 +48287,11 @@
         <v>-98.210456899999997</v>
       </c>
       <c r="R608" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="S608" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="S608" s="14" t="s">
+        <v>175</v>
+      </c>
       <c r="T608" s="14"/>
       <c r="U608" s="14"/>
       <c r="V608" s="14"/>
@@ -48080,7 +48300,7 @@
       <c r="Y608" s="14"/>
       <c r="Z608" s="15"/>
       <c r="AA608" s="16">
-        <v>8.3333333333333329E-2</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="609" spans="1:27" x14ac:dyDescent="0.3">
@@ -48291,114 +48511,115 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AA611" xr:uid="{AB8C860C-69C5-482A-A322-88D4F7BD0ED6}"/>
   <conditionalFormatting sqref="A598:A609">
-    <cfRule type="duplicateValues" dxfId="26" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P611">
-    <cfRule type="containsText" dxfId="25" priority="10" operator="containsText" text="ENVIADO A TICS">
+    <cfRule type="containsText" dxfId="46" priority="10" operator="containsText" text="ENVIADO A TICS">
       <formula>NOT(ISERROR(SEARCH("ENVIADO A TICS",P611)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="24" priority="11" operator="containsText" text="ENTREGADO/REVISIÓN">
+    <cfRule type="containsText" dxfId="45" priority="11" operator="containsText" text="ENTREGADO/REVISIÓN">
       <formula>NOT(ISERROR(SEARCH("ENTREGADO/REVISIÓN",P611)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="23" priority="12" operator="containsText" text="ENVIADO A LA CE/UM">
+    <cfRule type="containsText" dxfId="44" priority="12" operator="containsText" text="ENVIADO A LA CE/UM">
       <formula>NOT(ISERROR(SEARCH("ENVIADO A LA CE/UM",P611)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q611">
-    <cfRule type="containsText" dxfId="22" priority="9" operator="containsText" text="EN PROCESO">
+    <cfRule type="containsText" dxfId="43" priority="9" operator="containsText" text="EN PROCESO">
       <formula>NOT(ISERROR(SEARCH("EN PROCESO",Q611)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q611:T611 S1:V610">
-    <cfRule type="containsText" dxfId="21" priority="18" operator="containsText" text="CONCLUIDO">
+    <cfRule type="containsText" dxfId="42" priority="18" operator="containsText" text="CONCLUIDO">
       <formula>NOT(ISERROR(SEARCH("CONCLUIDO",Q1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R610">
-    <cfRule type="containsText" dxfId="20" priority="24" operator="containsText" text="ENVIADO A TICS">
+    <cfRule type="containsText" dxfId="41" priority="24" operator="containsText" text="ENVIADO A TICS">
       <formula>NOT(ISERROR(SEARCH("ENVIADO A TICS",R1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="19" priority="25" operator="containsText" text="ENTREGADO/REVISIÓN">
+    <cfRule type="containsText" dxfId="40" priority="25" operator="containsText" text="ENTREGADO/REVISIÓN">
       <formula>NOT(ISERROR(SEARCH("ENTREGADO/REVISIÓN",R1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="18" priority="26" operator="containsText" text="ENVIADO A LA CE/UM">
+    <cfRule type="containsText" dxfId="39" priority="26" operator="containsText" text="ENVIADO A LA CE/UM">
       <formula>NOT(ISERROR(SEARCH("ENVIADO A LA CE/UM",R1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R611:S611">
-    <cfRule type="containsText" dxfId="17" priority="7" operator="containsText" text="EN REVISIÓN CENTRAL">
+    <cfRule type="containsText" dxfId="38" priority="7" operator="containsText" text="EN REVISIÓN CENTRAL">
       <formula>NOT(ISERROR(SEARCH("EN REVISIÓN CENTRAL",R611)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="8" operator="containsText" text="ENVIADO A LA CE/UM">
+    <cfRule type="containsText" dxfId="37" priority="8" operator="containsText" text="ENVIADO A LA CE/UM">
       <formula>NOT(ISERROR(SEARCH("ENVIADO A LA CE/UM",R611)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S1:S610">
-    <cfRule type="containsText" dxfId="15" priority="23" operator="containsText" text="EN PROCESO">
+    <cfRule type="containsText" dxfId="36" priority="23" operator="containsText" text="EN PROCESO">
       <formula>NOT(ISERROR(SEARCH("EN PROCESO",S1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1">
-    <cfRule type="containsText" dxfId="14" priority="37" operator="containsText" text="ENVIADO A LA CE/UM">
+    <cfRule type="containsText" dxfId="35" priority="37" operator="containsText" text="ENVIADO A LA CE/UM">
       <formula>NOT(ISERROR(SEARCH("ENVIADO A LA CE/UM",T1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T611">
-    <cfRule type="containsText" dxfId="13" priority="5" operator="containsText" text="EN PROCESO">
+    <cfRule type="containsText" dxfId="34" priority="5" operator="containsText" text="EN PROCESO">
       <formula>NOT(ISERROR(SEARCH("EN PROCESO",T611)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="6" operator="containsText" text="ENVIADO">
+    <cfRule type="containsText" dxfId="33" priority="6" operator="containsText" text="ENVIADO">
       <formula>NOT(ISERROR(SEARCH("ENVIADO",T611)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:U610">
-    <cfRule type="containsText" dxfId="11" priority="21" operator="containsText" text="EN REVISIÓN CENTRAL">
+    <cfRule type="containsText" dxfId="32" priority="21" operator="containsText" text="EN REVISIÓN CENTRAL">
       <formula>NOT(ISERROR(SEARCH("EN REVISIÓN CENTRAL",T1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:U610">
-    <cfRule type="containsText" dxfId="10" priority="22" operator="containsText" text="ENVIADO A LA CE/UM">
+    <cfRule type="containsText" dxfId="31" priority="22" operator="containsText" text="ENVIADO A LA CE/UM">
       <formula>NOT(ISERROR(SEARCH("ENVIADO A LA CE/UM",T2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U611">
-    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="CONCLUIDAS">
+    <cfRule type="containsText" dxfId="30" priority="3" operator="containsText" text="CONCLUIDAS">
       <formula>NOT(ISERROR(SEARCH("CONCLUIDAS",U611)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="4" operator="containsText" text="PROGRAMADAS">
+    <cfRule type="containsText" dxfId="29" priority="4" operator="containsText" text="PROGRAMADAS">
       <formula>NOT(ISERROR(SEARCH("PROGRAMADAS",U611)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1:V610">
-    <cfRule type="containsText" dxfId="7" priority="19" operator="containsText" text="EN PROCESO">
+    <cfRule type="containsText" dxfId="28" priority="19" operator="containsText" text="EN PROCESO">
       <formula>NOT(ISERROR(SEARCH("EN PROCESO",V1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="20" operator="containsText" text="ENVIADO">
+    <cfRule type="containsText" dxfId="27" priority="20" operator="containsText" text="ENVIADO">
       <formula>NOT(ISERROR(SEARCH("ENVIADO",V1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V611:Y611">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="SI">
+    <cfRule type="containsText" dxfId="26" priority="1" operator="containsText" text="SI">
       <formula>NOT(ISERROR(SEARCH("SI",V611)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="NO">
+    <cfRule type="containsText" dxfId="25" priority="2" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",V611)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W1:W610">
-    <cfRule type="containsText" dxfId="3" priority="16" operator="containsText" text="CONCLUIDAS">
+    <cfRule type="containsText" dxfId="24" priority="16" operator="containsText" text="CONCLUIDAS">
       <formula>NOT(ISERROR(SEARCH("CONCLUIDAS",W1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="17" operator="containsText" text="PROGRAMADAS">
+    <cfRule type="containsText" dxfId="23" priority="17" operator="containsText" text="PROGRAMADAS">
       <formula>NOT(ISERROR(SEARCH("PROGRAMADAS",W1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1:Y610">
-    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="SI">
+    <cfRule type="containsText" dxfId="22" priority="14" operator="containsText" text="SI">
       <formula>NOT(ISERROR(SEARCH("SI",X1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="NO">
+    <cfRule type="containsText" dxfId="21" priority="15" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",X1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48431,10 +48652,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V610 T611" xr:uid="{1C9486F6-8D0D-4A38-8FD8-8BC1FACE1A7B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V610 T611" xr:uid="{144EA7A4-E3F1-4B8F-B3DD-448343A827F4}">
       <formula1>"ENVIADO,EN PROCESO,CONCLUIDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R611:S611 T2:U610" xr:uid="{2FA95037-028E-4376-9982-B44E5DD112F1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R611:S611 T2:U610" xr:uid="{C57B23E7-D96C-4F5E-AA77-F9798C979AE5}">
       <formula1>"ENVIADO A LA CE/UM,EN REVISIÓN CENTRAL,CONCLUIDO"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S610 Q611" xr:uid="{AE0DEDFC-13F6-40BA-BF00-44396BDF1740}">
@@ -48443,10 +48664,10 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P611 R2:R610" xr:uid="{61991F0D-90D9-4210-9723-5F3260BED9A8}">
       <formula1>"ENVIADO A LA CE/UM,ENTREGADO/REVISIÓN,ENVIADO A TICS"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W610 U611" xr:uid="{93D09A22-3806-427E-A1A6-DE87934522C3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2:W610 U611" xr:uid="{86BEF544-5A91-459C-BBED-C0F6A831D4A4}">
       <formula1>"PROGRAMADAS,CONCLUIDAS"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:Y610 V611:Y611" xr:uid="{698981F1-D065-4917-AB40-600ACA84DACE}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:Y610 V611:Y611" xr:uid="{C17B1AF7-9F2A-41B8-895D-80550B40FEAA}">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
   </dataValidations>
